--- a/ระบบลางาน ออนไลน์ 2025.xlsx
+++ b/ระบบลางาน ออนไลน์ 2025.xlsx
@@ -1,19 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project APP Leave Management System -Antigravity\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835" activeTab="5"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Setting" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Users" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="UsersMenu" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Agency" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="Departments" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="UserPolicies" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="Holidays" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="DayOfWeek" sheetId="8" r:id="rId12"/>
+    <sheet name="Setting" sheetId="1" r:id="rId1"/>
+    <sheet name="Users" sheetId="2" r:id="rId2"/>
+    <sheet name="UsersMenu" sheetId="3" r:id="rId3"/>
+    <sheet name="Agency" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="5" r:id="rId5"/>
+    <sheet name="UserPolicies" sheetId="6" r:id="rId6"/>
+    <sheet name="Holidays" sheetId="7" r:id="rId7"/>
+    <sheet name="DayOfWeek" sheetId="8" r:id="rId8"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -2672,87 +2680,93 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="15">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Prompt"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF4A86E8"/>
       <name val="Prompt"/>
     </font>
     <font>
       <u/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF4A86E8"/>
       <name val="Prompt"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Prompt"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Prompt"/>
     </font>
     <font>
       <u/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF4A86E8"/>
       <name val="Prompt"/>
     </font>
     <font>
       <u/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF4285F4"/>
       <name val="Prompt"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF745AF2"/>
       <name val="Prompt"/>
     </font>
     <font>
       <b/>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Prompt"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color theme="7"/>
       <name val="Prompt"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FF34A853"/>
       <name val="Prompt"/>
     </font>
     <font>
-      <sz val="9.0"/>
+      <sz val="9"/>
       <color rgb="FFEA4335"/>
       <name val="Prompt"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2760,7 +2774,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -2770,161 +2784,121 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="38">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2932,7 +2906,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -3122,20 +3096,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="40.5"/>
+    <col min="2" max="2" width="40.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3143,7 +3120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -3151,7 +3128,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" s="3" t="s">
         <v>4</v>
       </c>
@@ -3159,7 +3136,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -3167,7 +3144,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -3175,7 +3152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -3183,7 +3160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -3193,25 +3170,26 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="B5"/>
+    <hyperlink ref="B5" r:id="rId1"/>
   </hyperlinks>
-  <drawing r:id="rId2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K83"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="32.5"/>
-    <col customWidth="1" min="4" max="4" width="17.38"/>
-    <col customWidth="1" min="9" max="9" width="60.63"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
+    <col min="9" max="9" width="60.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11">
       <c r="A1" s="6" t="s">
         <v>14</v>
       </c>
@@ -3246,7 +3224,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:11">
       <c r="A2" s="11" t="s">
         <v>25</v>
       </c>
@@ -3263,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:11">
       <c r="A3" s="11" t="s">
         <v>26</v>
       </c>
@@ -3286,7 +3264,7 @@
         <v>32</v>
       </c>
       <c r="H3" s="14">
-        <v>45838.0</v>
+        <v>45838</v>
       </c>
       <c r="I3" s="15" t="s">
         <v>33</v>
@@ -3296,7 +3274,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:11">
       <c r="A4" s="11" t="s">
         <v>34</v>
       </c>
@@ -3319,7 +3297,7 @@
         <v>40</v>
       </c>
       <c r="H4" s="14">
-        <v>45837.0</v>
+        <v>45837</v>
       </c>
       <c r="I4" s="15" t="s">
         <v>41</v>
@@ -3331,7 +3309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:11">
       <c r="A5" s="20" t="s">
         <v>43</v>
       </c>
@@ -3354,7 +3332,7 @@
         <v>32</v>
       </c>
       <c r="H5" s="14">
-        <v>45838.0</v>
+        <v>45838</v>
       </c>
       <c r="I5" s="15" t="s">
         <v>47</v>
@@ -3364,7 +3342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:11">
       <c r="A6" s="20" t="s">
         <v>48</v>
       </c>
@@ -3387,7 +3365,7 @@
         <v>40</v>
       </c>
       <c r="H6" s="14">
-        <v>45839.0</v>
+        <v>45839</v>
       </c>
       <c r="I6" s="15" t="s">
         <v>54</v>
@@ -3397,11 +3375,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:11">
       <c r="A7" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="37" t="s">
         <v>56</v>
       </c>
       <c r="C7" s="21" t="s">
@@ -3420,7 +3398,7 @@
         <v>59</v>
       </c>
       <c r="H7" s="14">
-        <v>45838.0</v>
+        <v>45838</v>
       </c>
       <c r="I7" s="15" t="s">
         <v>60</v>
@@ -3430,7 +3408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:11">
       <c r="A8" s="20" t="s">
         <v>61</v>
       </c>
@@ -3453,7 +3431,7 @@
         <v>65</v>
       </c>
       <c r="H8" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I8" s="15" t="s">
         <v>66</v>
@@ -3463,7 +3441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:11">
       <c r="A9" s="20" t="s">
         <v>67</v>
       </c>
@@ -3486,7 +3464,7 @@
         <v>65</v>
       </c>
       <c r="H9" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I9" s="15" t="s">
         <v>71</v>
@@ -3496,7 +3474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:11">
       <c r="A10" s="20" t="s">
         <v>72</v>
       </c>
@@ -3519,7 +3497,7 @@
         <v>65</v>
       </c>
       <c r="H10" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I10" s="15" t="s">
         <v>76</v>
@@ -3529,7 +3507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:11">
       <c r="A11" s="20" t="s">
         <v>77</v>
       </c>
@@ -3552,7 +3530,7 @@
         <v>65</v>
       </c>
       <c r="H11" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I11" s="15" t="s">
         <v>81</v>
@@ -3562,7 +3540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:11">
       <c r="A12" s="20" t="s">
         <v>82</v>
       </c>
@@ -3585,7 +3563,7 @@
         <v>65</v>
       </c>
       <c r="H12" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I12" s="15" t="s">
         <v>86</v>
@@ -3595,7 +3573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:11">
       <c r="A13" s="20" t="s">
         <v>87</v>
       </c>
@@ -3618,7 +3596,7 @@
         <v>65</v>
       </c>
       <c r="H13" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I13" s="15" t="s">
         <v>91</v>
@@ -3628,7 +3606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:11">
       <c r="A14" s="20" t="s">
         <v>92</v>
       </c>
@@ -3651,7 +3629,7 @@
         <v>65</v>
       </c>
       <c r="H14" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I14" s="15" t="s">
         <v>96</v>
@@ -3661,7 +3639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:11">
       <c r="A15" s="20" t="s">
         <v>97</v>
       </c>
@@ -3684,7 +3662,7 @@
         <v>65</v>
       </c>
       <c r="H15" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I15" s="15" t="s">
         <v>101</v>
@@ -3694,7 +3672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:11">
       <c r="A16" s="20" t="s">
         <v>102</v>
       </c>
@@ -3717,7 +3695,7 @@
         <v>65</v>
       </c>
       <c r="H16" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I16" s="15" t="s">
         <v>106</v>
@@ -3727,7 +3705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:11">
       <c r="A17" s="20" t="s">
         <v>107</v>
       </c>
@@ -3744,7 +3722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:11">
       <c r="A18" s="20" t="s">
         <v>108</v>
       </c>
@@ -3767,7 +3745,7 @@
         <v>65</v>
       </c>
       <c r="H18" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I18" s="15" t="s">
         <v>112</v>
@@ -3777,7 +3755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:11">
       <c r="A19" s="20" t="s">
         <v>113</v>
       </c>
@@ -3800,7 +3778,7 @@
         <v>65</v>
       </c>
       <c r="H19" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I19" s="15" t="s">
         <v>117</v>
@@ -3810,7 +3788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:11">
       <c r="A20" s="20" t="s">
         <v>118</v>
       </c>
@@ -3833,7 +3811,7 @@
         <v>65</v>
       </c>
       <c r="H20" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I20" s="15" t="s">
         <v>122</v>
@@ -3843,7 +3821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:11">
       <c r="A21" s="20" t="s">
         <v>123</v>
       </c>
@@ -3866,7 +3844,7 @@
         <v>65</v>
       </c>
       <c r="H21" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I21" s="15" t="s">
         <v>127</v>
@@ -3876,7 +3854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:11">
       <c r="A22" s="20" t="s">
         <v>128</v>
       </c>
@@ -3899,7 +3877,7 @@
         <v>65</v>
       </c>
       <c r="H22" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I22" s="15" t="s">
         <v>132</v>
@@ -3909,7 +3887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:11">
       <c r="A23" s="20" t="s">
         <v>133</v>
       </c>
@@ -3932,7 +3910,7 @@
         <v>65</v>
       </c>
       <c r="H23" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I23" s="15" t="s">
         <v>137</v>
@@ -3942,7 +3920,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:11">
       <c r="A24" s="20" t="s">
         <v>138</v>
       </c>
@@ -3965,7 +3943,7 @@
         <v>65</v>
       </c>
       <c r="H24" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I24" s="15" t="s">
         <v>142</v>
@@ -3975,7 +3953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:11">
       <c r="A25" s="20" t="s">
         <v>143</v>
       </c>
@@ -3992,7 +3970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:11">
       <c r="A26" s="20" t="s">
         <v>144</v>
       </c>
@@ -4015,7 +3993,7 @@
         <v>65</v>
       </c>
       <c r="H26" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I26" s="15" t="s">
         <v>148</v>
@@ -4025,7 +4003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:11">
       <c r="A27" s="20" t="s">
         <v>149</v>
       </c>
@@ -4048,7 +4026,7 @@
         <v>65</v>
       </c>
       <c r="H27" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I27" s="15" t="s">
         <v>153</v>
@@ -4058,7 +4036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:11">
       <c r="A28" s="20" t="s">
         <v>154</v>
       </c>
@@ -4081,7 +4059,7 @@
         <v>65</v>
       </c>
       <c r="H28" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I28" s="15" t="s">
         <v>158</v>
@@ -4091,7 +4069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:11">
       <c r="A29" s="20" t="s">
         <v>159</v>
       </c>
@@ -4114,7 +4092,7 @@
         <v>65</v>
       </c>
       <c r="H29" s="14">
-        <v>45841.0</v>
+        <v>45841</v>
       </c>
       <c r="I29" s="15" t="s">
         <v>163</v>
@@ -4124,7 +4102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:11">
       <c r="A30" s="20" t="s">
         <v>164</v>
       </c>
@@ -4147,7 +4125,7 @@
         <v>65</v>
       </c>
       <c r="H30" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I30" s="15" t="s">
         <v>170</v>
@@ -4157,7 +4135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:11">
       <c r="A31" s="20" t="s">
         <v>171</v>
       </c>
@@ -4180,7 +4158,7 @@
         <v>59</v>
       </c>
       <c r="H31" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I31" s="15" t="s">
         <v>176</v>
@@ -4190,7 +4168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:11">
       <c r="A32" s="20" t="s">
         <v>177</v>
       </c>
@@ -4213,7 +4191,7 @@
         <v>65</v>
       </c>
       <c r="H32" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I32" s="15" t="s">
         <v>181</v>
@@ -4223,7 +4201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:11">
       <c r="A33" s="20" t="s">
         <v>182</v>
       </c>
@@ -4246,7 +4224,7 @@
         <v>65</v>
       </c>
       <c r="H33" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I33" s="15" t="s">
         <v>186</v>
@@ -4256,7 +4234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:11">
       <c r="A34" s="20" t="s">
         <v>187</v>
       </c>
@@ -4279,7 +4257,7 @@
         <v>65</v>
       </c>
       <c r="H34" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I34" s="15" t="s">
         <v>191</v>
@@ -4289,7 +4267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:11">
       <c r="A35" s="20" t="s">
         <v>192</v>
       </c>
@@ -4312,7 +4290,7 @@
         <v>65</v>
       </c>
       <c r="H35" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I35" s="15" t="s">
         <v>197</v>
@@ -4322,7 +4300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:11">
       <c r="A36" s="20" t="s">
         <v>198</v>
       </c>
@@ -4345,7 +4323,7 @@
         <v>59</v>
       </c>
       <c r="H36" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I36" s="15" t="s">
         <v>202</v>
@@ -4355,7 +4333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:11">
       <c r="A37" s="20" t="s">
         <v>203</v>
       </c>
@@ -4378,7 +4356,7 @@
         <v>65</v>
       </c>
       <c r="H37" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I37" s="15" t="s">
         <v>207</v>
@@ -4388,7 +4366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:11">
       <c r="A38" s="20" t="s">
         <v>208</v>
       </c>
@@ -4411,7 +4389,7 @@
         <v>65</v>
       </c>
       <c r="H38" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>212</v>
@@ -4421,7 +4399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:11">
       <c r="A39" s="20" t="s">
         <v>213</v>
       </c>
@@ -4444,7 +4422,7 @@
         <v>65</v>
       </c>
       <c r="H39" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I39" s="15" t="s">
         <v>217</v>
@@ -4454,7 +4432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:11">
       <c r="A40" s="20" t="s">
         <v>218</v>
       </c>
@@ -4477,7 +4455,7 @@
         <v>65</v>
       </c>
       <c r="H40" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I40" s="15" t="s">
         <v>222</v>
@@ -4487,7 +4465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:11">
       <c r="A41" s="20" t="s">
         <v>223</v>
       </c>
@@ -4510,7 +4488,7 @@
         <v>65</v>
       </c>
       <c r="H41" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I41" s="15" t="s">
         <v>227</v>
@@ -4520,7 +4498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:11">
       <c r="A42" s="20" t="s">
         <v>228</v>
       </c>
@@ -4543,7 +4521,7 @@
         <v>65</v>
       </c>
       <c r="H42" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I42" s="15" t="s">
         <v>232</v>
@@ -4553,7 +4531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:11">
       <c r="A43" s="20" t="s">
         <v>233</v>
       </c>
@@ -4576,7 +4554,7 @@
         <v>65</v>
       </c>
       <c r="H43" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I43" s="15" t="s">
         <v>237</v>
@@ -4586,7 +4564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:11">
       <c r="A44" s="20" t="s">
         <v>238</v>
       </c>
@@ -4609,7 +4587,7 @@
         <v>65</v>
       </c>
       <c r="H44" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I44" s="15" t="s">
         <v>242</v>
@@ -4619,7 +4597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:11">
       <c r="A45" s="20" t="s">
         <v>243</v>
       </c>
@@ -4642,7 +4620,7 @@
         <v>59</v>
       </c>
       <c r="H45" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I45" s="15" t="s">
         <v>249</v>
@@ -4652,7 +4630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:11">
       <c r="A46" s="20" t="s">
         <v>250</v>
       </c>
@@ -4675,7 +4653,7 @@
         <v>59</v>
       </c>
       <c r="H46" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I46" s="15" t="s">
         <v>255</v>
@@ -4685,7 +4663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:11">
       <c r="A47" s="20" t="s">
         <v>256</v>
       </c>
@@ -4708,7 +4686,7 @@
         <v>65</v>
       </c>
       <c r="H47" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I47" s="15" t="s">
         <v>260</v>
@@ -4718,7 +4696,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:11">
       <c r="A48" s="20" t="s">
         <v>261</v>
       </c>
@@ -4741,7 +4719,7 @@
         <v>65</v>
       </c>
       <c r="H48" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I48" s="15" t="s">
         <v>265</v>
@@ -4751,7 +4729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:11">
       <c r="A49" s="20" t="s">
         <v>266</v>
       </c>
@@ -4774,7 +4752,7 @@
         <v>65</v>
       </c>
       <c r="H49" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I49" s="15" t="s">
         <v>270</v>
@@ -4784,7 +4762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:11">
       <c r="A50" s="20" t="s">
         <v>271</v>
       </c>
@@ -4807,7 +4785,7 @@
         <v>65</v>
       </c>
       <c r="H50" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I50" s="15" t="s">
         <v>275</v>
@@ -4817,7 +4795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:11">
       <c r="A51" s="20" t="s">
         <v>276</v>
       </c>
@@ -4840,7 +4818,7 @@
         <v>65</v>
       </c>
       <c r="H51" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I51" s="15" t="s">
         <v>280</v>
@@ -4850,7 +4828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:11">
       <c r="A52" s="20" t="s">
         <v>281</v>
       </c>
@@ -4873,7 +4851,7 @@
         <v>65</v>
       </c>
       <c r="H52" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I52" s="15" t="s">
         <v>285</v>
@@ -4883,7 +4861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:11">
       <c r="A53" s="20" t="s">
         <v>286</v>
       </c>
@@ -4906,7 +4884,7 @@
         <v>65</v>
       </c>
       <c r="H53" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I53" s="15" t="s">
         <v>290</v>
@@ -4916,7 +4894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:11">
       <c r="A54" s="20" t="s">
         <v>291</v>
       </c>
@@ -4939,7 +4917,7 @@
         <v>59</v>
       </c>
       <c r="H54" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I54" s="15" t="s">
         <v>297</v>
@@ -4949,7 +4927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:11">
       <c r="A55" s="20" t="s">
         <v>298</v>
       </c>
@@ -4972,7 +4950,7 @@
         <v>65</v>
       </c>
       <c r="H55" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I55" s="15" t="s">
         <v>302</v>
@@ -4982,7 +4960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:11">
       <c r="A56" s="20" t="s">
         <v>303</v>
       </c>
@@ -5005,7 +4983,7 @@
         <v>65</v>
       </c>
       <c r="H56" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I56" s="15" t="s">
         <v>307</v>
@@ -5015,7 +4993,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:11">
       <c r="A57" s="20" t="s">
         <v>308</v>
       </c>
@@ -5038,7 +5016,7 @@
         <v>65</v>
       </c>
       <c r="H57" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I57" s="15" t="s">
         <v>312</v>
@@ -5048,7 +5026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:11">
       <c r="A58" s="20" t="s">
         <v>313</v>
       </c>
@@ -5071,7 +5049,7 @@
         <v>65</v>
       </c>
       <c r="H58" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I58" s="15" t="s">
         <v>317</v>
@@ -5081,7 +5059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:11">
       <c r="A59" s="20" t="s">
         <v>318</v>
       </c>
@@ -5104,7 +5082,7 @@
         <v>65</v>
       </c>
       <c r="H59" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I59" s="15" t="s">
         <v>322</v>
@@ -5114,7 +5092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:11">
       <c r="A60" s="20" t="s">
         <v>323</v>
       </c>
@@ -5137,7 +5115,7 @@
         <v>65</v>
       </c>
       <c r="H60" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I60" s="15" t="s">
         <v>327</v>
@@ -5147,7 +5125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:11">
       <c r="A61" s="20" t="s">
         <v>328</v>
       </c>
@@ -5170,7 +5148,7 @@
         <v>65</v>
       </c>
       <c r="H61" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I61" s="15" t="s">
         <v>332</v>
@@ -5180,7 +5158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:11">
       <c r="A62" s="20" t="s">
         <v>333</v>
       </c>
@@ -5203,7 +5181,7 @@
         <v>65</v>
       </c>
       <c r="H62" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I62" s="15" t="s">
         <v>337</v>
@@ -5213,7 +5191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:11">
       <c r="A63" s="20" t="s">
         <v>338</v>
       </c>
@@ -5236,7 +5214,7 @@
         <v>65</v>
       </c>
       <c r="H63" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I63" s="15" t="s">
         <v>342</v>
@@ -5246,7 +5224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:11">
       <c r="A64" s="20" t="s">
         <v>343</v>
       </c>
@@ -5269,7 +5247,7 @@
         <v>65</v>
       </c>
       <c r="H64" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I64" s="15" t="s">
         <v>347</v>
@@ -5279,7 +5257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:11">
       <c r="A65" s="20" t="s">
         <v>348</v>
       </c>
@@ -5302,7 +5280,7 @@
         <v>65</v>
       </c>
       <c r="H65" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I65" s="15" t="s">
         <v>352</v>
@@ -5312,7 +5290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:11">
       <c r="A66" s="20" t="s">
         <v>353</v>
       </c>
@@ -5329,7 +5307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:11">
       <c r="A67" s="20" t="s">
         <v>354</v>
       </c>
@@ -5352,7 +5330,7 @@
         <v>65</v>
       </c>
       <c r="H67" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I67" s="15" t="s">
         <v>358</v>
@@ -5362,7 +5340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:11">
       <c r="A68" s="20" t="s">
         <v>359</v>
       </c>
@@ -5385,7 +5363,7 @@
         <v>65</v>
       </c>
       <c r="H68" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I68" s="15" t="s">
         <v>363</v>
@@ -5395,7 +5373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:11">
       <c r="A69" s="20" t="s">
         <v>364</v>
       </c>
@@ -5418,7 +5396,7 @@
         <v>65</v>
       </c>
       <c r="H69" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I69" s="15" t="s">
         <v>368</v>
@@ -5428,7 +5406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:11">
       <c r="A70" s="20" t="s">
         <v>369</v>
       </c>
@@ -5451,7 +5429,7 @@
         <v>65</v>
       </c>
       <c r="H70" s="14">
-        <v>45843.0</v>
+        <v>45843</v>
       </c>
       <c r="I70" s="15" t="s">
         <v>373</v>
@@ -5461,7 +5439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:11">
       <c r="A71" s="20" t="s">
         <v>374</v>
       </c>
@@ -5484,7 +5462,7 @@
         <v>40</v>
       </c>
       <c r="H71" s="14">
-        <v>45853.0</v>
+        <v>45853</v>
       </c>
       <c r="I71" s="15" t="s">
         <v>378</v>
@@ -5494,7 +5472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:11">
       <c r="A72" s="20" t="s">
         <v>379</v>
       </c>
@@ -5517,7 +5495,7 @@
         <v>65</v>
       </c>
       <c r="H72" s="14">
-        <v>45871.0</v>
+        <v>45871</v>
       </c>
       <c r="I72" s="15" t="s">
         <v>383</v>
@@ -5527,7 +5505,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:11">
       <c r="A73" s="20" t="s">
         <v>384</v>
       </c>
@@ -5550,7 +5528,7 @@
         <v>65</v>
       </c>
       <c r="H73" s="14">
-        <v>45874.0</v>
+        <v>45874</v>
       </c>
       <c r="I73" s="15" t="s">
         <v>388</v>
@@ -5560,7 +5538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:11">
       <c r="A74" s="20" t="s">
         <v>389</v>
       </c>
@@ -5583,7 +5561,7 @@
         <v>65</v>
       </c>
       <c r="H74" s="14">
-        <v>45904.0</v>
+        <v>45904</v>
       </c>
       <c r="I74" s="15" t="s">
         <v>393</v>
@@ -5593,7 +5571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:11">
       <c r="A75" s="20" t="s">
         <v>394</v>
       </c>
@@ -5616,7 +5594,7 @@
         <v>65</v>
       </c>
       <c r="H75" s="14">
-        <v>46073.0</v>
+        <v>46073</v>
       </c>
       <c r="I75" s="15" t="s">
         <v>398</v>
@@ -5626,7 +5604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:11">
       <c r="A76" s="20" t="s">
         <v>399</v>
       </c>
@@ -5649,7 +5627,7 @@
         <v>65</v>
       </c>
       <c r="H76" s="14">
-        <v>46083.0</v>
+        <v>46083</v>
       </c>
       <c r="I76" s="15" t="s">
         <v>403</v>
@@ -5659,7 +5637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:11">
       <c r="A77" s="20" t="s">
         <v>404</v>
       </c>
@@ -5676,7 +5654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:11">
       <c r="A78" s="20" t="s">
         <v>405</v>
       </c>
@@ -5699,7 +5677,7 @@
         <v>65</v>
       </c>
       <c r="H78" s="14">
-        <v>46115.0</v>
+        <v>46115</v>
       </c>
       <c r="I78" s="15" t="s">
         <v>409</v>
@@ -5709,7 +5687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:11">
       <c r="A79" s="20" t="s">
         <v>410</v>
       </c>
@@ -5732,7 +5710,7 @@
         <v>59</v>
       </c>
       <c r="H79" s="14">
-        <v>46140.0</v>
+        <v>46140</v>
       </c>
       <c r="I79" s="15" t="s">
         <v>414</v>
@@ -5742,7 +5720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:11">
       <c r="A80" s="20" t="s">
         <v>415</v>
       </c>
@@ -5765,7 +5743,7 @@
         <v>65</v>
       </c>
       <c r="H80" s="14">
-        <v>46148.0</v>
+        <v>46148</v>
       </c>
       <c r="I80" s="15" t="s">
         <v>419</v>
@@ -5775,7 +5753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:11">
       <c r="A81" s="20" t="s">
         <v>420</v>
       </c>
@@ -5798,7 +5776,7 @@
         <v>65</v>
       </c>
       <c r="H81" s="14">
-        <v>46179.0</v>
+        <v>46179</v>
       </c>
       <c r="I81" s="15" t="s">
         <v>424</v>
@@ -5808,7 +5786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:11">
       <c r="A82" s="20" t="s">
         <v>425</v>
       </c>
@@ -5831,7 +5809,7 @@
         <v>65</v>
       </c>
       <c r="H82" s="14">
-        <v>46192.0</v>
+        <v>46192</v>
       </c>
       <c r="I82" s="15" t="s">
         <v>429</v>
@@ -5841,7 +5819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:11">
       <c r="A83" s="20" t="s">
         <v>430</v>
       </c>
@@ -5864,7 +5842,7 @@
         <v>65</v>
       </c>
       <c r="H83" s="14">
-        <v>46192.0</v>
+        <v>46192</v>
       </c>
       <c r="I83" s="15" t="s">
         <v>434</v>
@@ -5876,101 +5854,103 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="I3"/>
-    <hyperlink r:id="rId2" ref="I4"/>
-    <hyperlink r:id="rId3" ref="J4"/>
-    <hyperlink r:id="rId4" ref="I5"/>
-    <hyperlink r:id="rId5" ref="I6"/>
-    <hyperlink r:id="rId6" ref="I7"/>
-    <hyperlink r:id="rId7" ref="I8"/>
-    <hyperlink r:id="rId8" ref="I9"/>
-    <hyperlink r:id="rId9" ref="I10"/>
-    <hyperlink r:id="rId10" ref="I11"/>
-    <hyperlink r:id="rId11" ref="I12"/>
-    <hyperlink r:id="rId12" ref="I13"/>
-    <hyperlink r:id="rId13" ref="I14"/>
-    <hyperlink r:id="rId14" ref="I15"/>
-    <hyperlink r:id="rId15" ref="I16"/>
-    <hyperlink r:id="rId16" ref="I18"/>
-    <hyperlink r:id="rId17" ref="I19"/>
-    <hyperlink r:id="rId18" ref="I20"/>
-    <hyperlink r:id="rId19" ref="I21"/>
-    <hyperlink r:id="rId20" ref="I22"/>
-    <hyperlink r:id="rId21" ref="I23"/>
-    <hyperlink r:id="rId22" ref="I24"/>
-    <hyperlink r:id="rId23" ref="I26"/>
-    <hyperlink r:id="rId24" ref="I27"/>
-    <hyperlink r:id="rId25" ref="I28"/>
-    <hyperlink r:id="rId26" ref="I29"/>
-    <hyperlink r:id="rId27" ref="I30"/>
-    <hyperlink r:id="rId28" ref="I31"/>
-    <hyperlink r:id="rId29" ref="I32"/>
-    <hyperlink r:id="rId30" ref="I33"/>
-    <hyperlink r:id="rId31" ref="I34"/>
-    <hyperlink r:id="rId32" ref="I35"/>
-    <hyperlink r:id="rId33" ref="I36"/>
-    <hyperlink r:id="rId34" ref="I37"/>
-    <hyperlink r:id="rId35" ref="I38"/>
-    <hyperlink r:id="rId36" ref="I39"/>
-    <hyperlink r:id="rId37" ref="I40"/>
-    <hyperlink r:id="rId38" ref="I41"/>
-    <hyperlink r:id="rId39" ref="I42"/>
-    <hyperlink r:id="rId40" ref="I43"/>
-    <hyperlink r:id="rId41" ref="I44"/>
-    <hyperlink r:id="rId42" ref="I45"/>
-    <hyperlink r:id="rId43" ref="I46"/>
-    <hyperlink r:id="rId44" ref="I47"/>
-    <hyperlink r:id="rId45" ref="I48"/>
-    <hyperlink r:id="rId46" ref="I49"/>
-    <hyperlink r:id="rId47" ref="I50"/>
-    <hyperlink r:id="rId48" ref="I51"/>
-    <hyperlink r:id="rId49" ref="I52"/>
-    <hyperlink r:id="rId50" ref="I53"/>
-    <hyperlink r:id="rId51" ref="I54"/>
-    <hyperlink r:id="rId52" ref="I55"/>
-    <hyperlink r:id="rId53" ref="I56"/>
-    <hyperlink r:id="rId54" ref="I57"/>
-    <hyperlink r:id="rId55" ref="I58"/>
-    <hyperlink r:id="rId56" ref="I59"/>
-    <hyperlink r:id="rId57" ref="I60"/>
-    <hyperlink r:id="rId58" ref="I61"/>
-    <hyperlink r:id="rId59" ref="I62"/>
-    <hyperlink r:id="rId60" ref="I63"/>
-    <hyperlink r:id="rId61" ref="I64"/>
-    <hyperlink r:id="rId62" ref="I65"/>
-    <hyperlink r:id="rId63" ref="I67"/>
-    <hyperlink r:id="rId64" ref="I68"/>
-    <hyperlink r:id="rId65" ref="I69"/>
-    <hyperlink r:id="rId66" ref="I70"/>
-    <hyperlink r:id="rId67" ref="I71"/>
-    <hyperlink r:id="rId68" ref="I72"/>
-    <hyperlink r:id="rId69" ref="I73"/>
-    <hyperlink r:id="rId70" ref="I74"/>
-    <hyperlink r:id="rId71" ref="I75"/>
-    <hyperlink r:id="rId72" ref="I76"/>
-    <hyperlink r:id="rId73" ref="I78"/>
-    <hyperlink r:id="rId74" ref="I79"/>
-    <hyperlink r:id="rId75" ref="I80"/>
-    <hyperlink r:id="rId76" ref="I81"/>
-    <hyperlink r:id="rId77" ref="I82"/>
-    <hyperlink r:id="rId78" ref="I83"/>
+    <hyperlink ref="I3" r:id="rId1"/>
+    <hyperlink ref="I4" r:id="rId2"/>
+    <hyperlink ref="J4" r:id="rId3"/>
+    <hyperlink ref="I5" r:id="rId4"/>
+    <hyperlink ref="I6" r:id="rId5"/>
+    <hyperlink ref="I7" r:id="rId6"/>
+    <hyperlink ref="I8" r:id="rId7"/>
+    <hyperlink ref="I9" r:id="rId8"/>
+    <hyperlink ref="I10" r:id="rId9"/>
+    <hyperlink ref="I11" r:id="rId10"/>
+    <hyperlink ref="I12" r:id="rId11"/>
+    <hyperlink ref="I13" r:id="rId12"/>
+    <hyperlink ref="I14" r:id="rId13"/>
+    <hyperlink ref="I15" r:id="rId14"/>
+    <hyperlink ref="I16" r:id="rId15"/>
+    <hyperlink ref="I18" r:id="rId16"/>
+    <hyperlink ref="I19" r:id="rId17"/>
+    <hyperlink ref="I20" r:id="rId18"/>
+    <hyperlink ref="I21" r:id="rId19"/>
+    <hyperlink ref="I22" r:id="rId20"/>
+    <hyperlink ref="I23" r:id="rId21"/>
+    <hyperlink ref="I24" r:id="rId22"/>
+    <hyperlink ref="I26" r:id="rId23"/>
+    <hyperlink ref="I27" r:id="rId24"/>
+    <hyperlink ref="I28" r:id="rId25"/>
+    <hyperlink ref="I29" r:id="rId26"/>
+    <hyperlink ref="I30" r:id="rId27"/>
+    <hyperlink ref="I31" r:id="rId28"/>
+    <hyperlink ref="I32" r:id="rId29"/>
+    <hyperlink ref="I33" r:id="rId30"/>
+    <hyperlink ref="I34" r:id="rId31"/>
+    <hyperlink ref="I35" r:id="rId32"/>
+    <hyperlink ref="I36" r:id="rId33"/>
+    <hyperlink ref="I37" r:id="rId34"/>
+    <hyperlink ref="I38" r:id="rId35"/>
+    <hyperlink ref="I39" r:id="rId36"/>
+    <hyperlink ref="I40" r:id="rId37"/>
+    <hyperlink ref="I41" r:id="rId38"/>
+    <hyperlink ref="I42" r:id="rId39"/>
+    <hyperlink ref="I43" r:id="rId40"/>
+    <hyperlink ref="I44" r:id="rId41"/>
+    <hyperlink ref="I45" r:id="rId42"/>
+    <hyperlink ref="I46" r:id="rId43"/>
+    <hyperlink ref="I47" r:id="rId44"/>
+    <hyperlink ref="I48" r:id="rId45"/>
+    <hyperlink ref="I49" r:id="rId46"/>
+    <hyperlink ref="I50" r:id="rId47"/>
+    <hyperlink ref="I51" r:id="rId48"/>
+    <hyperlink ref="I52" r:id="rId49"/>
+    <hyperlink ref="I53" r:id="rId50"/>
+    <hyperlink ref="I54" r:id="rId51"/>
+    <hyperlink ref="I55" r:id="rId52"/>
+    <hyperlink ref="I56" r:id="rId53"/>
+    <hyperlink ref="I57" r:id="rId54"/>
+    <hyperlink ref="I58" r:id="rId55"/>
+    <hyperlink ref="I59" r:id="rId56"/>
+    <hyperlink ref="I60" r:id="rId57"/>
+    <hyperlink ref="I61" r:id="rId58"/>
+    <hyperlink ref="I62" r:id="rId59"/>
+    <hyperlink ref="I63" r:id="rId60"/>
+    <hyperlink ref="I64" r:id="rId61"/>
+    <hyperlink ref="I65" r:id="rId62"/>
+    <hyperlink ref="I67" r:id="rId63"/>
+    <hyperlink ref="I68" r:id="rId64"/>
+    <hyperlink ref="I69" r:id="rId65"/>
+    <hyperlink ref="I70" r:id="rId66"/>
+    <hyperlink ref="I71" r:id="rId67"/>
+    <hyperlink ref="I72" r:id="rId68"/>
+    <hyperlink ref="I73" r:id="rId69"/>
+    <hyperlink ref="I74" r:id="rId70"/>
+    <hyperlink ref="I75" r:id="rId71"/>
+    <hyperlink ref="I76" r:id="rId72"/>
+    <hyperlink ref="I78" r:id="rId73"/>
+    <hyperlink ref="I79" r:id="rId74"/>
+    <hyperlink ref="I80" r:id="rId75"/>
+    <hyperlink ref="I81" r:id="rId76"/>
+    <hyperlink ref="I82" r:id="rId77"/>
+    <hyperlink ref="I83" r:id="rId78"/>
+    <hyperlink ref="B7" r:id="rId79"/>
   </hyperlinks>
-  <drawing r:id="rId79"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="13.13"/>
-    <col customWidth="1" min="4" max="4" width="17.38"/>
+    <col min="1" max="1" width="13.140625" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6">
       <c r="A1" s="22" t="s">
         <v>435</v>
       </c>
@@ -5990,7 +5970,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6">
       <c r="A2" s="23" t="s">
         <v>437</v>
       </c>
@@ -6010,7 +5990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6">
       <c r="A3" s="24" t="s">
         <v>439</v>
       </c>
@@ -6030,7 +6010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6">
       <c r="A4" s="24" t="s">
         <v>441</v>
       </c>
@@ -6050,7 +6030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6">
       <c r="A5" s="24" t="s">
         <v>443</v>
       </c>
@@ -6070,7 +6050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6">
       <c r="A6" s="24" t="s">
         <v>445</v>
       </c>
@@ -6090,7 +6070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6">
       <c r="A7" s="24" t="s">
         <v>447</v>
       </c>
@@ -6110,7 +6090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6">
       <c r="A8" s="24" t="s">
         <v>449</v>
       </c>
@@ -6130,7 +6110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6">
       <c r="A9" s="24" t="s">
         <v>451</v>
       </c>
@@ -6150,7 +6130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6">
       <c r="A10" s="24" t="s">
         <v>453</v>
       </c>
@@ -6170,7 +6150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6">
       <c r="A11" s="24" t="s">
         <v>455</v>
       </c>
@@ -6190,7 +6170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6">
       <c r="A12" s="24" t="s">
         <v>457</v>
       </c>
@@ -6210,7 +6190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6">
       <c r="A13" s="24" t="s">
         <v>459</v>
       </c>
@@ -6230,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6">
       <c r="A14" s="24" t="s">
         <v>461</v>
       </c>
@@ -6250,7 +6230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6">
       <c r="A15" s="24" t="s">
         <v>463</v>
       </c>
@@ -6271,21 +6251,22 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="22.75"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
         <v>465</v>
       </c>
@@ -6293,7 +6274,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="13" t="s">
         <v>38</v>
       </c>
@@ -6301,7 +6282,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" s="27" t="s">
         <v>52</v>
       </c>
@@ -6309,7 +6290,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2">
       <c r="A4" s="27" t="s">
         <v>175</v>
       </c>
@@ -6317,7 +6298,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5" s="27" t="s">
         <v>196</v>
       </c>
@@ -6325,7 +6306,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2">
       <c r="A6" s="27" t="s">
         <v>168</v>
       </c>
@@ -6333,7 +6314,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7" s="27" t="s">
         <v>254</v>
       </c>
@@ -6341,7 +6322,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2">
       <c r="A8" s="27" t="s">
         <v>30</v>
       </c>
@@ -6349,7 +6330,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2">
       <c r="A9" s="27" t="s">
         <v>295</v>
       </c>
@@ -6357,7 +6338,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2">
       <c r="A10" s="27" t="s">
         <v>247</v>
       </c>
@@ -6366,18 +6347,19 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
         <v>476</v>
       </c>
@@ -6385,7 +6367,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="11" t="s">
         <v>39</v>
       </c>
@@ -6393,7 +6375,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" s="11" t="s">
         <v>31</v>
       </c>
@@ -6401,7 +6383,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2">
       <c r="A4" s="11" t="s">
         <v>248</v>
       </c>
@@ -6409,7 +6391,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5" s="11" t="s">
         <v>169</v>
       </c>
@@ -6417,7 +6399,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2">
       <c r="A6" s="27" t="s">
         <v>296</v>
       </c>
@@ -6425,7 +6407,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7" s="27" t="s">
         <v>53</v>
       </c>
@@ -6434,21 +6416,23 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:D309"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.25"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4" ht="12.75">
       <c r="A1" s="7" t="s">
         <v>484</v>
       </c>
@@ -6462,7 +6446,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="28" t="s">
         <v>488</v>
       </c>
@@ -6473,10 +6457,10 @@
         <v>489</v>
       </c>
       <c r="D2" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="28" t="s">
         <v>490</v>
       </c>
@@ -6487,10 +6471,10 @@
         <v>491</v>
       </c>
       <c r="D3" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="28" t="s">
         <v>492</v>
       </c>
@@ -6501,10 +6485,10 @@
         <v>493</v>
       </c>
       <c r="D4" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="28" t="s">
         <v>494</v>
       </c>
@@ -6515,10 +6499,10 @@
         <v>495</v>
       </c>
       <c r="D5" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="28" t="s">
         <v>496</v>
       </c>
@@ -6529,10 +6513,10 @@
         <v>489</v>
       </c>
       <c r="D6" s="29">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="28" t="s">
         <v>497</v>
       </c>
@@ -6543,10 +6527,10 @@
         <v>491</v>
       </c>
       <c r="D7" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="28" t="s">
         <v>498</v>
       </c>
@@ -6557,10 +6541,10 @@
         <v>493</v>
       </c>
       <c r="D8" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="28" t="s">
         <v>499</v>
       </c>
@@ -6571,10 +6555,10 @@
         <v>495</v>
       </c>
       <c r="D9" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="28" t="s">
         <v>500</v>
       </c>
@@ -6585,10 +6569,10 @@
         <v>489</v>
       </c>
       <c r="D10" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="28" t="s">
         <v>501</v>
       </c>
@@ -6599,10 +6583,10 @@
         <v>491</v>
       </c>
       <c r="D11" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="28" t="s">
         <v>502</v>
       </c>
@@ -6613,10 +6597,10 @@
         <v>493</v>
       </c>
       <c r="D12" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="28" t="s">
         <v>503</v>
       </c>
@@ -6627,10 +6611,10 @@
         <v>495</v>
       </c>
       <c r="D13" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="28" t="s">
         <v>504</v>
       </c>
@@ -6641,10 +6625,10 @@
         <v>489</v>
       </c>
       <c r="D14" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="28" t="s">
         <v>505</v>
       </c>
@@ -6655,10 +6639,10 @@
         <v>491</v>
       </c>
       <c r="D15" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="28" t="s">
         <v>506</v>
       </c>
@@ -6669,10 +6653,10 @@
         <v>493</v>
       </c>
       <c r="D16" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="28" t="s">
         <v>507</v>
       </c>
@@ -6683,10 +6667,10 @@
         <v>495</v>
       </c>
       <c r="D17" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="28" t="s">
         <v>508</v>
       </c>
@@ -6697,10 +6681,10 @@
         <v>489</v>
       </c>
       <c r="D18" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="28" t="s">
         <v>509</v>
       </c>
@@ -6711,10 +6695,10 @@
         <v>491</v>
       </c>
       <c r="D19" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="28" t="s">
         <v>510</v>
       </c>
@@ -6725,10 +6709,10 @@
         <v>493</v>
       </c>
       <c r="D20" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="28" t="s">
         <v>511</v>
       </c>
@@ -6739,10 +6723,10 @@
         <v>495</v>
       </c>
       <c r="D21" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
       <c r="A22" s="28" t="s">
         <v>512</v>
       </c>
@@ -6753,10 +6737,10 @@
         <v>489</v>
       </c>
       <c r="D22" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1">
       <c r="A23" s="28" t="s">
         <v>513</v>
       </c>
@@ -6767,10 +6751,10 @@
         <v>491</v>
       </c>
       <c r="D23" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1">
       <c r="A24" s="28" t="s">
         <v>514</v>
       </c>
@@ -6781,10 +6765,10 @@
         <v>493</v>
       </c>
       <c r="D24" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="28" t="s">
         <v>515</v>
       </c>
@@ -6795,10 +6779,10 @@
         <v>495</v>
       </c>
       <c r="D25" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1">
       <c r="A26" s="28" t="s">
         <v>516</v>
       </c>
@@ -6809,10 +6793,10 @@
         <v>489</v>
       </c>
       <c r="D26" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1">
       <c r="A27" s="28" t="s">
         <v>517</v>
       </c>
@@ -6823,10 +6807,10 @@
         <v>491</v>
       </c>
       <c r="D27" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1">
       <c r="A28" s="28" t="s">
         <v>518</v>
       </c>
@@ -6837,10 +6821,10 @@
         <v>493</v>
       </c>
       <c r="D28" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1">
       <c r="A29" s="28" t="s">
         <v>519</v>
       </c>
@@ -6851,10 +6835,10 @@
         <v>495</v>
       </c>
       <c r="D29" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="15.75" customHeight="1">
       <c r="A30" s="28" t="s">
         <v>520</v>
       </c>
@@ -6865,10 +6849,10 @@
         <v>489</v>
       </c>
       <c r="D30" s="29">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="15.75" customHeight="1">
       <c r="A31" s="28" t="s">
         <v>521</v>
       </c>
@@ -6879,10 +6863,10 @@
         <v>491</v>
       </c>
       <c r="D31" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="15.75" customHeight="1">
       <c r="A32" s="28" t="s">
         <v>522</v>
       </c>
@@ -6893,10 +6877,10 @@
         <v>493</v>
       </c>
       <c r="D32" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" s="28" t="s">
         <v>523</v>
       </c>
@@ -6907,10 +6891,10 @@
         <v>495</v>
       </c>
       <c r="D33" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" s="28" t="s">
         <v>524</v>
       </c>
@@ -6921,10 +6905,10 @@
         <v>489</v>
       </c>
       <c r="D34" s="29">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1">
       <c r="A35" s="28" t="s">
         <v>525</v>
       </c>
@@ -6935,10 +6919,10 @@
         <v>491</v>
       </c>
       <c r="D35" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1">
       <c r="A36" s="28" t="s">
         <v>526</v>
       </c>
@@ -6949,10 +6933,10 @@
         <v>493</v>
       </c>
       <c r="D36" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1">
       <c r="A37" s="28" t="s">
         <v>527</v>
       </c>
@@ -6963,10 +6947,10 @@
         <v>495</v>
       </c>
       <c r="D37" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15">
       <c r="A38" s="28" t="s">
         <v>528</v>
       </c>
@@ -6980,7 +6964,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:4" ht="15">
       <c r="A39" s="28" t="s">
         <v>529</v>
       </c>
@@ -6991,10 +6975,10 @@
         <v>491</v>
       </c>
       <c r="D39" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15">
       <c r="A40" s="28" t="s">
         <v>530</v>
       </c>
@@ -7005,10 +6989,10 @@
         <v>493</v>
       </c>
       <c r="D40" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="15">
       <c r="A41" s="28" t="s">
         <v>531</v>
       </c>
@@ -7019,10 +7003,10 @@
         <v>495</v>
       </c>
       <c r="D41" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="42">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="15">
       <c r="A42" s="28" t="s">
         <v>532</v>
       </c>
@@ -7036,7 +7020,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:4" ht="15">
       <c r="A43" s="28" t="s">
         <v>533</v>
       </c>
@@ -7047,10 +7031,10 @@
         <v>491</v>
       </c>
       <c r="D43" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="15">
       <c r="A44" s="28" t="s">
         <v>534</v>
       </c>
@@ -7061,10 +7045,10 @@
         <v>493</v>
       </c>
       <c r="D44" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="15">
       <c r="A45" s="28" t="s">
         <v>535</v>
       </c>
@@ -7075,10 +7059,10 @@
         <v>495</v>
       </c>
       <c r="D45" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15">
       <c r="A46" s="28" t="s">
         <v>536</v>
       </c>
@@ -7089,10 +7073,10 @@
         <v>489</v>
       </c>
       <c r="D46" s="29">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="15">
       <c r="A47" s="28" t="s">
         <v>537</v>
       </c>
@@ -7103,10 +7087,10 @@
         <v>491</v>
       </c>
       <c r="D47" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="15">
       <c r="A48" s="28" t="s">
         <v>538</v>
       </c>
@@ -7117,10 +7101,10 @@
         <v>493</v>
       </c>
       <c r="D48" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15">
       <c r="A49" s="28" t="s">
         <v>539</v>
       </c>
@@ -7131,10 +7115,10 @@
         <v>495</v>
       </c>
       <c r="D49" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15">
       <c r="A50" s="28" t="s">
         <v>540</v>
       </c>
@@ -7148,7 +7132,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:4" ht="15">
       <c r="A51" s="28" t="s">
         <v>541</v>
       </c>
@@ -7159,10 +7143,10 @@
         <v>491</v>
       </c>
       <c r="D51" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="15">
       <c r="A52" s="28" t="s">
         <v>542</v>
       </c>
@@ -7173,10 +7157,10 @@
         <v>493</v>
       </c>
       <c r="D52" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="15">
       <c r="A53" s="28" t="s">
         <v>543</v>
       </c>
@@ -7187,10 +7171,10 @@
         <v>495</v>
       </c>
       <c r="D53" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="15">
       <c r="A54" s="28" t="s">
         <v>544</v>
       </c>
@@ -7201,10 +7185,10 @@
         <v>489</v>
       </c>
       <c r="D54" s="29">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="55">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="15">
       <c r="A55" s="28" t="s">
         <v>545</v>
       </c>
@@ -7215,10 +7199,10 @@
         <v>491</v>
       </c>
       <c r="D55" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="56">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="15">
       <c r="A56" s="28" t="s">
         <v>546</v>
       </c>
@@ -7229,10 +7213,10 @@
         <v>493</v>
       </c>
       <c r="D56" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="15">
       <c r="A57" s="28" t="s">
         <v>547</v>
       </c>
@@ -7243,10 +7227,10 @@
         <v>495</v>
       </c>
       <c r="D57" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="15">
       <c r="A58" s="28" t="s">
         <v>548</v>
       </c>
@@ -7257,10 +7241,10 @@
         <v>489</v>
       </c>
       <c r="D58" s="29">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="15">
       <c r="A59" s="28" t="s">
         <v>549</v>
       </c>
@@ -7271,10 +7255,10 @@
         <v>491</v>
       </c>
       <c r="D59" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="60">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="15">
       <c r="A60" s="28" t="s">
         <v>550</v>
       </c>
@@ -7285,10 +7269,10 @@
         <v>493</v>
       </c>
       <c r="D60" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="15">
       <c r="A61" s="28" t="s">
         <v>551</v>
       </c>
@@ -7299,10 +7283,10 @@
         <v>495</v>
       </c>
       <c r="D61" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="15">
       <c r="A62" s="28" t="s">
         <v>552</v>
       </c>
@@ -7316,7 +7300,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:4" ht="15">
       <c r="A63" s="28" t="s">
         <v>553</v>
       </c>
@@ -7327,10 +7311,10 @@
         <v>491</v>
       </c>
       <c r="D63" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="15">
       <c r="A64" s="28" t="s">
         <v>554</v>
       </c>
@@ -7341,10 +7325,10 @@
         <v>493</v>
       </c>
       <c r="D64" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="65">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="15">
       <c r="A65" s="28" t="s">
         <v>555</v>
       </c>
@@ -7355,10 +7339,10 @@
         <v>495</v>
       </c>
       <c r="D65" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="66">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="15">
       <c r="A66" s="28" t="s">
         <v>556</v>
       </c>
@@ -7369,10 +7353,10 @@
         <v>489</v>
       </c>
       <c r="D66" s="29">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="67">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="15">
       <c r="A67" s="28" t="s">
         <v>557</v>
       </c>
@@ -7383,10 +7367,10 @@
         <v>491</v>
       </c>
       <c r="D67" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="68">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="15">
       <c r="A68" s="28" t="s">
         <v>558</v>
       </c>
@@ -7397,10 +7381,10 @@
         <v>493</v>
       </c>
       <c r="D68" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="15">
       <c r="A69" s="28" t="s">
         <v>559</v>
       </c>
@@ -7411,10 +7395,10 @@
         <v>495</v>
       </c>
       <c r="D69" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="15">
       <c r="A70" s="28" t="s">
         <v>560</v>
       </c>
@@ -7425,10 +7409,10 @@
         <v>489</v>
       </c>
       <c r="D70" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="71">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="15">
       <c r="A71" s="28" t="s">
         <v>561</v>
       </c>
@@ -7439,10 +7423,10 @@
         <v>491</v>
       </c>
       <c r="D71" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="15">
       <c r="A72" s="28" t="s">
         <v>562</v>
       </c>
@@ -7453,10 +7437,10 @@
         <v>493</v>
       </c>
       <c r="D72" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="15">
       <c r="A73" s="28" t="s">
         <v>563</v>
       </c>
@@ -7467,10 +7451,10 @@
         <v>495</v>
       </c>
       <c r="D73" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="15">
       <c r="A74" s="28" t="s">
         <v>564</v>
       </c>
@@ -7481,10 +7465,10 @@
         <v>489</v>
       </c>
       <c r="D74" s="29">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="15">
       <c r="A75" s="28" t="s">
         <v>565</v>
       </c>
@@ -7495,10 +7479,10 @@
         <v>491</v>
       </c>
       <c r="D75" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="76">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="15">
       <c r="A76" s="28" t="s">
         <v>566</v>
       </c>
@@ -7509,10 +7493,10 @@
         <v>493</v>
       </c>
       <c r="D76" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="15">
       <c r="A77" s="28" t="s">
         <v>567</v>
       </c>
@@ -7523,10 +7507,10 @@
         <v>495</v>
       </c>
       <c r="D77" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="15">
       <c r="A78" s="28" t="s">
         <v>568</v>
       </c>
@@ -7537,10 +7521,10 @@
         <v>489</v>
       </c>
       <c r="D78" s="29">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="15">
       <c r="A79" s="28" t="s">
         <v>569</v>
       </c>
@@ -7551,10 +7535,10 @@
         <v>491</v>
       </c>
       <c r="D79" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="15">
       <c r="A80" s="28" t="s">
         <v>570</v>
       </c>
@@ -7565,10 +7549,10 @@
         <v>493</v>
       </c>
       <c r="D80" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15">
       <c r="A81" s="28" t="s">
         <v>571</v>
       </c>
@@ -7579,10 +7563,10 @@
         <v>495</v>
       </c>
       <c r="D81" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15">
       <c r="A82" s="28" t="s">
         <v>572</v>
       </c>
@@ -7593,10 +7577,10 @@
         <v>489</v>
       </c>
       <c r="D82" s="29">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15">
       <c r="A83" s="28" t="s">
         <v>573</v>
       </c>
@@ -7607,10 +7591,10 @@
         <v>491</v>
       </c>
       <c r="D83" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="84">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="15">
       <c r="A84" s="28" t="s">
         <v>574</v>
       </c>
@@ -7621,10 +7605,10 @@
         <v>493</v>
       </c>
       <c r="D84" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="15">
       <c r="A85" s="28" t="s">
         <v>575</v>
       </c>
@@ -7635,10 +7619,10 @@
         <v>495</v>
       </c>
       <c r="D85" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="15">
       <c r="A86" s="28" t="s">
         <v>576</v>
       </c>
@@ -7649,10 +7633,10 @@
         <v>489</v>
       </c>
       <c r="D86" s="29">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="87">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15">
       <c r="A87" s="28" t="s">
         <v>577</v>
       </c>
@@ -7663,10 +7647,10 @@
         <v>491</v>
       </c>
       <c r="D87" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="15">
       <c r="A88" s="28" t="s">
         <v>578</v>
       </c>
@@ -7677,10 +7661,10 @@
         <v>493</v>
       </c>
       <c r="D88" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="89">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="15">
       <c r="A89" s="28" t="s">
         <v>579</v>
       </c>
@@ -7691,10 +7675,10 @@
         <v>495</v>
       </c>
       <c r="D89" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="15">
       <c r="A90" s="28" t="s">
         <v>580</v>
       </c>
@@ -7705,10 +7689,10 @@
         <v>489</v>
       </c>
       <c r="D90" s="29">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="91">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="15">
       <c r="A91" s="28" t="s">
         <v>581</v>
       </c>
@@ -7719,10 +7703,10 @@
         <v>491</v>
       </c>
       <c r="D91" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="15">
       <c r="A92" s="28" t="s">
         <v>582</v>
       </c>
@@ -7733,10 +7717,10 @@
         <v>493</v>
       </c>
       <c r="D92" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="93">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="15">
       <c r="A93" s="28" t="s">
         <v>583</v>
       </c>
@@ -7747,10 +7731,10 @@
         <v>495</v>
       </c>
       <c r="D93" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="94">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="15">
       <c r="A94" s="28" t="s">
         <v>584</v>
       </c>
@@ -7761,10 +7745,10 @@
         <v>489</v>
       </c>
       <c r="D94" s="29">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="15">
       <c r="A95" s="28" t="s">
         <v>585</v>
       </c>
@@ -7775,10 +7759,10 @@
         <v>491</v>
       </c>
       <c r="D95" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="96">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="15">
       <c r="A96" s="28" t="s">
         <v>586</v>
       </c>
@@ -7789,10 +7773,10 @@
         <v>493</v>
       </c>
       <c r="D96" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="97">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="15">
       <c r="A97" s="28" t="s">
         <v>587</v>
       </c>
@@ -7803,10 +7787,10 @@
         <v>495</v>
       </c>
       <c r="D97" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="15">
       <c r="A98" s="28" t="s">
         <v>588</v>
       </c>
@@ -7817,10 +7801,10 @@
         <v>489</v>
       </c>
       <c r="D98" s="29">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="15">
       <c r="A99" s="28" t="s">
         <v>589</v>
       </c>
@@ -7831,10 +7815,10 @@
         <v>491</v>
       </c>
       <c r="D99" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="15">
       <c r="A100" s="28" t="s">
         <v>590</v>
       </c>
@@ -7845,10 +7829,10 @@
         <v>493</v>
       </c>
       <c r="D100" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="101">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="15">
       <c r="A101" s="28" t="s">
         <v>591</v>
       </c>
@@ -7859,10 +7843,10 @@
         <v>495</v>
       </c>
       <c r="D101" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="15">
       <c r="A102" s="28" t="s">
         <v>592</v>
       </c>
@@ -7873,10 +7857,10 @@
         <v>489</v>
       </c>
       <c r="D102" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="103">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="15">
       <c r="A103" s="28" t="s">
         <v>593</v>
       </c>
@@ -7887,10 +7871,10 @@
         <v>491</v>
       </c>
       <c r="D103" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="104">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="15">
       <c r="A104" s="28" t="s">
         <v>594</v>
       </c>
@@ -7901,10 +7885,10 @@
         <v>495</v>
       </c>
       <c r="D104" s="29">
-        <v>17.0</v>
-      </c>
-    </row>
-    <row r="105">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15">
       <c r="A105" s="28" t="s">
         <v>595</v>
       </c>
@@ -7915,10 +7899,10 @@
         <v>493</v>
       </c>
       <c r="D105" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15">
       <c r="A106" s="28" t="s">
         <v>596</v>
       </c>
@@ -7929,10 +7913,10 @@
         <v>489</v>
       </c>
       <c r="D106" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="15">
       <c r="A107" s="28" t="s">
         <v>597</v>
       </c>
@@ -7943,10 +7927,10 @@
         <v>491</v>
       </c>
       <c r="D107" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="15">
       <c r="A108" s="28" t="s">
         <v>598</v>
       </c>
@@ -7957,10 +7941,10 @@
         <v>493</v>
       </c>
       <c r="D108" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="15">
       <c r="A109" s="28" t="s">
         <v>599</v>
       </c>
@@ -7971,10 +7955,10 @@
         <v>495</v>
       </c>
       <c r="D109" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="110">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="15">
       <c r="A110" s="28" t="s">
         <v>600</v>
       </c>
@@ -7985,10 +7969,10 @@
         <v>489</v>
       </c>
       <c r="D110" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="111">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="15">
       <c r="A111" s="28" t="s">
         <v>601</v>
       </c>
@@ -7999,10 +7983,10 @@
         <v>491</v>
       </c>
       <c r="D111" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="112">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="15">
       <c r="A112" s="28" t="s">
         <v>602</v>
       </c>
@@ -8013,10 +7997,10 @@
         <v>493</v>
       </c>
       <c r="D112" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" ht="15">
       <c r="A113" s="28" t="s">
         <v>603</v>
       </c>
@@ -8027,10 +8011,10 @@
         <v>495</v>
       </c>
       <c r="D113" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="114">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="15">
       <c r="A114" s="28" t="s">
         <v>604</v>
       </c>
@@ -8041,10 +8025,10 @@
         <v>489</v>
       </c>
       <c r="D114" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="115">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="15">
       <c r="A115" s="28" t="s">
         <v>605</v>
       </c>
@@ -8055,10 +8039,10 @@
         <v>491</v>
       </c>
       <c r="D115" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="116">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="15">
       <c r="A116" s="28" t="s">
         <v>606</v>
       </c>
@@ -8069,10 +8053,10 @@
         <v>493</v>
       </c>
       <c r="D116" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="117">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="15">
       <c r="A117" s="28" t="s">
         <v>607</v>
       </c>
@@ -8083,10 +8067,10 @@
         <v>495</v>
       </c>
       <c r="D117" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="118">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15">
       <c r="A118" s="28" t="s">
         <v>608</v>
       </c>
@@ -8097,10 +8081,10 @@
         <v>489</v>
       </c>
       <c r="D118" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="119">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15">
       <c r="A119" s="28" t="s">
         <v>609</v>
       </c>
@@ -8111,10 +8095,10 @@
         <v>491</v>
       </c>
       <c r="D119" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="120">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="15">
       <c r="A120" s="28" t="s">
         <v>610</v>
       </c>
@@ -8125,10 +8109,10 @@
         <v>493</v>
       </c>
       <c r="D120" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="121">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="15">
       <c r="A121" s="28" t="s">
         <v>611</v>
       </c>
@@ -8139,10 +8123,10 @@
         <v>495</v>
       </c>
       <c r="D121" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="122">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="15">
       <c r="A122" s="28" t="s">
         <v>612</v>
       </c>
@@ -8153,10 +8137,10 @@
         <v>489</v>
       </c>
       <c r="D122" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="123">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="15">
       <c r="A123" s="28" t="s">
         <v>613</v>
       </c>
@@ -8167,10 +8151,10 @@
         <v>491</v>
       </c>
       <c r="D123" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="124">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="15">
       <c r="A124" s="28" t="s">
         <v>614</v>
       </c>
@@ -8181,10 +8165,10 @@
         <v>493</v>
       </c>
       <c r="D124" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="125">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="15">
       <c r="A125" s="28" t="s">
         <v>615</v>
       </c>
@@ -8195,10 +8179,10 @@
         <v>495</v>
       </c>
       <c r="D125" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="126">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="15">
       <c r="A126" s="28" t="s">
         <v>616</v>
       </c>
@@ -8209,10 +8193,10 @@
         <v>489</v>
       </c>
       <c r="D126" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="127">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="15">
       <c r="A127" s="28" t="s">
         <v>617</v>
       </c>
@@ -8223,10 +8207,10 @@
         <v>491</v>
       </c>
       <c r="D127" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="128">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="15">
       <c r="A128" s="28" t="s">
         <v>618</v>
       </c>
@@ -8237,10 +8221,10 @@
         <v>493</v>
       </c>
       <c r="D128" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="129">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="15">
       <c r="A129" s="28" t="s">
         <v>619</v>
       </c>
@@ -8251,10 +8235,10 @@
         <v>495</v>
       </c>
       <c r="D129" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="130">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="15">
       <c r="A130" s="28" t="s">
         <v>620</v>
       </c>
@@ -8265,10 +8249,10 @@
         <v>489</v>
       </c>
       <c r="D130" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="131">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="15">
       <c r="A131" s="28" t="s">
         <v>621</v>
       </c>
@@ -8279,10 +8263,10 @@
         <v>491</v>
       </c>
       <c r="D131" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="132">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="15">
       <c r="A132" s="28" t="s">
         <v>622</v>
       </c>
@@ -8293,10 +8277,10 @@
         <v>493</v>
       </c>
       <c r="D132" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="133">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="15">
       <c r="A133" s="28" t="s">
         <v>623</v>
       </c>
@@ -8307,10 +8291,10 @@
         <v>495</v>
       </c>
       <c r="D133" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="134">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="15">
       <c r="A134" s="28" t="s">
         <v>624</v>
       </c>
@@ -8321,10 +8305,10 @@
         <v>489</v>
       </c>
       <c r="D134" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="135">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="15">
       <c r="A135" s="28" t="s">
         <v>625</v>
       </c>
@@ -8335,10 +8319,10 @@
         <v>491</v>
       </c>
       <c r="D135" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="136">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="15">
       <c r="A136" s="28" t="s">
         <v>626</v>
       </c>
@@ -8349,10 +8333,10 @@
         <v>493</v>
       </c>
       <c r="D136" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="137">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="15">
       <c r="A137" s="28" t="s">
         <v>627</v>
       </c>
@@ -8363,10 +8347,10 @@
         <v>495</v>
       </c>
       <c r="D137" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="138">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="15">
       <c r="A138" s="28" t="s">
         <v>628</v>
       </c>
@@ -8377,10 +8361,10 @@
         <v>489</v>
       </c>
       <c r="D138" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="139">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="15">
       <c r="A139" s="28" t="s">
         <v>629</v>
       </c>
@@ -8391,10 +8375,10 @@
         <v>491</v>
       </c>
       <c r="D139" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="140">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="15">
       <c r="A140" s="28" t="s">
         <v>630</v>
       </c>
@@ -8405,10 +8389,10 @@
         <v>493</v>
       </c>
       <c r="D140" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="141">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="15">
       <c r="A141" s="28" t="s">
         <v>631</v>
       </c>
@@ -8419,10 +8403,10 @@
         <v>495</v>
       </c>
       <c r="D141" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="142">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" ht="15">
       <c r="A142" s="28" t="s">
         <v>632</v>
       </c>
@@ -8433,10 +8417,10 @@
         <v>489</v>
       </c>
       <c r="D142" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="143">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="15">
       <c r="A143" s="28" t="s">
         <v>633</v>
       </c>
@@ -8447,10 +8431,10 @@
         <v>491</v>
       </c>
       <c r="D143" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="144">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="15">
       <c r="A144" s="28" t="s">
         <v>634</v>
       </c>
@@ -8461,10 +8445,10 @@
         <v>493</v>
       </c>
       <c r="D144" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="145">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="15">
       <c r="A145" s="28" t="s">
         <v>635</v>
       </c>
@@ -8475,10 +8459,10 @@
         <v>495</v>
       </c>
       <c r="D145" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="146">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="15">
       <c r="A146" s="28" t="s">
         <v>636</v>
       </c>
@@ -8489,10 +8473,10 @@
         <v>489</v>
       </c>
       <c r="D146" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="147">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="15">
       <c r="A147" s="28" t="s">
         <v>637</v>
       </c>
@@ -8503,10 +8487,10 @@
         <v>491</v>
       </c>
       <c r="D147" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="148">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="15">
       <c r="A148" s="28" t="s">
         <v>638</v>
       </c>
@@ -8517,10 +8501,10 @@
         <v>493</v>
       </c>
       <c r="D148" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="15">
       <c r="A149" s="28" t="s">
         <v>639</v>
       </c>
@@ -8531,10 +8515,10 @@
         <v>495</v>
       </c>
       <c r="D149" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="150">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="15">
       <c r="A150" s="28" t="s">
         <v>640</v>
       </c>
@@ -8545,10 +8529,10 @@
         <v>489</v>
       </c>
       <c r="D150" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="151">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="15">
       <c r="A151" s="28" t="s">
         <v>641</v>
       </c>
@@ -8559,10 +8543,10 @@
         <v>491</v>
       </c>
       <c r="D151" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="152">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="15">
       <c r="A152" s="28" t="s">
         <v>642</v>
       </c>
@@ -8573,10 +8557,10 @@
         <v>493</v>
       </c>
       <c r="D152" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="153">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="15">
       <c r="A153" s="28" t="s">
         <v>643</v>
       </c>
@@ -8587,10 +8571,10 @@
         <v>495</v>
       </c>
       <c r="D153" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="154">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" ht="15">
       <c r="A154" s="28" t="s">
         <v>644</v>
       </c>
@@ -8601,10 +8585,10 @@
         <v>489</v>
       </c>
       <c r="D154" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="155">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" ht="15">
       <c r="A155" s="28" t="s">
         <v>645</v>
       </c>
@@ -8615,10 +8599,10 @@
         <v>491</v>
       </c>
       <c r="D155" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="156">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" ht="15">
       <c r="A156" s="28" t="s">
         <v>646</v>
       </c>
@@ -8629,10 +8613,10 @@
         <v>493</v>
       </c>
       <c r="D156" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="157">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" ht="15">
       <c r="A157" s="28" t="s">
         <v>647</v>
       </c>
@@ -8643,10 +8627,10 @@
         <v>495</v>
       </c>
       <c r="D157" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="158">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" ht="15">
       <c r="A158" s="28" t="s">
         <v>648</v>
       </c>
@@ -8657,10 +8641,10 @@
         <v>489</v>
       </c>
       <c r="D158" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="159">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" ht="15">
       <c r="A159" s="28" t="s">
         <v>649</v>
       </c>
@@ -8671,10 +8655,10 @@
         <v>491</v>
       </c>
       <c r="D159" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="160">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" ht="15">
       <c r="A160" s="28" t="s">
         <v>650</v>
       </c>
@@ -8685,10 +8669,10 @@
         <v>493</v>
       </c>
       <c r="D160" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="161">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" ht="15">
       <c r="A161" s="28" t="s">
         <v>651</v>
       </c>
@@ -8699,10 +8683,10 @@
         <v>495</v>
       </c>
       <c r="D161" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="162">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" ht="15">
       <c r="A162" s="28" t="s">
         <v>652</v>
       </c>
@@ -8713,10 +8697,10 @@
         <v>489</v>
       </c>
       <c r="D162" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="163">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" ht="15">
       <c r="A163" s="28" t="s">
         <v>653</v>
       </c>
@@ -8727,10 +8711,10 @@
         <v>491</v>
       </c>
       <c r="D163" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="164">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" ht="15">
       <c r="A164" s="28" t="s">
         <v>654</v>
       </c>
@@ -8741,10 +8725,10 @@
         <v>493</v>
       </c>
       <c r="D164" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="165">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" ht="15">
       <c r="A165" s="28" t="s">
         <v>655</v>
       </c>
@@ -8755,10 +8739,10 @@
         <v>495</v>
       </c>
       <c r="D165" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="166">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" ht="15">
       <c r="A166" s="28" t="s">
         <v>656</v>
       </c>
@@ -8769,10 +8753,10 @@
         <v>489</v>
       </c>
       <c r="D166" s="29">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="167">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" ht="15">
       <c r="A167" s="28" t="s">
         <v>657</v>
       </c>
@@ -8783,10 +8767,10 @@
         <v>491</v>
       </c>
       <c r="D167" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="168">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" ht="15">
       <c r="A168" s="28" t="s">
         <v>658</v>
       </c>
@@ -8797,10 +8781,10 @@
         <v>493</v>
       </c>
       <c r="D168" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="169">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" ht="15">
       <c r="A169" s="28" t="s">
         <v>659</v>
       </c>
@@ -8811,10 +8795,10 @@
         <v>495</v>
       </c>
       <c r="D169" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="170">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" ht="15">
       <c r="A170" s="28" t="s">
         <v>660</v>
       </c>
@@ -8825,10 +8809,10 @@
         <v>489</v>
       </c>
       <c r="D170" s="29">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="171">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" ht="15">
       <c r="A171" s="28" t="s">
         <v>661</v>
       </c>
@@ -8839,10 +8823,10 @@
         <v>491</v>
       </c>
       <c r="D171" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="172">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" ht="15">
       <c r="A172" s="28" t="s">
         <v>662</v>
       </c>
@@ -8853,10 +8837,10 @@
         <v>493</v>
       </c>
       <c r="D172" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="173">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" ht="15">
       <c r="A173" s="28" t="s">
         <v>663</v>
       </c>
@@ -8867,10 +8851,10 @@
         <v>495</v>
       </c>
       <c r="D173" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="174">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" ht="15">
       <c r="A174" s="28" t="s">
         <v>664</v>
       </c>
@@ -8881,10 +8865,10 @@
         <v>489</v>
       </c>
       <c r="D174" s="29">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="175">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" ht="15">
       <c r="A175" s="28" t="s">
         <v>665</v>
       </c>
@@ -8895,10 +8879,10 @@
         <v>491</v>
       </c>
       <c r="D175" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="176">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" ht="15">
       <c r="A176" s="28" t="s">
         <v>666</v>
       </c>
@@ -8909,10 +8893,10 @@
         <v>493</v>
       </c>
       <c r="D176" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="177">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" ht="15">
       <c r="A177" s="28" t="s">
         <v>667</v>
       </c>
@@ -8923,10 +8907,10 @@
         <v>495</v>
       </c>
       <c r="D177" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="178">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" ht="15">
       <c r="A178" s="28" t="s">
         <v>668</v>
       </c>
@@ -8937,10 +8921,10 @@
         <v>489</v>
       </c>
       <c r="D178" s="29">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="179">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" ht="15">
       <c r="A179" s="28" t="s">
         <v>669</v>
       </c>
@@ -8951,10 +8935,10 @@
         <v>491</v>
       </c>
       <c r="D179" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="180">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" ht="15">
       <c r="A180" s="28" t="s">
         <v>670</v>
       </c>
@@ -8965,10 +8949,10 @@
         <v>493</v>
       </c>
       <c r="D180" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="181">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" ht="15">
       <c r="A181" s="28" t="s">
         <v>671</v>
       </c>
@@ -8979,10 +8963,10 @@
         <v>495</v>
       </c>
       <c r="D181" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="182">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" ht="15">
       <c r="A182" s="28" t="s">
         <v>672</v>
       </c>
@@ -8996,7 +8980,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:4" ht="15">
       <c r="A183" s="28" t="s">
         <v>673</v>
       </c>
@@ -9007,10 +8991,10 @@
         <v>491</v>
       </c>
       <c r="D183" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="184">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" ht="15">
       <c r="A184" s="28" t="s">
         <v>674</v>
       </c>
@@ -9021,10 +9005,10 @@
         <v>493</v>
       </c>
       <c r="D184" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="185">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" ht="15">
       <c r="A185" s="28" t="s">
         <v>675</v>
       </c>
@@ -9035,10 +9019,10 @@
         <v>495</v>
       </c>
       <c r="D185" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="186">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" ht="15">
       <c r="A186" s="28" t="s">
         <v>676</v>
       </c>
@@ -9049,10 +9033,10 @@
         <v>489</v>
       </c>
       <c r="D186" s="29">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="187">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" ht="15">
       <c r="A187" s="28" t="s">
         <v>677</v>
       </c>
@@ -9063,10 +9047,10 @@
         <v>491</v>
       </c>
       <c r="D187" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="188">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" ht="15">
       <c r="A188" s="28" t="s">
         <v>678</v>
       </c>
@@ -9077,10 +9061,10 @@
         <v>493</v>
       </c>
       <c r="D188" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="189">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" ht="15">
       <c r="A189" s="28" t="s">
         <v>679</v>
       </c>
@@ -9091,10 +9075,10 @@
         <v>495</v>
       </c>
       <c r="D189" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="190">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" ht="15">
       <c r="A190" s="28" t="s">
         <v>680</v>
       </c>
@@ -9105,10 +9089,10 @@
         <v>489</v>
       </c>
       <c r="D190" s="29">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="191">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" ht="15">
       <c r="A191" s="28" t="s">
         <v>681</v>
       </c>
@@ -9119,10 +9103,10 @@
         <v>491</v>
       </c>
       <c r="D191" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="192">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" ht="15">
       <c r="A192" s="28" t="s">
         <v>682</v>
       </c>
@@ -9133,10 +9117,10 @@
         <v>493</v>
       </c>
       <c r="D192" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="193">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" ht="15">
       <c r="A193" s="28" t="s">
         <v>683</v>
       </c>
@@ -9147,10 +9131,10 @@
         <v>495</v>
       </c>
       <c r="D193" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="194">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" ht="15">
       <c r="A194" s="28" t="s">
         <v>684</v>
       </c>
@@ -9161,10 +9145,10 @@
         <v>489</v>
       </c>
       <c r="D194" s="29">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="195">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="15">
       <c r="A195" s="28" t="s">
         <v>685</v>
       </c>
@@ -9175,10 +9159,10 @@
         <v>491</v>
       </c>
       <c r="D195" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="196">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" ht="15">
       <c r="A196" s="28" t="s">
         <v>686</v>
       </c>
@@ -9189,10 +9173,10 @@
         <v>493</v>
       </c>
       <c r="D196" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="197">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" ht="15">
       <c r="A197" s="28" t="s">
         <v>687</v>
       </c>
@@ -9203,10 +9187,10 @@
         <v>495</v>
       </c>
       <c r="D197" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="198">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" ht="15">
       <c r="A198" s="28" t="s">
         <v>688</v>
       </c>
@@ -9217,10 +9201,10 @@
         <v>489</v>
       </c>
       <c r="D198" s="29">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="199">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" ht="15">
       <c r="A199" s="28" t="s">
         <v>689</v>
       </c>
@@ -9231,10 +9215,10 @@
         <v>491</v>
       </c>
       <c r="D199" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="200">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" ht="15">
       <c r="A200" s="28" t="s">
         <v>690</v>
       </c>
@@ -9245,10 +9229,10 @@
         <v>493</v>
       </c>
       <c r="D200" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="201">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" ht="15">
       <c r="A201" s="28" t="s">
         <v>691</v>
       </c>
@@ -9259,10 +9243,10 @@
         <v>495</v>
       </c>
       <c r="D201" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="202">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="15">
       <c r="A202" s="28" t="s">
         <v>692</v>
       </c>
@@ -9273,10 +9257,10 @@
         <v>489</v>
       </c>
       <c r="D202" s="29">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="203">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" ht="15">
       <c r="A203" s="28" t="s">
         <v>693</v>
       </c>
@@ -9287,10 +9271,10 @@
         <v>491</v>
       </c>
       <c r="D203" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="204">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" ht="15">
       <c r="A204" s="28" t="s">
         <v>694</v>
       </c>
@@ -9301,10 +9285,10 @@
         <v>493</v>
       </c>
       <c r="D204" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="205">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" ht="15">
       <c r="A205" s="28" t="s">
         <v>695</v>
       </c>
@@ -9315,10 +9299,10 @@
         <v>495</v>
       </c>
       <c r="D205" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="206">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" ht="15">
       <c r="A206" s="28" t="s">
         <v>696</v>
       </c>
@@ -9329,10 +9313,10 @@
         <v>489</v>
       </c>
       <c r="D206" s="29">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="207">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" ht="15">
       <c r="A207" s="28" t="s">
         <v>697</v>
       </c>
@@ -9343,10 +9327,10 @@
         <v>491</v>
       </c>
       <c r="D207" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="208">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" ht="15">
       <c r="A208" s="28" t="s">
         <v>698</v>
       </c>
@@ -9357,10 +9341,10 @@
         <v>493</v>
       </c>
       <c r="D208" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="15">
       <c r="A209" s="28" t="s">
         <v>699</v>
       </c>
@@ -9371,10 +9355,10 @@
         <v>495</v>
       </c>
       <c r="D209" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="210">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" ht="15">
       <c r="A210" s="28" t="s">
         <v>700</v>
       </c>
@@ -9385,10 +9369,10 @@
         <v>489</v>
       </c>
       <c r="D210" s="29">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="211">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" ht="15">
       <c r="A211" s="28" t="s">
         <v>701</v>
       </c>
@@ -9399,10 +9383,10 @@
         <v>491</v>
       </c>
       <c r="D211" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="212">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" ht="15">
       <c r="A212" s="28" t="s">
         <v>702</v>
       </c>
@@ -9413,10 +9397,10 @@
         <v>493</v>
       </c>
       <c r="D212" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="213">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" ht="15">
       <c r="A213" s="28" t="s">
         <v>703</v>
       </c>
@@ -9427,10 +9411,10 @@
         <v>495</v>
       </c>
       <c r="D213" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="214">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" ht="15">
       <c r="A214" s="28" t="s">
         <v>704</v>
       </c>
@@ -9444,7 +9428,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:4" ht="15">
       <c r="A215" s="28" t="s">
         <v>705</v>
       </c>
@@ -9455,10 +9439,10 @@
         <v>491</v>
       </c>
       <c r="D215" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="216">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" ht="15">
       <c r="A216" s="28" t="s">
         <v>706</v>
       </c>
@@ -9469,10 +9453,10 @@
         <v>493</v>
       </c>
       <c r="D216" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="217">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" ht="15">
       <c r="A217" s="28" t="s">
         <v>707</v>
       </c>
@@ -9483,10 +9467,10 @@
         <v>495</v>
       </c>
       <c r="D217" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="218">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" ht="15">
       <c r="A218" s="28" t="s">
         <v>708</v>
       </c>
@@ -9497,10 +9481,10 @@
         <v>489</v>
       </c>
       <c r="D218" s="29">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="219">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" ht="15">
       <c r="A219" s="28" t="s">
         <v>709</v>
       </c>
@@ -9511,10 +9495,10 @@
         <v>491</v>
       </c>
       <c r="D219" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="220">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" ht="15">
       <c r="A220" s="28" t="s">
         <v>710</v>
       </c>
@@ -9525,10 +9509,10 @@
         <v>493</v>
       </c>
       <c r="D220" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="221">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" ht="15">
       <c r="A221" s="28" t="s">
         <v>711</v>
       </c>
@@ -9539,10 +9523,10 @@
         <v>495</v>
       </c>
       <c r="D221" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="222">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" ht="15">
       <c r="A222" s="28" t="s">
         <v>712</v>
       </c>
@@ -9553,10 +9537,10 @@
         <v>489</v>
       </c>
       <c r="D222" s="29">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="223">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" ht="15">
       <c r="A223" s="28" t="s">
         <v>713</v>
       </c>
@@ -9567,10 +9551,10 @@
         <v>491</v>
       </c>
       <c r="D223" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="224">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" ht="15">
       <c r="A224" s="28" t="s">
         <v>714</v>
       </c>
@@ -9581,10 +9565,10 @@
         <v>493</v>
       </c>
       <c r="D224" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="225">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" ht="15">
       <c r="A225" s="28" t="s">
         <v>715</v>
       </c>
@@ -9595,10 +9579,10 @@
         <v>495</v>
       </c>
       <c r="D225" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="226">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" ht="15">
       <c r="A226" s="28" t="s">
         <v>716</v>
       </c>
@@ -9609,10 +9593,10 @@
         <v>489</v>
       </c>
       <c r="D226" s="29">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="227">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" ht="15">
       <c r="A227" s="28" t="s">
         <v>717</v>
       </c>
@@ -9623,10 +9607,10 @@
         <v>491</v>
       </c>
       <c r="D227" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="228">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" ht="15">
       <c r="A228" s="28" t="s">
         <v>718</v>
       </c>
@@ -9637,10 +9621,10 @@
         <v>493</v>
       </c>
       <c r="D228" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="229">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" ht="15">
       <c r="A229" s="28" t="s">
         <v>719</v>
       </c>
@@ -9651,10 +9635,10 @@
         <v>495</v>
       </c>
       <c r="D229" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="230">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" ht="15">
       <c r="A230" s="28" t="s">
         <v>720</v>
       </c>
@@ -9665,10 +9649,10 @@
         <v>489</v>
       </c>
       <c r="D230" s="29">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="231">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" ht="15">
       <c r="A231" s="28" t="s">
         <v>721</v>
       </c>
@@ -9679,10 +9663,10 @@
         <v>491</v>
       </c>
       <c r="D231" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="232">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" ht="15">
       <c r="A232" s="28" t="s">
         <v>722</v>
       </c>
@@ -9693,10 +9677,10 @@
         <v>493</v>
       </c>
       <c r="D232" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="233">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="15">
       <c r="A233" s="28" t="s">
         <v>723</v>
       </c>
@@ -9707,10 +9691,10 @@
         <v>495</v>
       </c>
       <c r="D233" s="29">
-        <v>20.0</v>
-      </c>
-    </row>
-    <row r="234">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" ht="15">
       <c r="A234" s="28" t="s">
         <v>724</v>
       </c>
@@ -9721,10 +9705,10 @@
         <v>489</v>
       </c>
       <c r="D234" s="29">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="235">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" ht="15">
       <c r="A235" s="28" t="s">
         <v>725</v>
       </c>
@@ -9735,10 +9719,10 @@
         <v>491</v>
       </c>
       <c r="D235" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="236">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" ht="15">
       <c r="A236" s="28" t="s">
         <v>726</v>
       </c>
@@ -9749,10 +9733,10 @@
         <v>493</v>
       </c>
       <c r="D236" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="237">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" ht="15">
       <c r="A237" s="28" t="s">
         <v>727</v>
       </c>
@@ -9763,10 +9747,10 @@
         <v>495</v>
       </c>
       <c r="D237" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="238">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" ht="15">
       <c r="A238" s="28" t="s">
         <v>728</v>
       </c>
@@ -9777,10 +9761,10 @@
         <v>489</v>
       </c>
       <c r="D238" s="29">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="239">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="15">
       <c r="A239" s="28" t="s">
         <v>729</v>
       </c>
@@ -9791,10 +9775,10 @@
         <v>491</v>
       </c>
       <c r="D239" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="240">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="15">
       <c r="A240" s="28" t="s">
         <v>730</v>
       </c>
@@ -9805,10 +9789,10 @@
         <v>493</v>
       </c>
       <c r="D240" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="241">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" ht="15">
       <c r="A241" s="28" t="s">
         <v>731</v>
       </c>
@@ -9819,10 +9803,10 @@
         <v>495</v>
       </c>
       <c r="D241" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="242">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="15">
       <c r="A242" s="28" t="s">
         <v>732</v>
       </c>
@@ -9833,10 +9817,10 @@
         <v>489</v>
       </c>
       <c r="D242" s="29">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="243">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" ht="15">
       <c r="A243" s="28" t="s">
         <v>733</v>
       </c>
@@ -9847,10 +9831,10 @@
         <v>491</v>
       </c>
       <c r="D243" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="244">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="15">
       <c r="A244" s="28" t="s">
         <v>734</v>
       </c>
@@ -9861,10 +9845,10 @@
         <v>493</v>
       </c>
       <c r="D244" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="245">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="15">
       <c r="A245" s="28" t="s">
         <v>735</v>
       </c>
@@ -9875,10 +9859,10 @@
         <v>495</v>
       </c>
       <c r="D245" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="246">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="15">
       <c r="A246" s="28" t="s">
         <v>736</v>
       </c>
@@ -9889,10 +9873,10 @@
         <v>489</v>
       </c>
       <c r="D246" s="29">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="247">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="15">
       <c r="A247" s="28" t="s">
         <v>737</v>
       </c>
@@ -9903,10 +9887,10 @@
         <v>491</v>
       </c>
       <c r="D247" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="248">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="15">
       <c r="A248" s="28" t="s">
         <v>738</v>
       </c>
@@ -9917,10 +9901,10 @@
         <v>493</v>
       </c>
       <c r="D248" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="249">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="15">
       <c r="A249" s="28" t="s">
         <v>739</v>
       </c>
@@ -9931,10 +9915,10 @@
         <v>495</v>
       </c>
       <c r="D249" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="250">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="15">
       <c r="A250" s="28" t="s">
         <v>740</v>
       </c>
@@ -9945,10 +9929,10 @@
         <v>489</v>
       </c>
       <c r="D250" s="29">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="251">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="15">
       <c r="A251" s="28" t="s">
         <v>741</v>
       </c>
@@ -9959,10 +9943,10 @@
         <v>491</v>
       </c>
       <c r="D251" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="252">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" ht="15">
       <c r="A252" s="28" t="s">
         <v>742</v>
       </c>
@@ -9973,10 +9957,10 @@
         <v>493</v>
       </c>
       <c r="D252" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="253">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="15">
       <c r="A253" s="28" t="s">
         <v>743</v>
       </c>
@@ -9987,10 +9971,10 @@
         <v>495</v>
       </c>
       <c r="D253" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="254">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="15">
       <c r="A254" s="28" t="s">
         <v>744</v>
       </c>
@@ -10001,10 +9985,10 @@
         <v>489</v>
       </c>
       <c r="D254" s="29">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="255">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="15">
       <c r="A255" s="28" t="s">
         <v>745</v>
       </c>
@@ -10015,10 +9999,10 @@
         <v>491</v>
       </c>
       <c r="D255" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="256">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="15">
       <c r="A256" s="28" t="s">
         <v>746</v>
       </c>
@@ -10029,10 +10013,10 @@
         <v>493</v>
       </c>
       <c r="D256" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="257">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="15">
       <c r="A257" s="28" t="s">
         <v>747</v>
       </c>
@@ -10043,10 +10027,10 @@
         <v>495</v>
       </c>
       <c r="D257" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="258">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="15">
       <c r="A258" s="28" t="s">
         <v>748</v>
       </c>
@@ -10057,10 +10041,10 @@
         <v>489</v>
       </c>
       <c r="D258" s="29">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="259">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="15">
       <c r="A259" s="28" t="s">
         <v>749</v>
       </c>
@@ -10071,10 +10055,10 @@
         <v>491</v>
       </c>
       <c r="D259" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="260">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="15">
       <c r="A260" s="28" t="s">
         <v>750</v>
       </c>
@@ -10085,10 +10069,10 @@
         <v>493</v>
       </c>
       <c r="D260" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="261">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="15">
       <c r="A261" s="28" t="s">
         <v>751</v>
       </c>
@@ -10099,10 +10083,10 @@
         <v>495</v>
       </c>
       <c r="D261" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="262">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="15">
       <c r="A262" s="30" t="s">
         <v>752</v>
       </c>
@@ -10116,7 +10100,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:4" ht="15">
       <c r="A263" s="28" t="s">
         <v>753</v>
       </c>
@@ -10127,10 +10111,10 @@
         <v>491</v>
       </c>
       <c r="D263" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="264">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="15">
       <c r="A264" s="28" t="s">
         <v>754</v>
       </c>
@@ -10141,10 +10125,10 @@
         <v>493</v>
       </c>
       <c r="D264" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="265">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="15">
       <c r="A265" s="28" t="s">
         <v>755</v>
       </c>
@@ -10155,10 +10139,10 @@
         <v>495</v>
       </c>
       <c r="D265" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="266">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="15">
       <c r="A266" s="30" t="s">
         <v>756</v>
       </c>
@@ -10172,7 +10156,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:4" ht="15">
       <c r="A267" s="28" t="s">
         <v>757</v>
       </c>
@@ -10183,10 +10167,10 @@
         <v>491</v>
       </c>
       <c r="D267" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="268">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" ht="15">
       <c r="A268" s="28" t="s">
         <v>758</v>
       </c>
@@ -10197,10 +10181,10 @@
         <v>493</v>
       </c>
       <c r="D268" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="269">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="15">
       <c r="A269" s="28" t="s">
         <v>759</v>
       </c>
@@ -10211,10 +10195,10 @@
         <v>495</v>
       </c>
       <c r="D269" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="270">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="15">
       <c r="A270" s="30" t="s">
         <v>760</v>
       </c>
@@ -10225,10 +10209,10 @@
         <v>489</v>
       </c>
       <c r="D270" s="29">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="271">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="15">
       <c r="A271" s="28" t="s">
         <v>761</v>
       </c>
@@ -10239,10 +10223,10 @@
         <v>491</v>
       </c>
       <c r="D271" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="272">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="15">
       <c r="A272" s="28" t="s">
         <v>762</v>
       </c>
@@ -10253,10 +10237,10 @@
         <v>493</v>
       </c>
       <c r="D272" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="273">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" ht="15">
       <c r="A273" s="28" t="s">
         <v>763</v>
       </c>
@@ -10267,10 +10251,10 @@
         <v>495</v>
       </c>
       <c r="D273" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="274">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="15">
       <c r="A274" s="30" t="s">
         <v>764</v>
       </c>
@@ -10284,7 +10268,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:4" ht="15">
       <c r="A275" s="28" t="s">
         <v>765</v>
       </c>
@@ -10295,10 +10279,10 @@
         <v>491</v>
       </c>
       <c r="D275" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="276">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="15">
       <c r="A276" s="28" t="s">
         <v>766</v>
       </c>
@@ -10309,10 +10293,10 @@
         <v>493</v>
       </c>
       <c r="D276" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="277">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="15">
       <c r="A277" s="28" t="s">
         <v>767</v>
       </c>
@@ -10323,10 +10307,10 @@
         <v>495</v>
       </c>
       <c r="D277" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="278">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="15">
       <c r="A278" s="30" t="s">
         <v>768</v>
       </c>
@@ -10337,10 +10321,10 @@
         <v>489</v>
       </c>
       <c r="D278" s="29">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="15">
       <c r="A279" s="30" t="s">
         <v>769</v>
       </c>
@@ -10351,10 +10335,10 @@
         <v>491</v>
       </c>
       <c r="D279" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="280">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="15">
       <c r="A280" s="30" t="s">
         <v>770</v>
       </c>
@@ -10365,10 +10349,10 @@
         <v>493</v>
       </c>
       <c r="D280" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="281">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="15">
       <c r="A281" s="30" t="s">
         <v>771</v>
       </c>
@@ -10379,10 +10363,10 @@
         <v>495</v>
       </c>
       <c r="D281" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="282">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="15">
       <c r="A282" s="30" t="s">
         <v>772</v>
       </c>
@@ -10393,10 +10377,10 @@
         <v>489</v>
       </c>
       <c r="D282" s="29">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="15">
       <c r="A283" s="30" t="s">
         <v>773</v>
       </c>
@@ -10407,10 +10391,10 @@
         <v>491</v>
       </c>
       <c r="D283" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="284">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="15">
       <c r="A284" s="30" t="s">
         <v>774</v>
       </c>
@@ -10421,10 +10405,10 @@
         <v>493</v>
       </c>
       <c r="D284" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="285">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="15">
       <c r="A285" s="30" t="s">
         <v>775</v>
       </c>
@@ -10435,10 +10419,10 @@
         <v>495</v>
       </c>
       <c r="D285" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="286">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="15">
       <c r="A286" s="30" t="s">
         <v>776</v>
       </c>
@@ -10449,10 +10433,10 @@
         <v>493</v>
       </c>
       <c r="D286" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="287">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="15">
       <c r="A287" s="30" t="s">
         <v>777</v>
       </c>
@@ -10463,10 +10447,10 @@
         <v>495</v>
       </c>
       <c r="D287" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="288">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="15">
       <c r="A288" s="30" t="s">
         <v>778</v>
       </c>
@@ -10477,10 +10461,10 @@
         <v>491</v>
       </c>
       <c r="D288" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="289">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="15">
       <c r="A289" s="30" t="s">
         <v>779</v>
       </c>
@@ -10491,10 +10475,10 @@
         <v>489</v>
       </c>
       <c r="D289" s="29">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="15">
       <c r="A290" s="30" t="s">
         <v>780</v>
       </c>
@@ -10505,10 +10489,10 @@
         <v>489</v>
       </c>
       <c r="D290" s="29">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="15">
       <c r="A291" s="30" t="s">
         <v>781</v>
       </c>
@@ -10519,10 +10503,10 @@
         <v>491</v>
       </c>
       <c r="D291" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="292">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="15">
       <c r="A292" s="30" t="s">
         <v>782</v>
       </c>
@@ -10533,10 +10517,10 @@
         <v>493</v>
       </c>
       <c r="D292" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="293">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="15">
       <c r="A293" s="30" t="s">
         <v>783</v>
       </c>
@@ -10547,10 +10531,10 @@
         <v>495</v>
       </c>
       <c r="D293" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="294">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="15">
       <c r="A294" s="30" t="s">
         <v>784</v>
       </c>
@@ -10561,10 +10545,10 @@
         <v>495</v>
       </c>
       <c r="D294" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="295">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="15">
       <c r="A295" s="30" t="s">
         <v>785</v>
       </c>
@@ -10575,10 +10559,10 @@
         <v>489</v>
       </c>
       <c r="D295" s="29">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="15">
       <c r="A296" s="30" t="s">
         <v>786</v>
       </c>
@@ -10589,10 +10573,10 @@
         <v>491</v>
       </c>
       <c r="D296" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="297">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="15">
       <c r="A297" s="30" t="s">
         <v>787</v>
       </c>
@@ -10603,10 +10587,10 @@
         <v>493</v>
       </c>
       <c r="D297" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="298">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="15">
       <c r="A298" s="30" t="s">
         <v>788</v>
       </c>
@@ -10617,10 +10601,10 @@
         <v>489</v>
       </c>
       <c r="D298" s="29">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="15">
       <c r="A299" s="30" t="s">
         <v>789</v>
       </c>
@@ -10631,10 +10615,10 @@
         <v>491</v>
       </c>
       <c r="D299" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="300">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="15">
       <c r="A300" s="30" t="s">
         <v>790</v>
       </c>
@@ -10645,10 +10629,10 @@
         <v>493</v>
       </c>
       <c r="D300" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="301">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" ht="15">
       <c r="A301" s="30" t="s">
         <v>791</v>
       </c>
@@ -10659,10 +10643,10 @@
         <v>495</v>
       </c>
       <c r="D301" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="302">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" ht="15">
       <c r="A302" s="30" t="s">
         <v>792</v>
       </c>
@@ -10673,10 +10657,10 @@
         <v>489</v>
       </c>
       <c r="D302" s="29">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="15">
       <c r="A303" s="30" t="s">
         <v>793</v>
       </c>
@@ -10687,10 +10671,10 @@
         <v>491</v>
       </c>
       <c r="D303" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="304">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="15">
       <c r="A304" s="30" t="s">
         <v>794</v>
       </c>
@@ -10701,10 +10685,10 @@
         <v>493</v>
       </c>
       <c r="D304" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="305">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" ht="15">
       <c r="A305" s="30" t="s">
         <v>795</v>
       </c>
@@ -10715,10 +10699,10 @@
         <v>495</v>
       </c>
       <c r="D305" s="29">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="306">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" ht="15">
       <c r="A306" s="30" t="s">
         <v>796</v>
       </c>
@@ -10729,10 +10713,10 @@
         <v>489</v>
       </c>
       <c r="D306" s="29">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" ht="15">
       <c r="A307" s="30" t="s">
         <v>797</v>
       </c>
@@ -10743,10 +10727,10 @@
         <v>491</v>
       </c>
       <c r="D307" s="29">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="308">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" ht="15">
       <c r="A308" s="30" t="s">
         <v>798</v>
       </c>
@@ -10757,10 +10741,10 @@
         <v>493</v>
       </c>
       <c r="D308" s="29">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="309">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" ht="15">
       <c r="A309" s="30" t="s">
         <v>799</v>
       </c>
@@ -10771,27 +10755,28 @@
         <v>495</v>
       </c>
       <c r="D309" s="29">
-        <v>15.0</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:C42"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.5"/>
-    <col customWidth="1" min="2" max="2" width="13.63"/>
-    <col customWidth="1" min="3" max="3" width="31.88"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
         <v>800</v>
       </c>
@@ -10802,216 +10787,216 @@
         <v>802</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
         <v>803</v>
       </c>
       <c r="B2" s="31">
-        <v>46023.0</v>
+        <v>46023</v>
       </c>
       <c r="C2" s="32" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3">
       <c r="A3" s="13" t="s">
         <v>805</v>
       </c>
       <c r="B3" s="31">
-        <v>46024.0</v>
+        <v>46024</v>
       </c>
       <c r="C3" s="32" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3">
       <c r="A4" s="13" t="s">
         <v>807</v>
       </c>
       <c r="B4" s="31">
-        <v>46025.0</v>
+        <v>46025</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
         <v>808</v>
       </c>
       <c r="B5" s="31">
-        <v>46060.0</v>
+        <v>46060</v>
       </c>
       <c r="C5" s="32" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3">
       <c r="A6" s="13" t="s">
         <v>809</v>
       </c>
       <c r="B6" s="31">
-        <v>46084.0</v>
+        <v>46084</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3">
       <c r="A7" s="13" t="s">
         <v>811</v>
       </c>
       <c r="B7" s="31">
-        <v>46102.0</v>
+        <v>46102</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3">
       <c r="A8" s="13" t="s">
         <v>812</v>
       </c>
       <c r="B8" s="31">
-        <v>46118.0</v>
+        <v>46118</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3">
       <c r="A9" s="13" t="s">
         <v>814</v>
       </c>
       <c r="B9" s="31">
-        <v>46123.0</v>
+        <v>46123</v>
       </c>
       <c r="C9" s="32" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3">
       <c r="A10" s="13" t="s">
         <v>815</v>
       </c>
       <c r="B10" s="31">
-        <v>46125.0</v>
+        <v>46125</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3">
       <c r="A11" s="13" t="s">
         <v>817</v>
       </c>
       <c r="B11" s="31">
-        <v>46126.0</v>
+        <v>46126</v>
       </c>
       <c r="C11" s="32" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3">
       <c r="A12" s="13" t="s">
         <v>818</v>
       </c>
       <c r="B12" s="31">
-        <v>46127.0</v>
+        <v>46127</v>
       </c>
       <c r="C12" s="32" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3">
       <c r="A13" s="13" t="s">
         <v>819</v>
       </c>
       <c r="B13" s="31">
-        <v>46128.0</v>
+        <v>46128</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:3">
       <c r="A14" s="13" t="s">
         <v>820</v>
       </c>
       <c r="B14" s="31">
-        <v>46143.0</v>
+        <v>46143</v>
       </c>
       <c r="C14" s="32" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:3">
       <c r="A15" s="13" t="s">
         <v>822</v>
       </c>
       <c r="B15" s="31">
-        <v>46144.0</v>
+        <v>46144</v>
       </c>
       <c r="C15" s="32" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:3">
       <c r="A16" s="13" t="s">
         <v>823</v>
       </c>
       <c r="B16" s="31">
-        <v>46146.0</v>
+        <v>46146</v>
       </c>
       <c r="C16" s="32" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3">
       <c r="A17" s="13" t="s">
         <v>825</v>
       </c>
       <c r="B17" s="31">
-        <v>46172.0</v>
+        <v>46172</v>
       </c>
       <c r="C17" s="32" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3">
       <c r="A18" s="13" t="s">
         <v>826</v>
       </c>
       <c r="B18" s="31">
-        <v>46174.0</v>
+        <v>46174</v>
       </c>
       <c r="C18" s="32" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3">
       <c r="A19" s="13" t="s">
         <v>828</v>
       </c>
       <c r="B19" s="31">
-        <v>46176.0</v>
+        <v>46176</v>
       </c>
       <c r="C19" s="32" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3">
       <c r="A20" s="13" t="s">
         <v>830</v>
       </c>
       <c r="B20" s="31">
-        <v>46200.0</v>
+        <v>46200</v>
       </c>
       <c r="C20" s="32" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3">
       <c r="A21" s="13" t="s">
         <v>831</v>
       </c>
@@ -11022,7 +11007,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3">
       <c r="A22" s="13" t="s">
         <v>833</v>
       </c>
@@ -11033,7 +11018,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
         <v>836</v>
       </c>
@@ -11044,7 +11029,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3">
       <c r="A24" s="13" t="s">
         <v>839</v>
       </c>
@@ -11055,7 +11040,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3">
       <c r="A25" s="13" t="s">
         <v>842</v>
       </c>
@@ -11066,7 +11051,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3">
       <c r="A26" s="13" t="s">
         <v>845</v>
       </c>
@@ -11077,7 +11062,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3">
       <c r="A27" s="13" t="s">
         <v>847</v>
       </c>
@@ -11088,7 +11073,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3">
       <c r="A28" s="13" t="s">
         <v>849</v>
       </c>
@@ -11099,7 +11084,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3">
       <c r="A29" s="13" t="s">
         <v>852</v>
       </c>
@@ -11110,7 +11095,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
         <v>854</v>
       </c>
@@ -11121,7 +11106,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3">
       <c r="A31" s="13" t="s">
         <v>857</v>
       </c>
@@ -11132,7 +11117,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3">
       <c r="A32" s="13" t="s">
         <v>859</v>
       </c>
@@ -11143,7 +11128,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3">
       <c r="A33" s="13" t="s">
         <v>861</v>
       </c>
@@ -11154,7 +11139,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3">
       <c r="A34" s="13" t="s">
         <v>864</v>
       </c>
@@ -11165,7 +11150,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3">
       <c r="A35" s="13" t="s">
         <v>867</v>
       </c>
@@ -11176,7 +11161,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3">
       <c r="A36" s="13" t="s">
         <v>869</v>
       </c>
@@ -11187,7 +11172,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3">
       <c r="A37" s="13" t="s">
         <v>871</v>
       </c>
@@ -11198,48 +11183,49 @@
         <v>873</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3">
       <c r="A38" s="13"/>
       <c r="B38" s="13"/>
       <c r="C38" s="24"/>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3">
       <c r="A39" s="13"/>
       <c r="B39" s="13"/>
       <c r="C39" s="24"/>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3">
       <c r="A40" s="13"/>
       <c r="B40" s="13"/>
       <c r="C40" s="24"/>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3">
       <c r="A41" s="13"/>
       <c r="B41" s="13"/>
       <c r="C41" s="24"/>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3">
       <c r="A42" s="13"/>
       <c r="B42" s="13"/>
       <c r="C42" s="24"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.13"/>
-    <col customWidth="1" min="2" max="2" width="11.13"/>
+    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
         <v>874</v>
       </c>
@@ -11247,7 +11233,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2">
       <c r="A2" s="13" t="s">
         <v>876</v>
       </c>
@@ -11255,7 +11241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2">
       <c r="A3" s="13" t="s">
         <v>877</v>
       </c>
@@ -11263,7 +11249,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2">
       <c r="A4" s="13" t="s">
         <v>878</v>
       </c>
@@ -11271,7 +11257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2">
       <c r="A5" s="13" t="s">
         <v>879</v>
       </c>
@@ -11279,7 +11265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2">
       <c r="A6" s="13" t="s">
         <v>880</v>
       </c>
@@ -11287,7 +11273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2">
       <c r="A7" s="13" t="s">
         <v>881</v>
       </c>
@@ -11295,7 +11281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2">
       <c r="A8" s="13" t="s">
         <v>882</v>
       </c>
@@ -11304,6 +11290,6 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ระบบลางาน ออนไลน์ 2025.xlsx
+++ b/ระบบลางาน ออนไลน์ 2025.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Setting" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="883">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="884">
   <si>
     <t>Setting (Folder)</t>
   </si>
@@ -2675,6 +2675,9 @@
   </si>
   <si>
     <t>Sunday</t>
+  </si>
+  <si>
+    <t>ID</t>
   </si>
 </sst>
 </file>
@@ -2684,7 +2687,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2768,8 +2771,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Prompt"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2780,6 +2787,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF745AF2"/>
         <bgColor rgb="FF745AF2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2796,7 +2809,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -2883,6 +2896,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3181,15 +3208,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="32.42578125" customWidth="1"/>
     <col min="4" max="4" width="17.42578125" customWidth="1"/>
-    <col min="9" max="9" width="60.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="42" customWidth="1"/>
+    <col min="10" max="10" width="60.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:12">
       <c r="A1" s="6" t="s">
         <v>14</v>
       </c>
@@ -3202,46 +3230,50 @@
       <c r="D1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="38" t="s">
+        <v>883</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="L1" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:12">
       <c r="A2" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
-      <c r="E2" s="13"/>
+      <c r="E2" s="39"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="15"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="17" t="b">
+      <c r="H2" s="13"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:12">
       <c r="A3" s="11" t="s">
         <v>26</v>
       </c>
@@ -3254,27 +3286,28 @@
       <c r="D3" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="40"/>
+      <c r="F3" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="G3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="H3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="14">
+      <c r="I3" s="14">
         <v>45838</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="J3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="16"/>
-      <c r="K3" s="17" t="b">
+      <c r="K3" s="16"/>
+      <c r="L3" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:12">
       <c r="A4" s="11" t="s">
         <v>34</v>
       </c>
@@ -3287,29 +3320,32 @@
       <c r="D4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="41">
+        <v>160</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="G4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="H4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="14">
+      <c r="I4" s="14">
         <v>45837</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="J4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="J4" s="16" t="s">
+      <c r="K4" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="17" t="b">
+      <c r="L4" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:12">
       <c r="A5" s="20" t="s">
         <v>43</v>
       </c>
@@ -3322,27 +3358,30 @@
       <c r="D5" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="40">
+        <v>272</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="G5" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="H5" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="H5" s="14">
+      <c r="I5" s="14">
         <v>45838</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="J5" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="16"/>
-      <c r="K5" s="17" t="b">
+      <c r="K5" s="16"/>
+      <c r="L5" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:12">
       <c r="A6" s="20" t="s">
         <v>48</v>
       </c>
@@ -3355,27 +3394,30 @@
       <c r="D6" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="41">
+        <v>288</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="G6" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="H6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="14">
+      <c r="I6" s="14">
         <v>45839</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="J6" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17" t="b">
+      <c r="K6" s="16"/>
+      <c r="L6" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:12">
       <c r="A7" s="20" t="s">
         <v>55</v>
       </c>
@@ -3388,27 +3430,30 @@
       <c r="D7" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="41">
+        <v>92</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="G7" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="H7" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H7" s="14">
+      <c r="I7" s="14">
         <v>45838</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="J7" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="J7" s="16"/>
-      <c r="K7" s="17" t="b">
+      <c r="K7" s="16"/>
+      <c r="L7" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:12">
       <c r="A8" s="20" t="s">
         <v>61</v>
       </c>
@@ -3421,27 +3466,30 @@
       <c r="D8" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="40">
+        <v>158</v>
+      </c>
+      <c r="F8" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="G8" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="H8" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="14">
+      <c r="I8" s="14">
         <v>45841</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="J8" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="17" t="b">
+      <c r="K8" s="16"/>
+      <c r="L8" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:12">
       <c r="A9" s="20" t="s">
         <v>67</v>
       </c>
@@ -3454,27 +3502,30 @@
       <c r="D9" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="40">
+        <v>161</v>
+      </c>
+      <c r="F9" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="G9" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="20" t="s">
+      <c r="H9" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="14">
+      <c r="I9" s="14">
         <v>45841</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="J9" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="J9" s="16"/>
-      <c r="K9" s="17" t="b">
+      <c r="K9" s="16"/>
+      <c r="L9" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:12">
       <c r="A10" s="20" t="s">
         <v>72</v>
       </c>
@@ -3487,27 +3538,30 @@
       <c r="D10" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="40">
+        <v>168</v>
+      </c>
+      <c r="F10" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="20" t="s">
+      <c r="G10" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="H10" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="14">
+      <c r="I10" s="14">
         <v>45841</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="J10" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="16"/>
-      <c r="K10" s="17" t="b">
+      <c r="K10" s="16"/>
+      <c r="L10" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:12">
       <c r="A11" s="20" t="s">
         <v>77</v>
       </c>
@@ -3520,27 +3574,30 @@
       <c r="D11" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="40">
+        <v>195</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="20" t="s">
+      <c r="G11" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="H11" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="14">
+      <c r="I11" s="14">
         <v>45841</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="J11" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="16"/>
-      <c r="K11" s="17" t="b">
+      <c r="K11" s="16"/>
+      <c r="L11" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:12">
       <c r="A12" s="20" t="s">
         <v>82</v>
       </c>
@@ -3553,27 +3610,30 @@
       <c r="D12" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="40">
+        <v>198</v>
+      </c>
+      <c r="F12" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="G12" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="H12" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="14">
+      <c r="I12" s="14">
         <v>45841</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="J12" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="16"/>
-      <c r="K12" s="17" t="b">
+      <c r="K12" s="16"/>
+      <c r="L12" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:12">
       <c r="A13" s="20" t="s">
         <v>87</v>
       </c>
@@ -3586,27 +3646,30 @@
       <c r="D13" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="40">
+        <v>205</v>
+      </c>
+      <c r="F13" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="G13" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G13" s="20" t="s">
+      <c r="H13" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H13" s="14">
+      <c r="I13" s="14">
         <v>45841</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="J13" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="16"/>
-      <c r="K13" s="17" t="b">
+      <c r="K13" s="16"/>
+      <c r="L13" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:12">
       <c r="A14" s="20" t="s">
         <v>92</v>
       </c>
@@ -3619,27 +3682,30 @@
       <c r="D14" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="40">
+        <v>217</v>
+      </c>
+      <c r="F14" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="G14" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="H14" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H14" s="14">
+      <c r="I14" s="14">
         <v>45841</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="J14" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="J14" s="16"/>
-      <c r="K14" s="17" t="b">
+      <c r="K14" s="16"/>
+      <c r="L14" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:12">
       <c r="A15" s="20" t="s">
         <v>97</v>
       </c>
@@ -3652,27 +3718,30 @@
       <c r="D15" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="40">
+        <v>224</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="G15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="H15" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H15" s="14">
+      <c r="I15" s="14">
         <v>45841</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="J15" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="J15" s="16"/>
-      <c r="K15" s="17" t="b">
+      <c r="K15" s="16"/>
+      <c r="L15" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:12">
       <c r="A16" s="20" t="s">
         <v>102</v>
       </c>
@@ -3685,44 +3754,48 @@
       <c r="D16" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="40">
+        <v>228</v>
+      </c>
+      <c r="F16" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="G16" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="H16" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H16" s="14">
+      <c r="I16" s="14">
         <v>45841</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="J16" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="J16" s="16"/>
-      <c r="K16" s="17" t="b">
+      <c r="K16" s="16"/>
+      <c r="L16" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:12">
       <c r="A17" s="20" t="s">
         <v>107</v>
       </c>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
-      <c r="E17" s="20"/>
+      <c r="E17" s="41"/>
       <c r="F17" s="20"/>
       <c r="G17" s="20"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="16"/>
-      <c r="K17" s="17" t="b">
+      <c r="H17" s="20"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:12">
       <c r="A18" s="20" t="s">
         <v>108</v>
       </c>
@@ -3735,27 +3808,30 @@
       <c r="D18" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="E18" s="40">
+        <v>234</v>
+      </c>
+      <c r="F18" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="G18" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G18" s="20" t="s">
+      <c r="H18" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="14">
+      <c r="I18" s="14">
         <v>45841</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="J18" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="J18" s="16"/>
-      <c r="K18" s="17" t="b">
+      <c r="K18" s="16"/>
+      <c r="L18" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:12">
       <c r="A19" s="20" t="s">
         <v>113</v>
       </c>
@@ -3768,27 +3844,30 @@
       <c r="D19" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="40">
+        <v>236</v>
+      </c>
+      <c r="F19" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="G19" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="H19" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H19" s="14">
+      <c r="I19" s="14">
         <v>45841</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="J19" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="J19" s="16"/>
-      <c r="K19" s="17" t="b">
+      <c r="K19" s="16"/>
+      <c r="L19" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:12">
       <c r="A20" s="20" t="s">
         <v>118</v>
       </c>
@@ -3801,27 +3880,30 @@
       <c r="D20" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="40">
+        <v>238</v>
+      </c>
+      <c r="F20" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="G20" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="H20" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H20" s="14">
+      <c r="I20" s="14">
         <v>45841</v>
       </c>
-      <c r="I20" s="15" t="s">
+      <c r="J20" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="J20" s="16"/>
-      <c r="K20" s="17" t="b">
+      <c r="K20" s="16"/>
+      <c r="L20" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:12">
       <c r="A21" s="20" t="s">
         <v>123</v>
       </c>
@@ -3834,27 +3916,30 @@
       <c r="D21" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="E21" s="40">
+        <v>248</v>
+      </c>
+      <c r="F21" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F21" s="20" t="s">
+      <c r="G21" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G21" s="20" t="s">
+      <c r="H21" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H21" s="14">
+      <c r="I21" s="14">
         <v>45841</v>
       </c>
-      <c r="I21" s="15" t="s">
+      <c r="J21" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="J21" s="16"/>
-      <c r="K21" s="17" t="b">
+      <c r="K21" s="16"/>
+      <c r="L21" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:12">
       <c r="A22" s="20" t="s">
         <v>128</v>
       </c>
@@ -3867,27 +3952,30 @@
       <c r="D22" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="40">
+        <v>251</v>
+      </c>
+      <c r="F22" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F22" s="20" t="s">
+      <c r="G22" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="20" t="s">
+      <c r="H22" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H22" s="14">
+      <c r="I22" s="14">
         <v>45841</v>
       </c>
-      <c r="I22" s="15" t="s">
+      <c r="J22" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="J22" s="16"/>
-      <c r="K22" s="17" t="b">
+      <c r="K22" s="16"/>
+      <c r="L22" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:12">
       <c r="A23" s="20" t="s">
         <v>133</v>
       </c>
@@ -3900,27 +3988,30 @@
       <c r="D23" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="40">
+        <v>254</v>
+      </c>
+      <c r="F23" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F23" s="20" t="s">
+      <c r="G23" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G23" s="20" t="s">
+      <c r="H23" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H23" s="14">
+      <c r="I23" s="14">
         <v>45841</v>
       </c>
-      <c r="I23" s="15" t="s">
+      <c r="J23" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="J23" s="16"/>
-      <c r="K23" s="17" t="b">
+      <c r="K23" s="16"/>
+      <c r="L23" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:12">
       <c r="A24" s="20" t="s">
         <v>138</v>
       </c>
@@ -3933,44 +4024,48 @@
       <c r="D24" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="40">
+        <v>266</v>
+      </c>
+      <c r="F24" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="G24" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="H24" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H24" s="14">
+      <c r="I24" s="14">
         <v>45841</v>
       </c>
-      <c r="I24" s="15" t="s">
+      <c r="J24" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="J24" s="16"/>
-      <c r="K24" s="17" t="b">
+      <c r="K24" s="16"/>
+      <c r="L24" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:12">
       <c r="A25" s="20" t="s">
         <v>143</v>
       </c>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
-      <c r="E25" s="20"/>
+      <c r="E25" s="41"/>
       <c r="F25" s="20"/>
       <c r="G25" s="20"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="16"/>
-      <c r="K25" s="17" t="b">
+      <c r="H25" s="20"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="16"/>
+      <c r="L25" s="17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:12">
       <c r="A26" s="20" t="s">
         <v>144</v>
       </c>
@@ -3983,27 +4078,30 @@
       <c r="D26" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="40">
+        <v>276</v>
+      </c>
+      <c r="F26" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F26" s="20" t="s">
+      <c r="G26" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G26" s="20" t="s">
+      <c r="H26" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H26" s="14">
+      <c r="I26" s="14">
         <v>45841</v>
       </c>
-      <c r="I26" s="15" t="s">
+      <c r="J26" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="J26" s="16"/>
-      <c r="K26" s="17" t="b">
+      <c r="K26" s="16"/>
+      <c r="L26" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:12">
       <c r="A27" s="20" t="s">
         <v>149</v>
       </c>
@@ -4016,27 +4114,30 @@
       <c r="D27" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="E27" s="20" t="s">
+      <c r="E27" s="40">
+        <v>277</v>
+      </c>
+      <c r="F27" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="20" t="s">
+      <c r="G27" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G27" s="20" t="s">
+      <c r="H27" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H27" s="14">
+      <c r="I27" s="14">
         <v>45841</v>
       </c>
-      <c r="I27" s="15" t="s">
+      <c r="J27" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="J27" s="16"/>
-      <c r="K27" s="17" t="b">
+      <c r="K27" s="16"/>
+      <c r="L27" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:12">
       <c r="A28" s="20" t="s">
         <v>154</v>
       </c>
@@ -4049,27 +4150,30 @@
       <c r="D28" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="40">
+        <v>278</v>
+      </c>
+      <c r="F28" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F28" s="20" t="s">
+      <c r="G28" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G28" s="20" t="s">
+      <c r="H28" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H28" s="14">
+      <c r="I28" s="14">
         <v>45841</v>
       </c>
-      <c r="I28" s="15" t="s">
+      <c r="J28" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="J28" s="16"/>
-      <c r="K28" s="17" t="b">
+      <c r="K28" s="16"/>
+      <c r="L28" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:12">
       <c r="A29" s="20" t="s">
         <v>159</v>
       </c>
@@ -4082,27 +4186,30 @@
       <c r="D29" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="20" t="s">
+      <c r="E29" s="40">
+        <v>280</v>
+      </c>
+      <c r="F29" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="G29" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="H29" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H29" s="14">
+      <c r="I29" s="14">
         <v>45841</v>
       </c>
-      <c r="I29" s="15" t="s">
+      <c r="J29" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="J29" s="16"/>
-      <c r="K29" s="17" t="b">
+      <c r="K29" s="16"/>
+      <c r="L29" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:12">
       <c r="A30" s="20" t="s">
         <v>164</v>
       </c>
@@ -4115,27 +4222,30 @@
       <c r="D30" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="E30" s="40">
+        <v>65</v>
+      </c>
+      <c r="F30" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="G30" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="H30" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H30" s="14">
+      <c r="I30" s="14">
         <v>45843</v>
       </c>
-      <c r="I30" s="15" t="s">
+      <c r="J30" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="J30" s="16"/>
-      <c r="K30" s="17" t="b">
+      <c r="K30" s="16"/>
+      <c r="L30" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:12">
       <c r="A31" s="20" t="s">
         <v>171</v>
       </c>
@@ -4148,27 +4258,30 @@
       <c r="D31" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="E31" s="20" t="s">
+      <c r="E31" s="40">
+        <v>71</v>
+      </c>
+      <c r="F31" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="G31" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="H31" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H31" s="14">
+      <c r="I31" s="14">
         <v>45843</v>
       </c>
-      <c r="I31" s="15" t="s">
+      <c r="J31" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="J31" s="16"/>
-      <c r="K31" s="17" t="b">
+      <c r="K31" s="16"/>
+      <c r="L31" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:11">
+    <row r="32" spans="1:12">
       <c r="A32" s="20" t="s">
         <v>177</v>
       </c>
@@ -4181,27 +4294,30 @@
       <c r="D32" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="40">
+        <v>76</v>
+      </c>
+      <c r="F32" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F32" s="20" t="s">
+      <c r="G32" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G32" s="20" t="s">
+      <c r="H32" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H32" s="14">
+      <c r="I32" s="14">
         <v>45843</v>
       </c>
-      <c r="I32" s="15" t="s">
+      <c r="J32" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="J32" s="16"/>
-      <c r="K32" s="17" t="b">
+      <c r="K32" s="16"/>
+      <c r="L32" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:11">
+    <row r="33" spans="1:12">
       <c r="A33" s="20" t="s">
         <v>182</v>
       </c>
@@ -4214,27 +4330,28 @@
       <c r="D33" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="43"/>
+      <c r="F33" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="G33" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="H33" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H33" s="14">
+      <c r="I33" s="14">
         <v>45843</v>
       </c>
-      <c r="I33" s="15" t="s">
+      <c r="J33" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="J33" s="16"/>
-      <c r="K33" s="17" t="b">
+      <c r="K33" s="16"/>
+      <c r="L33" s="17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:11">
+    <row r="34" spans="1:12">
       <c r="A34" s="20" t="s">
         <v>187</v>
       </c>
@@ -4247,27 +4364,30 @@
       <c r="D34" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="E34" s="20" t="s">
+      <c r="E34" s="40">
+        <v>77</v>
+      </c>
+      <c r="F34" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F34" s="20" t="s">
+      <c r="G34" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G34" s="20" t="s">
+      <c r="H34" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H34" s="14">
+      <c r="I34" s="14">
         <v>45843</v>
       </c>
-      <c r="I34" s="15" t="s">
+      <c r="J34" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="J34" s="16"/>
-      <c r="K34" s="17" t="b">
+      <c r="K34" s="16"/>
+      <c r="L34" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:12">
       <c r="A35" s="20" t="s">
         <v>192</v>
       </c>
@@ -4280,27 +4400,30 @@
       <c r="D35" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="E35" s="20" t="s">
+      <c r="E35" s="40">
+        <v>79</v>
+      </c>
+      <c r="F35" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F35" s="20" t="s">
+      <c r="G35" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G35" s="20" t="s">
+      <c r="H35" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H35" s="14">
+      <c r="I35" s="14">
         <v>45843</v>
       </c>
-      <c r="I35" s="15" t="s">
+      <c r="J35" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="J35" s="16"/>
-      <c r="K35" s="17" t="b">
+      <c r="K35" s="16"/>
+      <c r="L35" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:11">
+    <row r="36" spans="1:12">
       <c r="A36" s="20" t="s">
         <v>198</v>
       </c>
@@ -4313,27 +4436,30 @@
       <c r="D36" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="40">
+        <v>101</v>
+      </c>
+      <c r="F36" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F36" s="20" t="s">
+      <c r="G36" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G36" s="20" t="s">
+      <c r="H36" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H36" s="14">
+      <c r="I36" s="14">
         <v>45843</v>
       </c>
-      <c r="I36" s="15" t="s">
+      <c r="J36" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="J36" s="16"/>
-      <c r="K36" s="17" t="b">
+      <c r="K36" s="16"/>
+      <c r="L36" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:11">
+    <row r="37" spans="1:12">
       <c r="A37" s="20" t="s">
         <v>203</v>
       </c>
@@ -4346,27 +4472,30 @@
       <c r="D37" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="40">
+        <v>106</v>
+      </c>
+      <c r="F37" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="G37" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="H37" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H37" s="14">
+      <c r="I37" s="14">
         <v>45843</v>
       </c>
-      <c r="I37" s="15" t="s">
+      <c r="J37" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="J37" s="16"/>
-      <c r="K37" s="17" t="b">
+      <c r="K37" s="16"/>
+      <c r="L37" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:12">
       <c r="A38" s="20" t="s">
         <v>208</v>
       </c>
@@ -4379,27 +4508,30 @@
       <c r="D38" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="E38" s="20" t="s">
+      <c r="E38" s="40">
+        <v>114</v>
+      </c>
+      <c r="F38" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F38" s="20" t="s">
+      <c r="G38" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G38" s="20" t="s">
+      <c r="H38" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H38" s="14">
+      <c r="I38" s="14">
         <v>45843</v>
       </c>
-      <c r="I38" s="15" t="s">
+      <c r="J38" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="J38" s="16"/>
-      <c r="K38" s="17" t="b">
+      <c r="K38" s="16"/>
+      <c r="L38" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:11">
+    <row r="39" spans="1:12">
       <c r="A39" s="20" t="s">
         <v>213</v>
       </c>
@@ -4412,27 +4544,30 @@
       <c r="D39" s="18" t="s">
         <v>216</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="E39" s="40">
+        <v>122</v>
+      </c>
+      <c r="F39" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F39" s="20" t="s">
+      <c r="G39" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G39" s="20" t="s">
+      <c r="H39" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H39" s="14">
+      <c r="I39" s="14">
         <v>45843</v>
       </c>
-      <c r="I39" s="15" t="s">
+      <c r="J39" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="J39" s="16"/>
-      <c r="K39" s="17" t="b">
+      <c r="K39" s="16"/>
+      <c r="L39" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:12">
       <c r="A40" s="20" t="s">
         <v>218</v>
       </c>
@@ -4445,27 +4580,30 @@
       <c r="D40" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="E40" s="20" t="s">
+      <c r="E40" s="40">
+        <v>137</v>
+      </c>
+      <c r="F40" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F40" s="20" t="s">
+      <c r="G40" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="H40" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H40" s="14">
+      <c r="I40" s="14">
         <v>45843</v>
       </c>
-      <c r="I40" s="15" t="s">
+      <c r="J40" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="J40" s="16"/>
-      <c r="K40" s="17" t="b">
+      <c r="K40" s="16"/>
+      <c r="L40" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:11">
+    <row r="41" spans="1:12">
       <c r="A41" s="20" t="s">
         <v>223</v>
       </c>
@@ -4478,27 +4616,30 @@
       <c r="D41" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="E41" s="20" t="s">
+      <c r="E41" s="40">
+        <v>141</v>
+      </c>
+      <c r="F41" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F41" s="20" t="s">
+      <c r="G41" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G41" s="20" t="s">
+      <c r="H41" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H41" s="14">
+      <c r="I41" s="14">
         <v>45843</v>
       </c>
-      <c r="I41" s="15" t="s">
+      <c r="J41" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="J41" s="16"/>
-      <c r="K41" s="17" t="b">
+      <c r="K41" s="16"/>
+      <c r="L41" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
+    <row r="42" spans="1:12">
       <c r="A42" s="20" t="s">
         <v>228</v>
       </c>
@@ -4511,27 +4652,30 @@
       <c r="D42" s="18" t="s">
         <v>231</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="40">
+        <v>147</v>
+      </c>
+      <c r="F42" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F42" s="20" t="s">
+      <c r="G42" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G42" s="20" t="s">
+      <c r="H42" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H42" s="14">
+      <c r="I42" s="14">
         <v>45843</v>
       </c>
-      <c r="I42" s="15" t="s">
+      <c r="J42" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="J42" s="16"/>
-      <c r="K42" s="17" t="b">
+      <c r="K42" s="16"/>
+      <c r="L42" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:12">
       <c r="A43" s="20" t="s">
         <v>233</v>
       </c>
@@ -4544,27 +4688,30 @@
       <c r="D43" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="E43" s="20" t="s">
+      <c r="E43" s="40">
+        <v>153</v>
+      </c>
+      <c r="F43" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F43" s="20" t="s">
+      <c r="G43" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G43" s="20" t="s">
+      <c r="H43" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H43" s="14">
+      <c r="I43" s="14">
         <v>45843</v>
       </c>
-      <c r="I43" s="15" t="s">
+      <c r="J43" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="J43" s="16"/>
-      <c r="K43" s="17" t="b">
+      <c r="K43" s="16"/>
+      <c r="L43" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:11">
+    <row r="44" spans="1:12">
       <c r="A44" s="20" t="s">
         <v>238</v>
       </c>
@@ -4577,27 +4724,30 @@
       <c r="D44" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="E44" s="20" t="s">
+      <c r="E44" s="40">
+        <v>167</v>
+      </c>
+      <c r="F44" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F44" s="20" t="s">
+      <c r="G44" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G44" s="20" t="s">
+      <c r="H44" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H44" s="14">
+      <c r="I44" s="14">
         <v>45843</v>
       </c>
-      <c r="I44" s="15" t="s">
+      <c r="J44" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="J44" s="16"/>
-      <c r="K44" s="17" t="b">
+      <c r="K44" s="16"/>
+      <c r="L44" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:11">
+    <row r="45" spans="1:12">
       <c r="A45" s="20" t="s">
         <v>243</v>
       </c>
@@ -4610,27 +4760,30 @@
       <c r="D45" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="E45" s="20" t="s">
+      <c r="E45" s="40">
+        <v>169</v>
+      </c>
+      <c r="F45" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="F45" s="20" t="s">
+      <c r="G45" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="G45" s="20" t="s">
+      <c r="H45" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H45" s="14">
+      <c r="I45" s="14">
         <v>45843</v>
       </c>
-      <c r="I45" s="15" t="s">
+      <c r="J45" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="J45" s="16"/>
-      <c r="K45" s="17" t="b">
+      <c r="K45" s="16"/>
+      <c r="L45" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:11">
+    <row r="46" spans="1:12">
       <c r="A46" s="20" t="s">
         <v>250</v>
       </c>
@@ -4643,27 +4796,30 @@
       <c r="D46" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="40">
+        <v>187</v>
+      </c>
+      <c r="F46" s="20" t="s">
         <v>254</v>
       </c>
-      <c r="F46" s="20" t="s">
+      <c r="G46" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G46" s="20" t="s">
+      <c r="H46" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H46" s="14">
+      <c r="I46" s="14">
         <v>45843</v>
       </c>
-      <c r="I46" s="15" t="s">
+      <c r="J46" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="J46" s="16"/>
-      <c r="K46" s="17" t="b">
+      <c r="K46" s="16"/>
+      <c r="L46" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:11">
+    <row r="47" spans="1:12">
       <c r="A47" s="20" t="s">
         <v>256</v>
       </c>
@@ -4676,27 +4832,30 @@
       <c r="D47" s="18" t="s">
         <v>259</v>
       </c>
-      <c r="E47" s="20" t="s">
+      <c r="E47" s="40">
+        <v>192</v>
+      </c>
+      <c r="F47" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F47" s="20" t="s">
+      <c r="G47" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G47" s="20" t="s">
+      <c r="H47" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H47" s="14">
+      <c r="I47" s="14">
         <v>45843</v>
       </c>
-      <c r="I47" s="15" t="s">
+      <c r="J47" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="J47" s="16"/>
-      <c r="K47" s="17" t="b">
+      <c r="K47" s="16"/>
+      <c r="L47" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:11">
+    <row r="48" spans="1:12">
       <c r="A48" s="20" t="s">
         <v>261</v>
       </c>
@@ -4709,27 +4868,30 @@
       <c r="D48" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="E48" s="20" t="s">
+      <c r="E48" s="40">
+        <v>193</v>
+      </c>
+      <c r="F48" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F48" s="20" t="s">
+      <c r="G48" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G48" s="20" t="s">
+      <c r="H48" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H48" s="14">
+      <c r="I48" s="14">
         <v>45843</v>
       </c>
-      <c r="I48" s="15" t="s">
+      <c r="J48" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="J48" s="16"/>
-      <c r="K48" s="17" t="b">
+      <c r="K48" s="16"/>
+      <c r="L48" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:11">
+    <row r="49" spans="1:12">
       <c r="A49" s="20" t="s">
         <v>266</v>
       </c>
@@ -4742,27 +4904,30 @@
       <c r="D49" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="E49" s="20" t="s">
+      <c r="E49" s="40">
+        <v>196</v>
+      </c>
+      <c r="F49" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F49" s="20" t="s">
+      <c r="G49" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G49" s="20" t="s">
+      <c r="H49" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H49" s="14">
+      <c r="I49" s="14">
         <v>45843</v>
       </c>
-      <c r="I49" s="15" t="s">
+      <c r="J49" s="15" t="s">
         <v>270</v>
       </c>
-      <c r="J49" s="16"/>
-      <c r="K49" s="17" t="b">
+      <c r="K49" s="16"/>
+      <c r="L49" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:11">
+    <row r="50" spans="1:12">
       <c r="A50" s="20" t="s">
         <v>271</v>
       </c>
@@ -4775,27 +4940,30 @@
       <c r="D50" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="40">
+        <v>197</v>
+      </c>
+      <c r="F50" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F50" s="20" t="s">
+      <c r="G50" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G50" s="20" t="s">
+      <c r="H50" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H50" s="14">
+      <c r="I50" s="14">
         <v>45843</v>
       </c>
-      <c r="I50" s="15" t="s">
+      <c r="J50" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="J50" s="16"/>
-      <c r="K50" s="17" t="b">
+      <c r="K50" s="16"/>
+      <c r="L50" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:11">
+    <row r="51" spans="1:12">
       <c r="A51" s="20" t="s">
         <v>276</v>
       </c>
@@ -4808,27 +4976,30 @@
       <c r="D51" s="18" t="s">
         <v>279</v>
       </c>
-      <c r="E51" s="20" t="s">
+      <c r="E51" s="40">
+        <v>203</v>
+      </c>
+      <c r="F51" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F51" s="20" t="s">
+      <c r="G51" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G51" s="20" t="s">
+      <c r="H51" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H51" s="14">
+      <c r="I51" s="14">
         <v>45843</v>
       </c>
-      <c r="I51" s="15" t="s">
+      <c r="J51" s="15" t="s">
         <v>280</v>
       </c>
-      <c r="J51" s="16"/>
-      <c r="K51" s="17" t="b">
+      <c r="K51" s="16"/>
+      <c r="L51" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:11">
+    <row r="52" spans="1:12">
       <c r="A52" s="20" t="s">
         <v>281</v>
       </c>
@@ -4841,27 +5012,30 @@
       <c r="D52" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="E52" s="20" t="s">
+      <c r="E52" s="40">
+        <v>206</v>
+      </c>
+      <c r="F52" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F52" s="20" t="s">
+      <c r="G52" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G52" s="20" t="s">
+      <c r="H52" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H52" s="14">
+      <c r="I52" s="14">
         <v>45843</v>
       </c>
-      <c r="I52" s="15" t="s">
+      <c r="J52" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="J52" s="16"/>
-      <c r="K52" s="17" t="b">
+      <c r="K52" s="16"/>
+      <c r="L52" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:11">
+    <row r="53" spans="1:12">
       <c r="A53" s="20" t="s">
         <v>286</v>
       </c>
@@ -4874,27 +5048,30 @@
       <c r="D53" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="40">
+        <v>213</v>
+      </c>
+      <c r="F53" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F53" s="20" t="s">
+      <c r="G53" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G53" s="20" t="s">
+      <c r="H53" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H53" s="14">
+      <c r="I53" s="14">
         <v>45843</v>
       </c>
-      <c r="I53" s="15" t="s">
+      <c r="J53" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="J53" s="16"/>
-      <c r="K53" s="17" t="b">
+      <c r="K53" s="16"/>
+      <c r="L53" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:11">
+    <row r="54" spans="1:12">
       <c r="A54" s="20" t="s">
         <v>291</v>
       </c>
@@ -4907,27 +5084,30 @@
       <c r="D54" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="E54" s="20" t="s">
+      <c r="E54" s="40">
+        <v>214</v>
+      </c>
+      <c r="F54" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="F54" s="20" t="s">
+      <c r="G54" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="G54" s="20" t="s">
+      <c r="H54" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H54" s="14">
+      <c r="I54" s="14">
         <v>45843</v>
       </c>
-      <c r="I54" s="15" t="s">
+      <c r="J54" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="J54" s="16"/>
-      <c r="K54" s="17" t="b">
+      <c r="K54" s="16"/>
+      <c r="L54" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:11">
+    <row r="55" spans="1:12">
       <c r="A55" s="20" t="s">
         <v>298</v>
       </c>
@@ -4940,27 +5120,30 @@
       <c r="D55" s="18" t="s">
         <v>301</v>
       </c>
-      <c r="E55" s="20" t="s">
+      <c r="E55" s="40">
+        <v>223</v>
+      </c>
+      <c r="F55" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F55" s="20" t="s">
+      <c r="G55" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G55" s="20" t="s">
+      <c r="H55" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H55" s="14">
+      <c r="I55" s="14">
         <v>45843</v>
       </c>
-      <c r="I55" s="15" t="s">
+      <c r="J55" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="J55" s="16"/>
-      <c r="K55" s="17" t="b">
+      <c r="K55" s="16"/>
+      <c r="L55" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:11">
+    <row r="56" spans="1:12">
       <c r="A56" s="20" t="s">
         <v>303</v>
       </c>
@@ -4973,27 +5156,30 @@
       <c r="D56" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="40">
+        <v>235</v>
+      </c>
+      <c r="F56" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F56" s="20" t="s">
+      <c r="G56" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G56" s="20" t="s">
+      <c r="H56" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H56" s="14">
+      <c r="I56" s="14">
         <v>45843</v>
       </c>
-      <c r="I56" s="15" t="s">
+      <c r="J56" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="J56" s="16"/>
-      <c r="K56" s="17" t="b">
+      <c r="K56" s="16"/>
+      <c r="L56" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:12">
       <c r="A57" s="20" t="s">
         <v>308</v>
       </c>
@@ -5006,27 +5192,30 @@
       <c r="D57" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="E57" s="20" t="s">
+      <c r="E57" s="40">
+        <v>240</v>
+      </c>
+      <c r="F57" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F57" s="20" t="s">
+      <c r="G57" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G57" s="20" t="s">
+      <c r="H57" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H57" s="14">
+      <c r="I57" s="14">
         <v>45843</v>
       </c>
-      <c r="I57" s="15" t="s">
+      <c r="J57" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="J57" s="16"/>
-      <c r="K57" s="17" t="b">
+      <c r="K57" s="16"/>
+      <c r="L57" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:12">
       <c r="A58" s="20" t="s">
         <v>313</v>
       </c>
@@ -5039,27 +5228,30 @@
       <c r="D58" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="E58" s="20" t="s">
+      <c r="E58" s="40">
+        <v>242</v>
+      </c>
+      <c r="F58" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F58" s="20" t="s">
+      <c r="G58" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G58" s="20" t="s">
+      <c r="H58" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H58" s="14">
+      <c r="I58" s="14">
         <v>45843</v>
       </c>
-      <c r="I58" s="15" t="s">
+      <c r="J58" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="J58" s="16"/>
-      <c r="K58" s="17" t="b">
+      <c r="K58" s="16"/>
+      <c r="L58" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:12">
       <c r="A59" s="20" t="s">
         <v>318</v>
       </c>
@@ -5072,27 +5264,30 @@
       <c r="D59" s="18" t="s">
         <v>321</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="40">
+        <v>246</v>
+      </c>
+      <c r="F59" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F59" s="20" t="s">
+      <c r="G59" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G59" s="20" t="s">
+      <c r="H59" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H59" s="14">
+      <c r="I59" s="14">
         <v>45843</v>
       </c>
-      <c r="I59" s="15" t="s">
+      <c r="J59" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="J59" s="16"/>
-      <c r="K59" s="17" t="b">
+      <c r="K59" s="16"/>
+      <c r="L59" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:12">
       <c r="A60" s="20" t="s">
         <v>323</v>
       </c>
@@ -5105,27 +5300,28 @@
       <c r="D60" s="18" t="s">
         <v>326</v>
       </c>
-      <c r="E60" s="20" t="s">
+      <c r="E60" s="40"/>
+      <c r="F60" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F60" s="20" t="s">
+      <c r="G60" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G60" s="20" t="s">
+      <c r="H60" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H60" s="14">
+      <c r="I60" s="14">
         <v>45843</v>
       </c>
-      <c r="I60" s="15" t="s">
+      <c r="J60" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="J60" s="16"/>
-      <c r="K60" s="17" t="b">
+      <c r="K60" s="16"/>
+      <c r="L60" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:12">
       <c r="A61" s="20" t="s">
         <v>328</v>
       </c>
@@ -5138,27 +5334,30 @@
       <c r="D61" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="E61" s="20" t="s">
+      <c r="E61" s="40">
+        <v>261</v>
+      </c>
+      <c r="F61" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F61" s="20" t="s">
+      <c r="G61" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G61" s="20" t="s">
+      <c r="H61" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H61" s="14">
+      <c r="I61" s="14">
         <v>45843</v>
       </c>
-      <c r="I61" s="15" t="s">
+      <c r="J61" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="J61" s="16"/>
-      <c r="K61" s="17" t="b">
+      <c r="K61" s="16"/>
+      <c r="L61" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:11">
+    <row r="62" spans="1:12">
       <c r="A62" s="20" t="s">
         <v>333</v>
       </c>
@@ -5171,27 +5370,30 @@
       <c r="D62" s="18" t="s">
         <v>336</v>
       </c>
-      <c r="E62" s="20" t="s">
+      <c r="E62" s="40">
+        <v>262</v>
+      </c>
+      <c r="F62" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F62" s="20" t="s">
+      <c r="G62" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G62" s="20" t="s">
+      <c r="H62" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H62" s="14">
+      <c r="I62" s="14">
         <v>45843</v>
       </c>
-      <c r="I62" s="15" t="s">
+      <c r="J62" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="J62" s="16"/>
-      <c r="K62" s="17" t="b">
+      <c r="K62" s="16"/>
+      <c r="L62" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:12">
       <c r="A63" s="20" t="s">
         <v>338</v>
       </c>
@@ -5204,27 +5406,30 @@
       <c r="D63" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="E63" s="20" t="s">
+      <c r="E63" s="40">
+        <v>264</v>
+      </c>
+      <c r="F63" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F63" s="20" t="s">
+      <c r="G63" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G63" s="20" t="s">
+      <c r="H63" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H63" s="14">
+      <c r="I63" s="14">
         <v>45843</v>
       </c>
-      <c r="I63" s="15" t="s">
+      <c r="J63" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="J63" s="16"/>
-      <c r="K63" s="17" t="b">
+      <c r="K63" s="16"/>
+      <c r="L63" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:12">
       <c r="A64" s="20" t="s">
         <v>343</v>
       </c>
@@ -5237,27 +5442,30 @@
       <c r="D64" s="18" t="s">
         <v>346</v>
       </c>
-      <c r="E64" s="20" t="s">
+      <c r="E64" s="40">
+        <v>265</v>
+      </c>
+      <c r="F64" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F64" s="20" t="s">
+      <c r="G64" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G64" s="20" t="s">
+      <c r="H64" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H64" s="14">
+      <c r="I64" s="14">
         <v>45843</v>
       </c>
-      <c r="I64" s="15" t="s">
+      <c r="J64" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="J64" s="16"/>
-      <c r="K64" s="17" t="b">
+      <c r="K64" s="16"/>
+      <c r="L64" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:11">
+    <row r="65" spans="1:12">
       <c r="A65" s="20" t="s">
         <v>348</v>
       </c>
@@ -5270,44 +5478,48 @@
       <c r="D65" s="18" t="s">
         <v>351</v>
       </c>
-      <c r="E65" s="20" t="s">
+      <c r="E65" s="40">
+        <v>270</v>
+      </c>
+      <c r="F65" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F65" s="20" t="s">
+      <c r="G65" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G65" s="20" t="s">
+      <c r="H65" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H65" s="14">
+      <c r="I65" s="14">
         <v>45843</v>
       </c>
-      <c r="I65" s="15" t="s">
+      <c r="J65" s="15" t="s">
         <v>352</v>
       </c>
-      <c r="J65" s="16"/>
-      <c r="K65" s="17" t="b">
+      <c r="K65" s="16"/>
+      <c r="L65" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:11">
+    <row r="66" spans="1:12">
       <c r="A66" s="20" t="s">
         <v>353</v>
       </c>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
       <c r="D66" s="12"/>
-      <c r="E66" s="20"/>
+      <c r="E66" s="41"/>
       <c r="F66" s="20"/>
       <c r="G66" s="20"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15"/>
-      <c r="J66" s="16"/>
-      <c r="K66" s="17" t="b">
+      <c r="H66" s="20"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="15"/>
+      <c r="K66" s="16"/>
+      <c r="L66" s="17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:11">
+    <row r="67" spans="1:12">
       <c r="A67" s="20" t="s">
         <v>354</v>
       </c>
@@ -5320,27 +5532,30 @@
       <c r="D67" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="E67" s="20" t="s">
+      <c r="E67" s="41">
+        <v>281</v>
+      </c>
+      <c r="F67" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F67" s="20" t="s">
+      <c r="G67" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G67" s="20" t="s">
+      <c r="H67" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H67" s="14">
+      <c r="I67" s="14">
         <v>45843</v>
       </c>
-      <c r="I67" s="15" t="s">
+      <c r="J67" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="J67" s="16"/>
-      <c r="K67" s="17" t="b">
+      <c r="K67" s="16"/>
+      <c r="L67" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:11">
+    <row r="68" spans="1:12">
       <c r="A68" s="20" t="s">
         <v>359</v>
       </c>
@@ -5353,27 +5568,30 @@
       <c r="D68" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="E68" s="20" t="s">
+      <c r="E68" s="40">
+        <v>284</v>
+      </c>
+      <c r="F68" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F68" s="20" t="s">
+      <c r="G68" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G68" s="20" t="s">
+      <c r="H68" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H68" s="14">
+      <c r="I68" s="14">
         <v>45843</v>
       </c>
-      <c r="I68" s="15" t="s">
+      <c r="J68" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="J68" s="16"/>
-      <c r="K68" s="17" t="b">
+      <c r="K68" s="16"/>
+      <c r="L68" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:11">
+    <row r="69" spans="1:12">
       <c r="A69" s="20" t="s">
         <v>364</v>
       </c>
@@ -5386,27 +5604,30 @@
       <c r="D69" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="40">
+        <v>285</v>
+      </c>
+      <c r="F69" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F69" s="20" t="s">
+      <c r="G69" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G69" s="20" t="s">
+      <c r="H69" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H69" s="14">
+      <c r="I69" s="14">
         <v>45843</v>
       </c>
-      <c r="I69" s="15" t="s">
+      <c r="J69" s="15" t="s">
         <v>368</v>
       </c>
-      <c r="J69" s="16"/>
-      <c r="K69" s="17" t="b">
+      <c r="K69" s="16"/>
+      <c r="L69" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:11">
+    <row r="70" spans="1:12">
       <c r="A70" s="20" t="s">
         <v>369</v>
       </c>
@@ -5419,27 +5640,30 @@
       <c r="D70" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="E70" s="20" t="s">
+      <c r="E70" s="40">
+        <v>286</v>
+      </c>
+      <c r="F70" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F70" s="20" t="s">
+      <c r="G70" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G70" s="20" t="s">
+      <c r="H70" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H70" s="14">
+      <c r="I70" s="14">
         <v>45843</v>
       </c>
-      <c r="I70" s="15" t="s">
+      <c r="J70" s="15" t="s">
         <v>373</v>
       </c>
-      <c r="J70" s="16"/>
-      <c r="K70" s="17" t="b">
+      <c r="K70" s="16"/>
+      <c r="L70" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:12">
       <c r="A71" s="20" t="s">
         <v>374</v>
       </c>
@@ -5452,27 +5676,28 @@
       <c r="D71" s="18" t="s">
         <v>377</v>
       </c>
-      <c r="E71" s="20" t="s">
+      <c r="E71" s="40"/>
+      <c r="F71" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F71" s="20" t="s">
+      <c r="G71" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="G71" s="20" t="s">
+      <c r="H71" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="H71" s="14">
+      <c r="I71" s="14">
         <v>45853</v>
       </c>
-      <c r="I71" s="15" t="s">
+      <c r="J71" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="J71" s="16"/>
-      <c r="K71" s="17" t="b">
+      <c r="K71" s="16"/>
+      <c r="L71" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:12">
       <c r="A72" s="20" t="s">
         <v>379</v>
       </c>
@@ -5485,27 +5710,30 @@
       <c r="D72" s="18" t="s">
         <v>382</v>
       </c>
-      <c r="E72" s="20" t="s">
+      <c r="E72" s="40">
+        <v>289</v>
+      </c>
+      <c r="F72" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F72" s="20" t="s">
+      <c r="G72" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G72" s="20" t="s">
+      <c r="H72" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H72" s="14">
+      <c r="I72" s="14">
         <v>45871</v>
       </c>
-      <c r="I72" s="15" t="s">
+      <c r="J72" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="J72" s="16"/>
-      <c r="K72" s="17" t="b">
+      <c r="K72" s="16"/>
+      <c r="L72" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:12">
       <c r="A73" s="20" t="s">
         <v>384</v>
       </c>
@@ -5518,27 +5746,30 @@
       <c r="D73" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="E73" s="20" t="s">
+      <c r="E73" s="40">
+        <v>290</v>
+      </c>
+      <c r="F73" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F73" s="20" t="s">
+      <c r="G73" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G73" s="20" t="s">
+      <c r="H73" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H73" s="14">
+      <c r="I73" s="14">
         <v>45874</v>
       </c>
-      <c r="I73" s="15" t="s">
+      <c r="J73" s="15" t="s">
         <v>388</v>
       </c>
-      <c r="J73" s="16"/>
-      <c r="K73" s="17" t="b">
+      <c r="K73" s="16"/>
+      <c r="L73" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:12">
       <c r="A74" s="20" t="s">
         <v>389</v>
       </c>
@@ -5551,27 +5782,30 @@
       <c r="D74" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="E74" s="20" t="s">
+      <c r="E74" s="40">
+        <v>291</v>
+      </c>
+      <c r="F74" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F74" s="20" t="s">
+      <c r="G74" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G74" s="20" t="s">
+      <c r="H74" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H74" s="14">
+      <c r="I74" s="14">
         <v>45904</v>
       </c>
-      <c r="I74" s="15" t="s">
+      <c r="J74" s="15" t="s">
         <v>393</v>
       </c>
-      <c r="J74" s="16"/>
-      <c r="K74" s="17" t="b">
+      <c r="K74" s="16"/>
+      <c r="L74" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:12">
       <c r="A75" s="20" t="s">
         <v>394</v>
       </c>
@@ -5584,27 +5818,30 @@
       <c r="D75" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="E75" s="20" t="s">
+      <c r="E75" s="40">
+        <v>297</v>
+      </c>
+      <c r="F75" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F75" s="20" t="s">
+      <c r="G75" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G75" s="20" t="s">
+      <c r="H75" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H75" s="14">
+      <c r="I75" s="14">
         <v>46073</v>
       </c>
-      <c r="I75" s="15" t="s">
+      <c r="J75" s="15" t="s">
         <v>398</v>
       </c>
-      <c r="J75" s="16"/>
-      <c r="K75" s="17" t="b">
+      <c r="K75" s="16"/>
+      <c r="L75" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:12">
       <c r="A76" s="20" t="s">
         <v>399</v>
       </c>
@@ -5617,44 +5854,48 @@
       <c r="D76" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="E76" s="20" t="s">
+      <c r="E76" s="40">
+        <v>261003</v>
+      </c>
+      <c r="F76" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F76" s="20" t="s">
+      <c r="G76" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G76" s="20" t="s">
+      <c r="H76" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H76" s="14">
+      <c r="I76" s="14">
         <v>46083</v>
       </c>
-      <c r="I76" s="15" t="s">
+      <c r="J76" s="15" t="s">
         <v>403</v>
       </c>
-      <c r="J76" s="16"/>
-      <c r="K76" s="17" t="b">
+      <c r="K76" s="16"/>
+      <c r="L76" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:11">
+    <row r="77" spans="1:12">
       <c r="A77" s="20" t="s">
         <v>404</v>
       </c>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
       <c r="D77" s="12"/>
-      <c r="E77" s="20"/>
+      <c r="E77" s="41"/>
       <c r="F77" s="20"/>
       <c r="G77" s="20"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="16"/>
-      <c r="K77" s="17" t="b">
+      <c r="H77" s="20"/>
+      <c r="I77" s="14"/>
+      <c r="J77" s="15"/>
+      <c r="K77" s="16"/>
+      <c r="L77" s="17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:11">
+    <row r="78" spans="1:12">
       <c r="A78" s="20" t="s">
         <v>405</v>
       </c>
@@ -5667,27 +5908,30 @@
       <c r="D78" s="18" t="s">
         <v>408</v>
       </c>
-      <c r="E78" s="20" t="s">
+      <c r="E78" s="40">
+        <v>292</v>
+      </c>
+      <c r="F78" s="20" t="s">
         <v>196</v>
       </c>
-      <c r="F78" s="20" t="s">
+      <c r="G78" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G78" s="20" t="s">
+      <c r="H78" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H78" s="14">
+      <c r="I78" s="14">
         <v>46115</v>
       </c>
-      <c r="I78" s="15" t="s">
+      <c r="J78" s="15" t="s">
         <v>409</v>
       </c>
-      <c r="J78" s="16"/>
-      <c r="K78" s="17" t="b">
+      <c r="K78" s="16"/>
+      <c r="L78" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:12">
       <c r="A79" s="20" t="s">
         <v>410</v>
       </c>
@@ -5700,27 +5944,30 @@
       <c r="D79" s="18" t="s">
         <v>413</v>
       </c>
-      <c r="E79" s="20" t="s">
+      <c r="E79" s="40">
+        <v>293</v>
+      </c>
+      <c r="F79" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F79" s="20" t="s">
+      <c r="G79" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G79" s="20" t="s">
+      <c r="H79" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="H79" s="14">
+      <c r="I79" s="14">
         <v>46140</v>
       </c>
-      <c r="I79" s="15" t="s">
+      <c r="J79" s="15" t="s">
         <v>414</v>
       </c>
-      <c r="J79" s="16"/>
-      <c r="K79" s="17" t="b">
+      <c r="K79" s="16"/>
+      <c r="L79" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:11">
+    <row r="80" spans="1:12">
       <c r="A80" s="20" t="s">
         <v>415</v>
       </c>
@@ -5733,27 +5980,28 @@
       <c r="D80" s="18" t="s">
         <v>418</v>
       </c>
-      <c r="E80" s="20" t="s">
+      <c r="E80" s="40"/>
+      <c r="F80" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F80" s="20" t="s">
+      <c r="G80" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="G80" s="20" t="s">
+      <c r="H80" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H80" s="14">
+      <c r="I80" s="14">
         <v>46148</v>
       </c>
-      <c r="I80" s="15" t="s">
+      <c r="J80" s="15" t="s">
         <v>419</v>
       </c>
-      <c r="J80" s="16"/>
-      <c r="K80" s="17" t="b">
+      <c r="K80" s="16"/>
+      <c r="L80" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:11">
+    <row r="81" spans="1:12">
       <c r="A81" s="20" t="s">
         <v>420</v>
       </c>
@@ -5766,27 +6014,30 @@
       <c r="D81" s="18" t="s">
         <v>423</v>
       </c>
-      <c r="E81" s="20" t="s">
+      <c r="E81" s="40">
+        <v>295</v>
+      </c>
+      <c r="F81" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F81" s="20" t="s">
+      <c r="G81" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G81" s="20" t="s">
+      <c r="H81" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H81" s="14">
+      <c r="I81" s="14">
         <v>46179</v>
       </c>
-      <c r="I81" s="15" t="s">
+      <c r="J81" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="J81" s="16"/>
-      <c r="K81" s="17" t="b">
+      <c r="K81" s="16"/>
+      <c r="L81" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:12">
       <c r="A82" s="20" t="s">
         <v>425</v>
       </c>
@@ -5799,27 +6050,30 @@
       <c r="D82" s="18" t="s">
         <v>428</v>
       </c>
-      <c r="E82" s="20" t="s">
+      <c r="E82" s="40">
+        <v>296</v>
+      </c>
+      <c r="F82" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F82" s="20" t="s">
+      <c r="G82" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="G82" s="20" t="s">
+      <c r="H82" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H82" s="14">
+      <c r="I82" s="14">
         <v>46192</v>
       </c>
-      <c r="I82" s="15" t="s">
+      <c r="J82" s="15" t="s">
         <v>429</v>
       </c>
-      <c r="J82" s="16"/>
-      <c r="K82" s="17" t="b">
+      <c r="K82" s="16"/>
+      <c r="L82" s="17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:12">
       <c r="A83" s="20" t="s">
         <v>430</v>
       </c>
@@ -5832,106 +6086,109 @@
       <c r="D83" s="18" t="s">
         <v>433</v>
       </c>
-      <c r="E83" s="20" t="s">
+      <c r="E83" s="40">
+        <v>298</v>
+      </c>
+      <c r="F83" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="F83" s="20" t="s">
+      <c r="G83" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="G83" s="20" t="s">
+      <c r="H83" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H83" s="14">
+      <c r="I83" s="14">
         <v>46192</v>
       </c>
-      <c r="I83" s="15" t="s">
+      <c r="J83" s="15" t="s">
         <v>434</v>
       </c>
-      <c r="J83" s="16"/>
-      <c r="K83" s="17" t="b">
+      <c r="K83" s="16"/>
+      <c r="L83" s="17" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1"/>
-    <hyperlink ref="I4" r:id="rId2"/>
-    <hyperlink ref="J4" r:id="rId3"/>
-    <hyperlink ref="I5" r:id="rId4"/>
-    <hyperlink ref="I6" r:id="rId5"/>
-    <hyperlink ref="I7" r:id="rId6"/>
-    <hyperlink ref="I8" r:id="rId7"/>
-    <hyperlink ref="I9" r:id="rId8"/>
-    <hyperlink ref="I10" r:id="rId9"/>
-    <hyperlink ref="I11" r:id="rId10"/>
-    <hyperlink ref="I12" r:id="rId11"/>
-    <hyperlink ref="I13" r:id="rId12"/>
-    <hyperlink ref="I14" r:id="rId13"/>
-    <hyperlink ref="I15" r:id="rId14"/>
-    <hyperlink ref="I16" r:id="rId15"/>
-    <hyperlink ref="I18" r:id="rId16"/>
-    <hyperlink ref="I19" r:id="rId17"/>
-    <hyperlink ref="I20" r:id="rId18"/>
-    <hyperlink ref="I21" r:id="rId19"/>
-    <hyperlink ref="I22" r:id="rId20"/>
-    <hyperlink ref="I23" r:id="rId21"/>
-    <hyperlink ref="I24" r:id="rId22"/>
-    <hyperlink ref="I26" r:id="rId23"/>
-    <hyperlink ref="I27" r:id="rId24"/>
-    <hyperlink ref="I28" r:id="rId25"/>
-    <hyperlink ref="I29" r:id="rId26"/>
-    <hyperlink ref="I30" r:id="rId27"/>
-    <hyperlink ref="I31" r:id="rId28"/>
-    <hyperlink ref="I32" r:id="rId29"/>
-    <hyperlink ref="I33" r:id="rId30"/>
-    <hyperlink ref="I34" r:id="rId31"/>
-    <hyperlink ref="I35" r:id="rId32"/>
-    <hyperlink ref="I36" r:id="rId33"/>
-    <hyperlink ref="I37" r:id="rId34"/>
-    <hyperlink ref="I38" r:id="rId35"/>
-    <hyperlink ref="I39" r:id="rId36"/>
-    <hyperlink ref="I40" r:id="rId37"/>
-    <hyperlink ref="I41" r:id="rId38"/>
-    <hyperlink ref="I42" r:id="rId39"/>
-    <hyperlink ref="I43" r:id="rId40"/>
-    <hyperlink ref="I44" r:id="rId41"/>
-    <hyperlink ref="I45" r:id="rId42"/>
-    <hyperlink ref="I46" r:id="rId43"/>
-    <hyperlink ref="I47" r:id="rId44"/>
-    <hyperlink ref="I48" r:id="rId45"/>
-    <hyperlink ref="I49" r:id="rId46"/>
-    <hyperlink ref="I50" r:id="rId47"/>
-    <hyperlink ref="I51" r:id="rId48"/>
-    <hyperlink ref="I52" r:id="rId49"/>
-    <hyperlink ref="I53" r:id="rId50"/>
-    <hyperlink ref="I54" r:id="rId51"/>
-    <hyperlink ref="I55" r:id="rId52"/>
-    <hyperlink ref="I56" r:id="rId53"/>
-    <hyperlink ref="I57" r:id="rId54"/>
-    <hyperlink ref="I58" r:id="rId55"/>
-    <hyperlink ref="I59" r:id="rId56"/>
-    <hyperlink ref="I60" r:id="rId57"/>
-    <hyperlink ref="I61" r:id="rId58"/>
-    <hyperlink ref="I62" r:id="rId59"/>
-    <hyperlink ref="I63" r:id="rId60"/>
-    <hyperlink ref="I64" r:id="rId61"/>
-    <hyperlink ref="I65" r:id="rId62"/>
-    <hyperlink ref="I67" r:id="rId63"/>
-    <hyperlink ref="I68" r:id="rId64"/>
-    <hyperlink ref="I69" r:id="rId65"/>
-    <hyperlink ref="I70" r:id="rId66"/>
-    <hyperlink ref="I71" r:id="rId67"/>
-    <hyperlink ref="I72" r:id="rId68"/>
-    <hyperlink ref="I73" r:id="rId69"/>
-    <hyperlink ref="I74" r:id="rId70"/>
-    <hyperlink ref="I75" r:id="rId71"/>
-    <hyperlink ref="I76" r:id="rId72"/>
-    <hyperlink ref="I78" r:id="rId73"/>
-    <hyperlink ref="I79" r:id="rId74"/>
-    <hyperlink ref="I80" r:id="rId75"/>
-    <hyperlink ref="I81" r:id="rId76"/>
-    <hyperlink ref="I82" r:id="rId77"/>
-    <hyperlink ref="I83" r:id="rId78"/>
+    <hyperlink ref="J3" r:id="rId1"/>
+    <hyperlink ref="J4" r:id="rId2"/>
+    <hyperlink ref="K4" r:id="rId3"/>
+    <hyperlink ref="J5" r:id="rId4"/>
+    <hyperlink ref="J6" r:id="rId5"/>
+    <hyperlink ref="J7" r:id="rId6"/>
+    <hyperlink ref="J8" r:id="rId7"/>
+    <hyperlink ref="J9" r:id="rId8"/>
+    <hyperlink ref="J10" r:id="rId9"/>
+    <hyperlink ref="J11" r:id="rId10"/>
+    <hyperlink ref="J12" r:id="rId11"/>
+    <hyperlink ref="J13" r:id="rId12"/>
+    <hyperlink ref="J14" r:id="rId13"/>
+    <hyperlink ref="J15" r:id="rId14"/>
+    <hyperlink ref="J16" r:id="rId15"/>
+    <hyperlink ref="J18" r:id="rId16"/>
+    <hyperlink ref="J19" r:id="rId17"/>
+    <hyperlink ref="J20" r:id="rId18"/>
+    <hyperlink ref="J21" r:id="rId19"/>
+    <hyperlink ref="J22" r:id="rId20"/>
+    <hyperlink ref="J23" r:id="rId21"/>
+    <hyperlink ref="J24" r:id="rId22"/>
+    <hyperlink ref="J26" r:id="rId23"/>
+    <hyperlink ref="J27" r:id="rId24"/>
+    <hyperlink ref="J28" r:id="rId25"/>
+    <hyperlink ref="J29" r:id="rId26"/>
+    <hyperlink ref="J30" r:id="rId27"/>
+    <hyperlink ref="J31" r:id="rId28"/>
+    <hyperlink ref="J32" r:id="rId29"/>
+    <hyperlink ref="J33" r:id="rId30"/>
+    <hyperlink ref="J34" r:id="rId31"/>
+    <hyperlink ref="J35" r:id="rId32"/>
+    <hyperlink ref="J36" r:id="rId33"/>
+    <hyperlink ref="J37" r:id="rId34"/>
+    <hyperlink ref="J38" r:id="rId35"/>
+    <hyperlink ref="J39" r:id="rId36"/>
+    <hyperlink ref="J40" r:id="rId37"/>
+    <hyperlink ref="J41" r:id="rId38"/>
+    <hyperlink ref="J42" r:id="rId39"/>
+    <hyperlink ref="J43" r:id="rId40"/>
+    <hyperlink ref="J44" r:id="rId41"/>
+    <hyperlink ref="J45" r:id="rId42"/>
+    <hyperlink ref="J46" r:id="rId43"/>
+    <hyperlink ref="J47" r:id="rId44"/>
+    <hyperlink ref="J48" r:id="rId45"/>
+    <hyperlink ref="J49" r:id="rId46"/>
+    <hyperlink ref="J50" r:id="rId47"/>
+    <hyperlink ref="J51" r:id="rId48"/>
+    <hyperlink ref="J52" r:id="rId49"/>
+    <hyperlink ref="J53" r:id="rId50"/>
+    <hyperlink ref="J54" r:id="rId51"/>
+    <hyperlink ref="J55" r:id="rId52"/>
+    <hyperlink ref="J56" r:id="rId53"/>
+    <hyperlink ref="J57" r:id="rId54"/>
+    <hyperlink ref="J58" r:id="rId55"/>
+    <hyperlink ref="J59" r:id="rId56"/>
+    <hyperlink ref="J60" r:id="rId57"/>
+    <hyperlink ref="J61" r:id="rId58"/>
+    <hyperlink ref="J62" r:id="rId59"/>
+    <hyperlink ref="J63" r:id="rId60"/>
+    <hyperlink ref="J64" r:id="rId61"/>
+    <hyperlink ref="J65" r:id="rId62"/>
+    <hyperlink ref="J67" r:id="rId63"/>
+    <hyperlink ref="J68" r:id="rId64"/>
+    <hyperlink ref="J69" r:id="rId65"/>
+    <hyperlink ref="J70" r:id="rId66"/>
+    <hyperlink ref="J71" r:id="rId67"/>
+    <hyperlink ref="J72" r:id="rId68"/>
+    <hyperlink ref="J73" r:id="rId69"/>
+    <hyperlink ref="J74" r:id="rId70"/>
+    <hyperlink ref="J75" r:id="rId71"/>
+    <hyperlink ref="J76" r:id="rId72"/>
+    <hyperlink ref="J78" r:id="rId73"/>
+    <hyperlink ref="J79" r:id="rId74"/>
+    <hyperlink ref="J80" r:id="rId75"/>
+    <hyperlink ref="J81" r:id="rId76"/>
+    <hyperlink ref="J82" r:id="rId77"/>
+    <hyperlink ref="J83" r:id="rId78"/>
     <hyperlink ref="B7" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ระบบลางาน ออนไลน์ 2025.xlsx
+++ b/ระบบลางาน ออนไลน์ 2025.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1738" uniqueCount="880">
   <si>
     <t>Setting (Folder)</t>
   </si>
@@ -1274,18 +1274,6 @@
   </si>
   <si>
     <t>USER-079</t>
-  </si>
-  <si>
-    <t>wisanu.mon.sa2534@gmail.com</t>
-  </si>
-  <si>
-    <t>0526</t>
-  </si>
-  <si>
-    <t>วิษณุ สมงาม</t>
-  </si>
-  <si>
-    <t>https://lh3.googleusercontent.com/d/1aphEZLPvnLj5MsT7fVByA_AwTcfFxGlC</t>
   </si>
   <si>
     <t>USER-080</t>
@@ -3231,7 +3219,7 @@
         <v>17</v>
       </c>
       <c r="E1" s="38" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>18</v>
@@ -3417,7 +3405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" ht="12.75">
       <c r="A7" s="20" t="s">
         <v>55</v>
       </c>
@@ -3453,7 +3441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" ht="12.75">
       <c r="A8" s="20" t="s">
         <v>61</v>
       </c>
@@ -3489,7 +3477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" ht="12.75">
       <c r="A9" s="20" t="s">
         <v>67</v>
       </c>
@@ -5971,48 +5959,30 @@
       <c r="A80" s="20" t="s">
         <v>415</v>
       </c>
-      <c r="B80" s="18" t="s">
-        <v>416</v>
-      </c>
-      <c r="C80" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="D80" s="18" t="s">
-        <v>418</v>
-      </c>
+      <c r="B80" s="18"/>
+      <c r="C80" s="18"/>
+      <c r="D80" s="18"/>
       <c r="E80" s="40"/>
-      <c r="F80" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="G80" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="H80" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="I80" s="14">
-        <v>46148</v>
-      </c>
-      <c r="J80" s="15" t="s">
-        <v>419</v>
-      </c>
+      <c r="F80" s="20"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="15"/>
       <c r="K80" s="16"/>
-      <c r="L80" s="17" t="b">
-        <v>1</v>
-      </c>
+      <c r="L80" s="17"/>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" s="20" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D81" s="18" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="E81" s="40">
         <v>295</v>
@@ -6030,7 +6000,7 @@
         <v>46179</v>
       </c>
       <c r="J81" s="15" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="K81" s="16"/>
       <c r="L81" s="17" t="b">
@@ -6039,16 +6009,16 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82" s="20" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B82" s="18" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D82" s="18" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="E82" s="40">
         <v>296</v>
@@ -6066,7 +6036,7 @@
         <v>46192</v>
       </c>
       <c r="J82" s="15" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="K82" s="16"/>
       <c r="L82" s="17" t="b">
@@ -6075,16 +6045,16 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" s="20" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C83" s="18" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D83" s="18" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E83" s="40">
         <v>298</v>
@@ -6102,7 +6072,7 @@
         <v>46192</v>
       </c>
       <c r="J83" s="15" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="K83" s="16"/>
       <c r="L83" s="17" t="b">
@@ -6185,11 +6155,10 @@
     <hyperlink ref="J76" r:id="rId72"/>
     <hyperlink ref="J78" r:id="rId73"/>
     <hyperlink ref="J79" r:id="rId74"/>
-    <hyperlink ref="J80" r:id="rId75"/>
-    <hyperlink ref="J81" r:id="rId76"/>
-    <hyperlink ref="J82" r:id="rId77"/>
-    <hyperlink ref="J83" r:id="rId78"/>
-    <hyperlink ref="B7" r:id="rId79"/>
+    <hyperlink ref="J81" r:id="rId75"/>
+    <hyperlink ref="J82" r:id="rId76"/>
+    <hyperlink ref="J83" r:id="rId77"/>
+    <hyperlink ref="B7" r:id="rId78"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6209,10 +6178,10 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="22" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>32</v>
@@ -6229,10 +6198,10 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="23" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C2" s="25" t="b">
         <v>1</v>
@@ -6249,10 +6218,10 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="24" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C3" s="26" t="b">
         <v>1</v>
@@ -6269,10 +6238,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="24" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C4" s="26" t="b">
         <v>1</v>
@@ -6289,10 +6258,10 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="24" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="C5" s="26" t="b">
         <v>1</v>
@@ -6309,10 +6278,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="24" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C6" s="26" t="b">
         <v>1</v>
@@ -6329,10 +6298,10 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="24" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C7" s="25" t="b">
         <v>1</v>
@@ -6349,10 +6318,10 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="24" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C8" s="26" t="b">
         <v>1</v>
@@ -6369,10 +6338,10 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="24" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C9" s="26" t="b">
         <v>1</v>
@@ -6389,10 +6358,10 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="24" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C10" s="25" t="b">
         <v>1</v>
@@ -6409,10 +6378,10 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="24" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C11" s="25" t="b">
         <v>1</v>
@@ -6429,10 +6398,10 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="24" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C12" s="25" t="b">
         <v>1</v>
@@ -6449,10 +6418,10 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="24" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B13" s="24" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C13" s="25" t="b">
         <v>1</v>
@@ -6469,10 +6438,10 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="24" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C14" s="25" t="b">
         <v>1</v>
@@ -6489,10 +6458,10 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="24" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C15" s="25" t="b">
         <v>1</v>
@@ -6525,10 +6494,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6536,7 +6505,7 @@
         <v>38</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6544,7 +6513,7 @@
         <v>52</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6552,7 +6521,7 @@
         <v>175</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6560,7 +6529,7 @@
         <v>196</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6568,7 +6537,7 @@
         <v>168</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6576,7 +6545,7 @@
         <v>254</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6584,7 +6553,7 @@
         <v>30</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -6592,7 +6561,7 @@
         <v>295</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -6600,7 +6569,7 @@
         <v>247</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
     </row>
   </sheetData>
@@ -6618,10 +6587,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6629,7 +6598,7 @@
         <v>39</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6637,7 +6606,7 @@
         <v>31</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6645,7 +6614,7 @@
         <v>248</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -6653,7 +6622,7 @@
         <v>169</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -6661,7 +6630,7 @@
         <v>296</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -6669,7 +6638,7 @@
         <v>53</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -6691,27 +6660,27 @@
   <sheetData>
     <row r="1" spans="1:4" ht="12.75">
       <c r="A1" s="7" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1">
       <c r="A2" s="28" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="B2" s="28" t="s">
         <v>34</v>
       </c>
       <c r="C2" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D2" s="29">
         <v>15</v>
@@ -6719,13 +6688,13 @@
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1">
       <c r="A3" s="28" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="B3" s="28" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D3" s="29">
         <v>30</v>
@@ -6733,13 +6702,13 @@
     </row>
     <row r="4" spans="1:4" ht="15.75" customHeight="1">
       <c r="A4" s="28" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B4" s="28" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D4" s="29">
         <v>3</v>
@@ -6747,13 +6716,13 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1">
       <c r="A5" s="28" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="B5" s="28" t="s">
         <v>34</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D5" s="29">
         <v>15</v>
@@ -6761,13 +6730,13 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1">
       <c r="A6" s="28" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="B6" s="28" t="s">
         <v>43</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D6" s="29">
         <v>7</v>
@@ -6775,13 +6744,13 @@
     </row>
     <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="28" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="B7" s="28" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D7" s="29">
         <v>30</v>
@@ -6789,13 +6758,13 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="28" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D8" s="29">
         <v>3</v>
@@ -6803,13 +6772,13 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="28" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="B9" s="28" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D9" s="29">
         <v>15</v>
@@ -6817,13 +6786,13 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="28" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="B10" s="28" t="s">
         <v>55</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D10" s="29">
         <v>15</v>
@@ -6831,13 +6800,13 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="28" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="B11" s="28" t="s">
         <v>55</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D11" s="29">
         <v>30</v>
@@ -6845,13 +6814,13 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" s="28" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B12" s="28" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D12" s="29">
         <v>3</v>
@@ -6859,13 +6828,13 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" s="28" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="B13" s="28" t="s">
         <v>55</v>
       </c>
       <c r="C13" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D13" s="29">
         <v>15</v>
@@ -6873,13 +6842,13 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" s="28" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B14" s="28" t="s">
         <v>61</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D14" s="29">
         <v>15</v>
@@ -6887,13 +6856,13 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" s="28" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B15" s="28" t="s">
         <v>61</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D15" s="29">
         <v>30</v>
@@ -6901,13 +6870,13 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" s="28" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="B16" s="28" t="s">
         <v>61</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D16" s="29">
         <v>3</v>
@@ -6915,13 +6884,13 @@
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1">
       <c r="A17" s="28" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="B17" s="28" t="s">
         <v>61</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D17" s="29">
         <v>15</v>
@@ -6929,13 +6898,13 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1">
       <c r="A18" s="28" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D18" s="29">
         <v>15</v>
@@ -6943,13 +6912,13 @@
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1">
       <c r="A19" s="28" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B19" s="28" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D19" s="29">
         <v>30</v>
@@ -6957,13 +6926,13 @@
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1">
       <c r="A20" s="28" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="B20" s="28" t="s">
         <v>67</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D20" s="29">
         <v>3</v>
@@ -6971,13 +6940,13 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1">
       <c r="A21" s="28" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="B21" s="28" t="s">
         <v>67</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D21" s="29">
         <v>15</v>
@@ -6985,13 +6954,13 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1">
       <c r="A22" s="28" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B22" s="28" t="s">
         <v>72</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D22" s="29">
         <v>15</v>
@@ -6999,13 +6968,13 @@
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1">
       <c r="A23" s="28" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B23" s="28" t="s">
         <v>72</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D23" s="29">
         <v>30</v>
@@ -7013,13 +6982,13 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1">
       <c r="A24" s="28" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B24" s="28" t="s">
         <v>72</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D24" s="29">
         <v>3</v>
@@ -7027,13 +6996,13 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1">
       <c r="A25" s="28" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B25" s="28" t="s">
         <v>72</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D25" s="29">
         <v>15</v>
@@ -7041,13 +7010,13 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1">
       <c r="A26" s="28" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B26" s="28" t="s">
         <v>77</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D26" s="29">
         <v>15</v>
@@ -7055,13 +7024,13 @@
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1">
       <c r="A27" s="28" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B27" s="28" t="s">
         <v>77</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D27" s="29">
         <v>30</v>
@@ -7069,13 +7038,13 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1">
       <c r="A28" s="28" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B28" s="28" t="s">
         <v>77</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D28" s="29">
         <v>3</v>
@@ -7083,13 +7052,13 @@
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1">
       <c r="A29" s="28" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B29" s="28" t="s">
         <v>77</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D29" s="29">
         <v>15</v>
@@ -7097,13 +7066,13 @@
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1">
       <c r="A30" s="28" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B30" s="28" t="s">
         <v>82</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D30" s="29">
         <v>14</v>
@@ -7111,13 +7080,13 @@
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1">
       <c r="A31" s="28" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B31" s="28" t="s">
         <v>82</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D31" s="29">
         <v>30</v>
@@ -7125,13 +7094,13 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1">
       <c r="A32" s="28" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B32" s="28" t="s">
         <v>82</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D32" s="29">
         <v>3</v>
@@ -7139,13 +7108,13 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" s="28" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B33" s="28" t="s">
         <v>82</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D33" s="29">
         <v>15</v>
@@ -7153,13 +7122,13 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" s="28" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B34" s="28" t="s">
         <v>87</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D34" s="29">
         <v>14</v>
@@ -7167,13 +7136,13 @@
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1">
       <c r="A35" s="28" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B35" s="28" t="s">
         <v>87</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D35" s="29">
         <v>30</v>
@@ -7181,13 +7150,13 @@
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1">
       <c r="A36" s="28" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B36" s="28" t="s">
         <v>87</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D36" s="29">
         <v>3</v>
@@ -7195,13 +7164,13 @@
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1">
       <c r="A37" s="28" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B37" s="28" t="s">
         <v>87</v>
       </c>
       <c r="C37" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D37" s="29">
         <v>15</v>
@@ -7209,13 +7178,13 @@
     </row>
     <row r="38" spans="1:4" ht="15">
       <c r="A38" s="28" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B38" s="28" t="s">
         <v>92</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D38" s="29">
         <v>12.5</v>
@@ -7223,13 +7192,13 @@
     </row>
     <row r="39" spans="1:4" ht="15">
       <c r="A39" s="28" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B39" s="28" t="s">
         <v>92</v>
       </c>
       <c r="C39" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D39" s="29">
         <v>30</v>
@@ -7237,13 +7206,13 @@
     </row>
     <row r="40" spans="1:4" ht="15">
       <c r="A40" s="28" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="B40" s="28" t="s">
         <v>92</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D40" s="29">
         <v>3</v>
@@ -7251,13 +7220,13 @@
     </row>
     <row r="41" spans="1:4" ht="15">
       <c r="A41" s="28" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B41" s="28" t="s">
         <v>92</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D41" s="29">
         <v>15</v>
@@ -7265,13 +7234,13 @@
     </row>
     <row r="42" spans="1:4" ht="15">
       <c r="A42" s="28" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="B42" s="28" t="s">
         <v>97</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D42" s="29">
         <v>13.5</v>
@@ -7279,13 +7248,13 @@
     </row>
     <row r="43" spans="1:4" ht="15">
       <c r="A43" s="28" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B43" s="28" t="s">
         <v>97</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D43" s="29">
         <v>30</v>
@@ -7293,13 +7262,13 @@
     </row>
     <row r="44" spans="1:4" ht="15">
       <c r="A44" s="28" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B44" s="28" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D44" s="29">
         <v>3</v>
@@ -7307,13 +7276,13 @@
     </row>
     <row r="45" spans="1:4" ht="15">
       <c r="A45" s="28" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="B45" s="28" t="s">
         <v>97</v>
       </c>
       <c r="C45" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D45" s="29">
         <v>15</v>
@@ -7321,13 +7290,13 @@
     </row>
     <row r="46" spans="1:4" ht="15">
       <c r="A46" s="28" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="B46" s="28" t="s">
         <v>102</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D46" s="29">
         <v>11</v>
@@ -7335,13 +7304,13 @@
     </row>
     <row r="47" spans="1:4" ht="15">
       <c r="A47" s="28" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B47" s="28" t="s">
         <v>102</v>
       </c>
       <c r="C47" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D47" s="29">
         <v>30</v>
@@ -7349,13 +7318,13 @@
     </row>
     <row r="48" spans="1:4" ht="15">
       <c r="A48" s="28" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="B48" s="28" t="s">
         <v>102</v>
       </c>
       <c r="C48" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D48" s="29">
         <v>3</v>
@@ -7363,13 +7332,13 @@
     </row>
     <row r="49" spans="1:4" ht="15">
       <c r="A49" s="28" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B49" s="28" t="s">
         <v>102</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D49" s="29">
         <v>15</v>
@@ -7377,13 +7346,13 @@
     </row>
     <row r="50" spans="1:4" ht="15">
       <c r="A50" s="28" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="B50" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C50" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D50" s="29">
         <v>11.5</v>
@@ -7391,13 +7360,13 @@
     </row>
     <row r="51" spans="1:4" ht="15">
       <c r="A51" s="28" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B51" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D51" s="29">
         <v>30</v>
@@ -7405,13 +7374,13 @@
     </row>
     <row r="52" spans="1:4" ht="15">
       <c r="A52" s="28" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="B52" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C52" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D52" s="29">
         <v>3</v>
@@ -7419,13 +7388,13 @@
     </row>
     <row r="53" spans="1:4" ht="15">
       <c r="A53" s="28" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="B53" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C53" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D53" s="29">
         <v>15</v>
@@ -7433,13 +7402,13 @@
     </row>
     <row r="54" spans="1:4" ht="15">
       <c r="A54" s="28" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B54" s="28" t="s">
         <v>108</v>
       </c>
       <c r="C54" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D54" s="29">
         <v>13</v>
@@ -7447,13 +7416,13 @@
     </row>
     <row r="55" spans="1:4" ht="15">
       <c r="A55" s="28" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B55" s="28" t="s">
         <v>108</v>
       </c>
       <c r="C55" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D55" s="29">
         <v>30</v>
@@ -7461,13 +7430,13 @@
     </row>
     <row r="56" spans="1:4" ht="15">
       <c r="A56" s="28" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B56" s="28" t="s">
         <v>108</v>
       </c>
       <c r="C56" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D56" s="29">
         <v>3</v>
@@ -7475,13 +7444,13 @@
     </row>
     <row r="57" spans="1:4" ht="15">
       <c r="A57" s="28" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="B57" s="28" t="s">
         <v>108</v>
       </c>
       <c r="C57" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D57" s="29">
         <v>15</v>
@@ -7489,13 +7458,13 @@
     </row>
     <row r="58" spans="1:4" ht="15">
       <c r="A58" s="28" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B58" s="28" t="s">
         <v>113</v>
       </c>
       <c r="C58" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D58" s="29">
         <v>13</v>
@@ -7503,13 +7472,13 @@
     </row>
     <row r="59" spans="1:4" ht="15">
       <c r="A59" s="28" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="B59" s="28" t="s">
         <v>113</v>
       </c>
       <c r="C59" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D59" s="29">
         <v>30</v>
@@ -7517,13 +7486,13 @@
     </row>
     <row r="60" spans="1:4" ht="15">
       <c r="A60" s="28" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B60" s="28" t="s">
         <v>113</v>
       </c>
       <c r="C60" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D60" s="29">
         <v>3</v>
@@ -7531,13 +7500,13 @@
     </row>
     <row r="61" spans="1:4" ht="15">
       <c r="A61" s="28" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B61" s="28" t="s">
         <v>113</v>
       </c>
       <c r="C61" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D61" s="29">
         <v>15</v>
@@ -7545,13 +7514,13 @@
     </row>
     <row r="62" spans="1:4" ht="15">
       <c r="A62" s="28" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B62" s="28" t="s">
         <v>118</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D62" s="29">
         <v>12.5</v>
@@ -7559,13 +7528,13 @@
     </row>
     <row r="63" spans="1:4" ht="15">
       <c r="A63" s="28" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B63" s="28" t="s">
         <v>118</v>
       </c>
       <c r="C63" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D63" s="29">
         <v>30</v>
@@ -7573,13 +7542,13 @@
     </row>
     <row r="64" spans="1:4" ht="15">
       <c r="A64" s="28" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="B64" s="28" t="s">
         <v>118</v>
       </c>
       <c r="C64" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D64" s="29">
         <v>3</v>
@@ -7587,13 +7556,13 @@
     </row>
     <row r="65" spans="1:4" ht="15">
       <c r="A65" s="28" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="B65" s="28" t="s">
         <v>118</v>
       </c>
       <c r="C65" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D65" s="29">
         <v>30</v>
@@ -7601,13 +7570,13 @@
     </row>
     <row r="66" spans="1:4" ht="15">
       <c r="A66" s="28" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="B66" s="28" t="s">
         <v>123</v>
       </c>
       <c r="C66" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D66" s="29">
         <v>9</v>
@@ -7615,13 +7584,13 @@
     </row>
     <row r="67" spans="1:4" ht="15">
       <c r="A67" s="28" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B67" s="28" t="s">
         <v>123</v>
       </c>
       <c r="C67" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D67" s="29">
         <v>30</v>
@@ -7629,13 +7598,13 @@
     </row>
     <row r="68" spans="1:4" ht="15">
       <c r="A68" s="28" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B68" s="28" t="s">
         <v>123</v>
       </c>
       <c r="C68" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D68" s="29">
         <v>3</v>
@@ -7643,13 +7612,13 @@
     </row>
     <row r="69" spans="1:4" ht="15">
       <c r="A69" s="28" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B69" s="28" t="s">
         <v>123</v>
       </c>
       <c r="C69" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D69" s="29">
         <v>15</v>
@@ -7657,13 +7626,13 @@
     </row>
     <row r="70" spans="1:4" ht="15">
       <c r="A70" s="28" t="s">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B70" s="28" t="s">
         <v>128</v>
       </c>
       <c r="C70" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D70" s="29">
         <v>15</v>
@@ -7671,13 +7640,13 @@
     </row>
     <row r="71" spans="1:4" ht="15">
       <c r="A71" s="28" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B71" s="28" t="s">
         <v>128</v>
       </c>
       <c r="C71" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D71" s="29">
         <v>30</v>
@@ -7685,13 +7654,13 @@
     </row>
     <row r="72" spans="1:4" ht="15">
       <c r="A72" s="28" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B72" s="28" t="s">
         <v>128</v>
       </c>
       <c r="C72" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D72" s="29">
         <v>3</v>
@@ -7699,13 +7668,13 @@
     </row>
     <row r="73" spans="1:4" ht="15">
       <c r="A73" s="28" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B73" s="28" t="s">
         <v>128</v>
       </c>
       <c r="C73" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D73" s="29">
         <v>15</v>
@@ -7713,13 +7682,13 @@
     </row>
     <row r="74" spans="1:4" ht="15">
       <c r="A74" s="28" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B74" s="28" t="s">
         <v>133</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D74" s="29">
         <v>10</v>
@@ -7727,13 +7696,13 @@
     </row>
     <row r="75" spans="1:4" ht="15">
       <c r="A75" s="28" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B75" s="28" t="s">
         <v>133</v>
       </c>
       <c r="C75" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D75" s="29">
         <v>30</v>
@@ -7741,13 +7710,13 @@
     </row>
     <row r="76" spans="1:4" ht="15">
       <c r="A76" s="28" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B76" s="28" t="s">
         <v>133</v>
       </c>
       <c r="C76" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D76" s="29">
         <v>3</v>
@@ -7755,13 +7724,13 @@
     </row>
     <row r="77" spans="1:4" ht="15">
       <c r="A77" s="28" t="s">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B77" s="28" t="s">
         <v>133</v>
       </c>
       <c r="C77" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D77" s="29">
         <v>15</v>
@@ -7769,13 +7738,13 @@
     </row>
     <row r="78" spans="1:4" ht="15">
       <c r="A78" s="28" t="s">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="B78" s="28" t="s">
         <v>138</v>
       </c>
       <c r="C78" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D78" s="29">
         <v>8</v>
@@ -7783,13 +7752,13 @@
     </row>
     <row r="79" spans="1:4" ht="15">
       <c r="A79" s="28" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="B79" s="28" t="s">
         <v>138</v>
       </c>
       <c r="C79" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D79" s="29">
         <v>30</v>
@@ -7797,13 +7766,13 @@
     </row>
     <row r="80" spans="1:4" ht="15">
       <c r="A80" s="28" t="s">
-        <v>570</v>
+        <v>566</v>
       </c>
       <c r="B80" s="28" t="s">
         <v>138</v>
       </c>
       <c r="C80" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D80" s="29">
         <v>3</v>
@@ -7811,13 +7780,13 @@
     </row>
     <row r="81" spans="1:4" ht="15">
       <c r="A81" s="28" t="s">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="B81" s="28" t="s">
         <v>138</v>
       </c>
       <c r="C81" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D81" s="29">
         <v>15</v>
@@ -7825,13 +7794,13 @@
     </row>
     <row r="82" spans="1:4" ht="15">
       <c r="A82" s="28" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="B82" s="28" t="s">
         <v>143</v>
       </c>
       <c r="C82" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D82" s="29">
         <v>8</v>
@@ -7839,13 +7808,13 @@
     </row>
     <row r="83" spans="1:4" ht="15">
       <c r="A83" s="28" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B83" s="28" t="s">
         <v>143</v>
       </c>
       <c r="C83" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D83" s="29">
         <v>30</v>
@@ -7853,13 +7822,13 @@
     </row>
     <row r="84" spans="1:4" ht="15">
       <c r="A84" s="28" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B84" s="28" t="s">
         <v>143</v>
       </c>
       <c r="C84" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D84" s="29">
         <v>3</v>
@@ -7867,13 +7836,13 @@
     </row>
     <row r="85" spans="1:4" ht="15">
       <c r="A85" s="28" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B85" s="28" t="s">
         <v>143</v>
       </c>
       <c r="C85" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D85" s="29">
         <v>15</v>
@@ -7881,13 +7850,13 @@
     </row>
     <row r="86" spans="1:4" ht="15">
       <c r="A86" s="28" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B86" s="28" t="s">
         <v>144</v>
       </c>
       <c r="C86" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D86" s="29">
         <v>6</v>
@@ -7895,13 +7864,13 @@
     </row>
     <row r="87" spans="1:4" ht="15">
       <c r="A87" s="28" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B87" s="28" t="s">
         <v>144</v>
       </c>
       <c r="C87" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D87" s="29">
         <v>30</v>
@@ -7909,13 +7878,13 @@
     </row>
     <row r="88" spans="1:4" ht="15">
       <c r="A88" s="28" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B88" s="28" t="s">
         <v>144</v>
       </c>
       <c r="C88" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D88" s="29">
         <v>3</v>
@@ -7923,13 +7892,13 @@
     </row>
     <row r="89" spans="1:4" ht="15">
       <c r="A89" s="28" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="B89" s="28" t="s">
         <v>144</v>
       </c>
       <c r="C89" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D89" s="29">
         <v>15</v>
@@ -7937,13 +7906,13 @@
     </row>
     <row r="90" spans="1:4" ht="15">
       <c r="A90" s="28" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="B90" s="28" t="s">
         <v>149</v>
       </c>
       <c r="C90" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D90" s="29">
         <v>6</v>
@@ -7951,13 +7920,13 @@
     </row>
     <row r="91" spans="1:4" ht="15">
       <c r="A91" s="28" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="B91" s="28" t="s">
         <v>149</v>
       </c>
       <c r="C91" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D91" s="29">
         <v>30</v>
@@ -7965,13 +7934,13 @@
     </row>
     <row r="92" spans="1:4" ht="15">
       <c r="A92" s="28" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B92" s="28" t="s">
         <v>149</v>
       </c>
       <c r="C92" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D92" s="29">
         <v>3</v>
@@ -7979,13 +7948,13 @@
     </row>
     <row r="93" spans="1:4" ht="15">
       <c r="A93" s="28" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B93" s="28" t="s">
         <v>149</v>
       </c>
       <c r="C93" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D93" s="29">
         <v>15</v>
@@ -7993,13 +7962,13 @@
     </row>
     <row r="94" spans="1:4" ht="15">
       <c r="A94" s="28" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="B94" s="28" t="s">
         <v>154</v>
       </c>
       <c r="C94" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D94" s="29">
         <v>7</v>
@@ -8007,13 +7976,13 @@
     </row>
     <row r="95" spans="1:4" ht="15">
       <c r="A95" s="28" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B95" s="28" t="s">
         <v>154</v>
       </c>
       <c r="C95" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D95" s="29">
         <v>30</v>
@@ -8021,13 +7990,13 @@
     </row>
     <row r="96" spans="1:4" ht="15">
       <c r="A96" s="28" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="B96" s="28" t="s">
         <v>154</v>
       </c>
       <c r="C96" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D96" s="29">
         <v>3</v>
@@ -8035,13 +8004,13 @@
     </row>
     <row r="97" spans="1:4" ht="15">
       <c r="A97" s="28" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B97" s="28" t="s">
         <v>154</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D97" s="29">
         <v>15</v>
@@ -8049,13 +8018,13 @@
     </row>
     <row r="98" spans="1:4" ht="15">
       <c r="A98" s="28" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B98" s="28" t="s">
         <v>159</v>
       </c>
       <c r="C98" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D98" s="29">
         <v>6</v>
@@ -8063,13 +8032,13 @@
     </row>
     <row r="99" spans="1:4" ht="15">
       <c r="A99" s="28" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B99" s="28" t="s">
         <v>159</v>
       </c>
       <c r="C99" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D99" s="29">
         <v>30</v>
@@ -8077,13 +8046,13 @@
     </row>
     <row r="100" spans="1:4" ht="15">
       <c r="A100" s="28" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B100" s="28" t="s">
         <v>159</v>
       </c>
       <c r="C100" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D100" s="29">
         <v>3</v>
@@ -8091,13 +8060,13 @@
     </row>
     <row r="101" spans="1:4" ht="15">
       <c r="A101" s="28" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B101" s="28" t="s">
         <v>159</v>
       </c>
       <c r="C101" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D101" s="29">
         <v>15</v>
@@ -8105,13 +8074,13 @@
     </row>
     <row r="102" spans="1:4" ht="15">
       <c r="A102" s="28" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B102" s="28" t="s">
         <v>182</v>
       </c>
       <c r="C102" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D102" s="29">
         <v>15</v>
@@ -8119,13 +8088,13 @@
     </row>
     <row r="103" spans="1:4" ht="15">
       <c r="A103" s="28" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="B103" s="28" t="s">
         <v>182</v>
       </c>
       <c r="C103" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D103" s="29">
         <v>30</v>
@@ -8133,13 +8102,13 @@
     </row>
     <row r="104" spans="1:4" ht="15">
       <c r="A104" s="28" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B104" s="28" t="s">
         <v>182</v>
       </c>
       <c r="C104" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D104" s="29">
         <v>17</v>
@@ -8147,13 +8116,13 @@
     </row>
     <row r="105" spans="1:4" ht="15">
       <c r="A105" s="28" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B105" s="28" t="s">
         <v>182</v>
       </c>
       <c r="C105" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D105" s="29">
         <v>3</v>
@@ -8161,13 +8130,13 @@
     </row>
     <row r="106" spans="1:4" ht="15">
       <c r="A106" s="28" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B106" s="28" t="s">
         <v>164</v>
       </c>
       <c r="C106" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D106" s="29">
         <v>15</v>
@@ -8175,13 +8144,13 @@
     </row>
     <row r="107" spans="1:4" ht="15">
       <c r="A107" s="28" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
       <c r="B107" s="28" t="s">
         <v>164</v>
       </c>
       <c r="C107" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D107" s="29">
         <v>30</v>
@@ -8189,13 +8158,13 @@
     </row>
     <row r="108" spans="1:4" ht="15">
       <c r="A108" s="28" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B108" s="28" t="s">
         <v>164</v>
       </c>
       <c r="C108" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D108" s="29">
         <v>3</v>
@@ -8203,13 +8172,13 @@
     </row>
     <row r="109" spans="1:4" ht="15">
       <c r="A109" s="28" t="s">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B109" s="28" t="s">
         <v>164</v>
       </c>
       <c r="C109" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D109" s="29">
         <v>15</v>
@@ -8217,13 +8186,13 @@
     </row>
     <row r="110" spans="1:4" ht="15">
       <c r="A110" s="28" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="B110" s="28" t="s">
         <v>171</v>
       </c>
       <c r="C110" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D110" s="29">
         <v>15</v>
@@ -8231,13 +8200,13 @@
     </row>
     <row r="111" spans="1:4" ht="15">
       <c r="A111" s="28" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B111" s="28" t="s">
         <v>171</v>
       </c>
       <c r="C111" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D111" s="29">
         <v>30</v>
@@ -8245,13 +8214,13 @@
     </row>
     <row r="112" spans="1:4" ht="15">
       <c r="A112" s="28" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
       <c r="B112" s="28" t="s">
         <v>171</v>
       </c>
       <c r="C112" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D112" s="29">
         <v>3</v>
@@ -8259,13 +8228,13 @@
     </row>
     <row r="113" spans="1:4" ht="15">
       <c r="A113" s="28" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B113" s="28" t="s">
         <v>171</v>
       </c>
       <c r="C113" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D113" s="29">
         <v>15</v>
@@ -8273,13 +8242,13 @@
     </row>
     <row r="114" spans="1:4" ht="15">
       <c r="A114" s="28" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B114" s="28" t="s">
         <v>177</v>
       </c>
       <c r="C114" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D114" s="29">
         <v>15</v>
@@ -8287,13 +8256,13 @@
     </row>
     <row r="115" spans="1:4" ht="15">
       <c r="A115" s="28" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B115" s="28" t="s">
         <v>177</v>
       </c>
       <c r="C115" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D115" s="29">
         <v>30</v>
@@ -8301,13 +8270,13 @@
     </row>
     <row r="116" spans="1:4" ht="15">
       <c r="A116" s="28" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="B116" s="28" t="s">
         <v>177</v>
       </c>
       <c r="C116" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D116" s="29">
         <v>3</v>
@@ -8315,13 +8284,13 @@
     </row>
     <row r="117" spans="1:4" ht="15">
       <c r="A117" s="28" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B117" s="28" t="s">
         <v>177</v>
       </c>
       <c r="C117" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D117" s="29">
         <v>15</v>
@@ -8329,13 +8298,13 @@
     </row>
     <row r="118" spans="1:4" ht="15">
       <c r="A118" s="28" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="B118" s="28" t="s">
         <v>187</v>
       </c>
       <c r="C118" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D118" s="29">
         <v>15</v>
@@ -8343,13 +8312,13 @@
     </row>
     <row r="119" spans="1:4" ht="15">
       <c r="A119" s="28" t="s">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B119" s="28" t="s">
         <v>187</v>
       </c>
       <c r="C119" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D119" s="29">
         <v>30</v>
@@ -8357,13 +8326,13 @@
     </row>
     <row r="120" spans="1:4" ht="15">
       <c r="A120" s="28" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B120" s="28" t="s">
         <v>187</v>
       </c>
       <c r="C120" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D120" s="29">
         <v>3</v>
@@ -8371,13 +8340,13 @@
     </row>
     <row r="121" spans="1:4" ht="15">
       <c r="A121" s="28" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B121" s="28" t="s">
         <v>187</v>
       </c>
       <c r="C121" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D121" s="29">
         <v>15</v>
@@ -8385,13 +8354,13 @@
     </row>
     <row r="122" spans="1:4" ht="15">
       <c r="A122" s="28" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B122" s="28" t="s">
         <v>192</v>
       </c>
       <c r="C122" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D122" s="29">
         <v>15</v>
@@ -8399,13 +8368,13 @@
     </row>
     <row r="123" spans="1:4" ht="15">
       <c r="A123" s="28" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B123" s="28" t="s">
         <v>192</v>
       </c>
       <c r="C123" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D123" s="29">
         <v>30</v>
@@ -8413,13 +8382,13 @@
     </row>
     <row r="124" spans="1:4" ht="15">
       <c r="A124" s="28" t="s">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="B124" s="28" t="s">
         <v>192</v>
       </c>
       <c r="C124" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D124" s="29">
         <v>3</v>
@@ -8427,13 +8396,13 @@
     </row>
     <row r="125" spans="1:4" ht="15">
       <c r="A125" s="28" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B125" s="28" t="s">
         <v>192</v>
       </c>
       <c r="C125" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D125" s="29">
         <v>15</v>
@@ -8441,13 +8410,13 @@
     </row>
     <row r="126" spans="1:4" ht="15">
       <c r="A126" s="28" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B126" s="28" t="s">
         <v>198</v>
       </c>
       <c r="C126" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D126" s="29">
         <v>15</v>
@@ -8455,13 +8424,13 @@
     </row>
     <row r="127" spans="1:4" ht="15">
       <c r="A127" s="28" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B127" s="28" t="s">
         <v>198</v>
       </c>
       <c r="C127" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D127" s="29">
         <v>30</v>
@@ -8469,13 +8438,13 @@
     </row>
     <row r="128" spans="1:4" ht="15">
       <c r="A128" s="28" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
       <c r="B128" s="28" t="s">
         <v>198</v>
       </c>
       <c r="C128" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D128" s="29">
         <v>3</v>
@@ -8483,13 +8452,13 @@
     </row>
     <row r="129" spans="1:4" ht="15">
       <c r="A129" s="28" t="s">
-        <v>619</v>
+        <v>615</v>
       </c>
       <c r="B129" s="28" t="s">
         <v>198</v>
       </c>
       <c r="C129" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D129" s="29">
         <v>15</v>
@@ -8497,13 +8466,13 @@
     </row>
     <row r="130" spans="1:4" ht="15">
       <c r="A130" s="28" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B130" s="28" t="s">
         <v>203</v>
       </c>
       <c r="C130" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D130" s="29">
         <v>15</v>
@@ -8511,13 +8480,13 @@
     </row>
     <row r="131" spans="1:4" ht="15">
       <c r="A131" s="28" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="B131" s="28" t="s">
         <v>203</v>
       </c>
       <c r="C131" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D131" s="29">
         <v>30</v>
@@ -8525,13 +8494,13 @@
     </row>
     <row r="132" spans="1:4" ht="15">
       <c r="A132" s="28" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="B132" s="28" t="s">
         <v>203</v>
       </c>
       <c r="C132" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D132" s="29">
         <v>3</v>
@@ -8539,13 +8508,13 @@
     </row>
     <row r="133" spans="1:4" ht="15">
       <c r="A133" s="28" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B133" s="28" t="s">
         <v>203</v>
       </c>
       <c r="C133" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D133" s="29">
         <v>15</v>
@@ -8553,13 +8522,13 @@
     </row>
     <row r="134" spans="1:4" ht="15">
       <c r="A134" s="28" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B134" s="28" t="s">
         <v>208</v>
       </c>
       <c r="C134" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D134" s="29">
         <v>15</v>
@@ -8567,13 +8536,13 @@
     </row>
     <row r="135" spans="1:4" ht="15">
       <c r="A135" s="28" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B135" s="28" t="s">
         <v>208</v>
       </c>
       <c r="C135" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D135" s="29">
         <v>30</v>
@@ -8581,13 +8550,13 @@
     </row>
     <row r="136" spans="1:4" ht="15">
       <c r="A136" s="28" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B136" s="28" t="s">
         <v>208</v>
       </c>
       <c r="C136" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D136" s="29">
         <v>3</v>
@@ -8595,13 +8564,13 @@
     </row>
     <row r="137" spans="1:4" ht="15">
       <c r="A137" s="28" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B137" s="28" t="s">
         <v>208</v>
       </c>
       <c r="C137" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D137" s="29">
         <v>15</v>
@@ -8609,13 +8578,13 @@
     </row>
     <row r="138" spans="1:4" ht="15">
       <c r="A138" s="28" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B138" s="28" t="s">
         <v>213</v>
       </c>
       <c r="C138" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D138" s="29">
         <v>15</v>
@@ -8623,13 +8592,13 @@
     </row>
     <row r="139" spans="1:4" ht="15">
       <c r="A139" s="28" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B139" s="28" t="s">
         <v>213</v>
       </c>
       <c r="C139" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D139" s="29">
         <v>30</v>
@@ -8637,13 +8606,13 @@
     </row>
     <row r="140" spans="1:4" ht="15">
       <c r="A140" s="28" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B140" s="28" t="s">
         <v>213</v>
       </c>
       <c r="C140" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D140" s="29">
         <v>3</v>
@@ -8651,13 +8620,13 @@
     </row>
     <row r="141" spans="1:4" ht="15">
       <c r="A141" s="28" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="B141" s="28" t="s">
         <v>213</v>
       </c>
       <c r="C141" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D141" s="29">
         <v>15</v>
@@ -8665,13 +8634,13 @@
     </row>
     <row r="142" spans="1:4" ht="15">
       <c r="A142" s="28" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B142" s="28" t="s">
         <v>218</v>
       </c>
       <c r="C142" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D142" s="29">
         <v>15</v>
@@ -8679,13 +8648,13 @@
     </row>
     <row r="143" spans="1:4" ht="15">
       <c r="A143" s="28" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B143" s="28" t="s">
         <v>218</v>
       </c>
       <c r="C143" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D143" s="29">
         <v>30</v>
@@ -8693,13 +8662,13 @@
     </row>
     <row r="144" spans="1:4" ht="15">
       <c r="A144" s="28" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B144" s="28" t="s">
         <v>218</v>
       </c>
       <c r="C144" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D144" s="29">
         <v>3</v>
@@ -8707,13 +8676,13 @@
     </row>
     <row r="145" spans="1:4" ht="15">
       <c r="A145" s="28" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B145" s="28" t="s">
         <v>218</v>
       </c>
       <c r="C145" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D145" s="29">
         <v>15</v>
@@ -8721,13 +8690,13 @@
     </row>
     <row r="146" spans="1:4" ht="15">
       <c r="A146" s="28" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B146" s="28" t="s">
         <v>223</v>
       </c>
       <c r="C146" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D146" s="29">
         <v>15</v>
@@ -8735,13 +8704,13 @@
     </row>
     <row r="147" spans="1:4" ht="15">
       <c r="A147" s="28" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B147" s="28" t="s">
         <v>223</v>
       </c>
       <c r="C147" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D147" s="29">
         <v>30</v>
@@ -8749,13 +8718,13 @@
     </row>
     <row r="148" spans="1:4" ht="15">
       <c r="A148" s="28" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B148" s="28" t="s">
         <v>223</v>
       </c>
       <c r="C148" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D148" s="29">
         <v>3</v>
@@ -8763,13 +8732,13 @@
     </row>
     <row r="149" spans="1:4" ht="15">
       <c r="A149" s="28" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B149" s="28" t="s">
         <v>223</v>
       </c>
       <c r="C149" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D149" s="29">
         <v>15</v>
@@ -8777,13 +8746,13 @@
     </row>
     <row r="150" spans="1:4" ht="15">
       <c r="A150" s="28" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B150" s="28" t="s">
         <v>228</v>
       </c>
       <c r="C150" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D150" s="29">
         <v>15</v>
@@ -8791,13 +8760,13 @@
     </row>
     <row r="151" spans="1:4" ht="15">
       <c r="A151" s="28" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B151" s="28" t="s">
         <v>228</v>
       </c>
       <c r="C151" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D151" s="29">
         <v>30</v>
@@ -8805,13 +8774,13 @@
     </row>
     <row r="152" spans="1:4" ht="15">
       <c r="A152" s="28" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B152" s="28" t="s">
         <v>228</v>
       </c>
       <c r="C152" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D152" s="29">
         <v>3</v>
@@ -8819,13 +8788,13 @@
     </row>
     <row r="153" spans="1:4" ht="15">
       <c r="A153" s="28" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="B153" s="28" t="s">
         <v>228</v>
       </c>
       <c r="C153" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D153" s="29">
         <v>15</v>
@@ -8833,13 +8802,13 @@
     </row>
     <row r="154" spans="1:4" ht="15">
       <c r="A154" s="28" t="s">
-        <v>644</v>
+        <v>640</v>
       </c>
       <c r="B154" s="28" t="s">
         <v>233</v>
       </c>
       <c r="C154" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D154" s="29">
         <v>15</v>
@@ -8847,13 +8816,13 @@
     </row>
     <row r="155" spans="1:4" ht="15">
       <c r="A155" s="28" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="B155" s="28" t="s">
         <v>233</v>
       </c>
       <c r="C155" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D155" s="29">
         <v>30</v>
@@ -8861,13 +8830,13 @@
     </row>
     <row r="156" spans="1:4" ht="15">
       <c r="A156" s="28" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="B156" s="28" t="s">
         <v>233</v>
       </c>
       <c r="C156" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D156" s="29">
         <v>3</v>
@@ -8875,13 +8844,13 @@
     </row>
     <row r="157" spans="1:4" ht="15">
       <c r="A157" s="28" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B157" s="28" t="s">
         <v>233</v>
       </c>
       <c r="C157" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D157" s="29">
         <v>15</v>
@@ -8889,13 +8858,13 @@
     </row>
     <row r="158" spans="1:4" ht="15">
       <c r="A158" s="28" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="B158" s="28" t="s">
         <v>238</v>
       </c>
       <c r="C158" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D158" s="29">
         <v>15</v>
@@ -8903,13 +8872,13 @@
     </row>
     <row r="159" spans="1:4" ht="15">
       <c r="A159" s="28" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="B159" s="28" t="s">
         <v>238</v>
       </c>
       <c r="C159" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D159" s="29">
         <v>30</v>
@@ -8917,13 +8886,13 @@
     </row>
     <row r="160" spans="1:4" ht="15">
       <c r="A160" s="28" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="B160" s="28" t="s">
         <v>238</v>
       </c>
       <c r="C160" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D160" s="29">
         <v>3</v>
@@ -8931,13 +8900,13 @@
     </row>
     <row r="161" spans="1:4" ht="15">
       <c r="A161" s="28" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B161" s="28" t="s">
         <v>238</v>
       </c>
       <c r="C161" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D161" s="29">
         <v>15</v>
@@ -8945,13 +8914,13 @@
     </row>
     <row r="162" spans="1:4" ht="15">
       <c r="A162" s="28" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B162" s="28" t="s">
         <v>243</v>
       </c>
       <c r="C162" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D162" s="29">
         <v>15</v>
@@ -8959,13 +8928,13 @@
     </row>
     <row r="163" spans="1:4" ht="15">
       <c r="A163" s="28" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B163" s="28" t="s">
         <v>243</v>
       </c>
       <c r="C163" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D163" s="29">
         <v>30</v>
@@ -8973,13 +8942,13 @@
     </row>
     <row r="164" spans="1:4" ht="15">
       <c r="A164" s="28" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B164" s="28" t="s">
         <v>243</v>
       </c>
       <c r="C164" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D164" s="29">
         <v>3</v>
@@ -8987,13 +8956,13 @@
     </row>
     <row r="165" spans="1:4" ht="15">
       <c r="A165" s="28" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="B165" s="28" t="s">
         <v>243</v>
       </c>
       <c r="C165" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D165" s="29">
         <v>15</v>
@@ -9001,13 +8970,13 @@
     </row>
     <row r="166" spans="1:4" ht="15">
       <c r="A166" s="28" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="B166" s="28" t="s">
         <v>250</v>
       </c>
       <c r="C166" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D166" s="29">
         <v>14</v>
@@ -9015,13 +8984,13 @@
     </row>
     <row r="167" spans="1:4" ht="15">
       <c r="A167" s="28" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B167" s="28" t="s">
         <v>250</v>
       </c>
       <c r="C167" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D167" s="29">
         <v>30</v>
@@ -9029,13 +8998,13 @@
     </row>
     <row r="168" spans="1:4" ht="15">
       <c r="A168" s="28" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="B168" s="28" t="s">
         <v>250</v>
       </c>
       <c r="C168" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D168" s="29">
         <v>3</v>
@@ -9043,13 +9012,13 @@
     </row>
     <row r="169" spans="1:4" ht="15">
       <c r="A169" s="28" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="B169" s="28" t="s">
         <v>250</v>
       </c>
       <c r="C169" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D169" s="29">
         <v>15</v>
@@ -9057,13 +9026,13 @@
     </row>
     <row r="170" spans="1:4" ht="15">
       <c r="A170" s="28" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B170" s="28" t="s">
         <v>256</v>
       </c>
       <c r="C170" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D170" s="29">
         <v>14</v>
@@ -9071,13 +9040,13 @@
     </row>
     <row r="171" spans="1:4" ht="15">
       <c r="A171" s="28" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B171" s="28" t="s">
         <v>256</v>
       </c>
       <c r="C171" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D171" s="29">
         <v>30</v>
@@ -9085,13 +9054,13 @@
     </row>
     <row r="172" spans="1:4" ht="15">
       <c r="A172" s="28" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="B172" s="28" t="s">
         <v>256</v>
       </c>
       <c r="C172" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D172" s="29">
         <v>3</v>
@@ -9099,13 +9068,13 @@
     </row>
     <row r="173" spans="1:4" ht="15">
       <c r="A173" s="28" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B173" s="28" t="s">
         <v>256</v>
       </c>
       <c r="C173" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D173" s="29">
         <v>15</v>
@@ -9113,13 +9082,13 @@
     </row>
     <row r="174" spans="1:4" ht="15">
       <c r="A174" s="28" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B174" s="28" t="s">
         <v>261</v>
       </c>
       <c r="C174" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D174" s="29">
         <v>14</v>
@@ -9127,13 +9096,13 @@
     </row>
     <row r="175" spans="1:4" ht="15">
       <c r="A175" s="28" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B175" s="28" t="s">
         <v>261</v>
       </c>
       <c r="C175" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D175" s="29">
         <v>30</v>
@@ -9141,13 +9110,13 @@
     </row>
     <row r="176" spans="1:4" ht="15">
       <c r="A176" s="28" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="B176" s="28" t="s">
         <v>261</v>
       </c>
       <c r="C176" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D176" s="29">
         <v>3</v>
@@ -9155,13 +9124,13 @@
     </row>
     <row r="177" spans="1:4" ht="15">
       <c r="A177" s="28" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B177" s="28" t="s">
         <v>261</v>
       </c>
       <c r="C177" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D177" s="29">
         <v>15</v>
@@ -9169,13 +9138,13 @@
     </row>
     <row r="178" spans="1:4" ht="15">
       <c r="A178" s="28" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B178" s="28" t="s">
         <v>266</v>
       </c>
       <c r="C178" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D178" s="29">
         <v>13</v>
@@ -9183,13 +9152,13 @@
     </row>
     <row r="179" spans="1:4" ht="15">
       <c r="A179" s="28" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B179" s="28" t="s">
         <v>266</v>
       </c>
       <c r="C179" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D179" s="29">
         <v>30</v>
@@ -9197,13 +9166,13 @@
     </row>
     <row r="180" spans="1:4" ht="15">
       <c r="A180" s="28" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B180" s="28" t="s">
         <v>266</v>
       </c>
       <c r="C180" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D180" s="29">
         <v>3</v>
@@ -9211,13 +9180,13 @@
     </row>
     <row r="181" spans="1:4" ht="15">
       <c r="A181" s="28" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B181" s="28" t="s">
         <v>266</v>
       </c>
       <c r="C181" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D181" s="29">
         <v>15</v>
@@ -9225,13 +9194,13 @@
     </row>
     <row r="182" spans="1:4" ht="15">
       <c r="A182" s="28" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="B182" s="28" t="s">
         <v>271</v>
       </c>
       <c r="C182" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D182" s="29">
         <v>13.5</v>
@@ -9239,13 +9208,13 @@
     </row>
     <row r="183" spans="1:4" ht="15">
       <c r="A183" s="28" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="B183" s="28" t="s">
         <v>271</v>
       </c>
       <c r="C183" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D183" s="29">
         <v>30</v>
@@ -9253,13 +9222,13 @@
     </row>
     <row r="184" spans="1:4" ht="15">
       <c r="A184" s="28" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="B184" s="28" t="s">
         <v>271</v>
       </c>
       <c r="C184" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D184" s="29">
         <v>3</v>
@@ -9267,13 +9236,13 @@
     </row>
     <row r="185" spans="1:4" ht="15">
       <c r="A185" s="28" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B185" s="28" t="s">
         <v>271</v>
       </c>
       <c r="C185" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D185" s="29">
         <v>15</v>
@@ -9281,13 +9250,13 @@
     </row>
     <row r="186" spans="1:4" ht="15">
       <c r="A186" s="28" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="B186" s="28" t="s">
         <v>276</v>
       </c>
       <c r="C186" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D186" s="29">
         <v>13</v>
@@ -9295,13 +9264,13 @@
     </row>
     <row r="187" spans="1:4" ht="15">
       <c r="A187" s="28" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B187" s="28" t="s">
         <v>276</v>
       </c>
       <c r="C187" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D187" s="29">
         <v>30</v>
@@ -9309,13 +9278,13 @@
     </row>
     <row r="188" spans="1:4" ht="15">
       <c r="A188" s="28" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="B188" s="28" t="s">
         <v>276</v>
       </c>
       <c r="C188" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D188" s="29">
         <v>3</v>
@@ -9323,13 +9292,13 @@
     </row>
     <row r="189" spans="1:4" ht="15">
       <c r="A189" s="28" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B189" s="28" t="s">
         <v>276</v>
       </c>
       <c r="C189" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D189" s="29">
         <v>15</v>
@@ -9337,13 +9306,13 @@
     </row>
     <row r="190" spans="1:4" ht="15">
       <c r="A190" s="28" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B190" s="28" t="s">
         <v>281</v>
       </c>
       <c r="C190" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D190" s="29">
         <v>14</v>
@@ -9351,13 +9320,13 @@
     </row>
     <row r="191" spans="1:4" ht="15">
       <c r="A191" s="28" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="B191" s="28" t="s">
         <v>281</v>
       </c>
       <c r="C191" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D191" s="29">
         <v>30</v>
@@ -9365,13 +9334,13 @@
     </row>
     <row r="192" spans="1:4" ht="15">
       <c r="A192" s="28" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B192" s="28" t="s">
         <v>281</v>
       </c>
       <c r="C192" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D192" s="29">
         <v>3</v>
@@ -9379,13 +9348,13 @@
     </row>
     <row r="193" spans="1:4" ht="15">
       <c r="A193" s="28" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B193" s="28" t="s">
         <v>281</v>
       </c>
       <c r="C193" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D193" s="29">
         <v>15</v>
@@ -9393,13 +9362,13 @@
     </row>
     <row r="194" spans="1:4" ht="15">
       <c r="A194" s="28" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B194" s="28" t="s">
         <v>286</v>
       </c>
       <c r="C194" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D194" s="29">
         <v>12</v>
@@ -9407,13 +9376,13 @@
     </row>
     <row r="195" spans="1:4" ht="15">
       <c r="A195" s="28" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="B195" s="28" t="s">
         <v>286</v>
       </c>
       <c r="C195" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D195" s="29">
         <v>30</v>
@@ -9421,13 +9390,13 @@
     </row>
     <row r="196" spans="1:4" ht="15">
       <c r="A196" s="28" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="B196" s="28" t="s">
         <v>286</v>
       </c>
       <c r="C196" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D196" s="29">
         <v>3</v>
@@ -9435,13 +9404,13 @@
     </row>
     <row r="197" spans="1:4" ht="15">
       <c r="A197" s="28" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="B197" s="28" t="s">
         <v>286</v>
       </c>
       <c r="C197" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D197" s="29">
         <v>15</v>
@@ -9449,13 +9418,13 @@
     </row>
     <row r="198" spans="1:4" ht="15">
       <c r="A198" s="28" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="B198" s="28" t="s">
         <v>291</v>
       </c>
       <c r="C198" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D198" s="29">
         <v>12</v>
@@ -9463,13 +9432,13 @@
     </row>
     <row r="199" spans="1:4" ht="15">
       <c r="A199" s="28" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="B199" s="28" t="s">
         <v>291</v>
       </c>
       <c r="C199" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D199" s="29">
         <v>30</v>
@@ -9477,13 +9446,13 @@
     </row>
     <row r="200" spans="1:4" ht="15">
       <c r="A200" s="28" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B200" s="28" t="s">
         <v>291</v>
       </c>
       <c r="C200" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D200" s="29">
         <v>3</v>
@@ -9491,13 +9460,13 @@
     </row>
     <row r="201" spans="1:4" ht="15">
       <c r="A201" s="28" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B201" s="28" t="s">
         <v>291</v>
       </c>
       <c r="C201" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D201" s="29">
         <v>15</v>
@@ -9505,13 +9474,13 @@
     </row>
     <row r="202" spans="1:4" ht="15">
       <c r="A202" s="28" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B202" s="28" t="s">
         <v>298</v>
       </c>
       <c r="C202" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D202" s="29">
         <v>12</v>
@@ -9519,13 +9488,13 @@
     </row>
     <row r="203" spans="1:4" ht="15">
       <c r="A203" s="28" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="B203" s="28" t="s">
         <v>298</v>
       </c>
       <c r="C203" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D203" s="29">
         <v>30</v>
@@ -9533,13 +9502,13 @@
     </row>
     <row r="204" spans="1:4" ht="15">
       <c r="A204" s="28" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B204" s="28" t="s">
         <v>298</v>
       </c>
       <c r="C204" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D204" s="29">
         <v>3</v>
@@ -9547,13 +9516,13 @@
     </row>
     <row r="205" spans="1:4" ht="15">
       <c r="A205" s="28" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="B205" s="28" t="s">
         <v>298</v>
       </c>
       <c r="C205" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D205" s="29">
         <v>15</v>
@@ -9561,13 +9530,13 @@
     </row>
     <row r="206" spans="1:4" ht="15">
       <c r="A206" s="28" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B206" s="28" t="s">
         <v>303</v>
       </c>
       <c r="C206" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D206" s="29">
         <v>11</v>
@@ -9575,13 +9544,13 @@
     </row>
     <row r="207" spans="1:4" ht="15">
       <c r="A207" s="28" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="B207" s="28" t="s">
         <v>303</v>
       </c>
       <c r="C207" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D207" s="29">
         <v>30</v>
@@ -9589,13 +9558,13 @@
     </row>
     <row r="208" spans="1:4" ht="15">
       <c r="A208" s="28" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B208" s="28" t="s">
         <v>303</v>
       </c>
       <c r="C208" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D208" s="29">
         <v>3</v>
@@ -9603,13 +9572,13 @@
     </row>
     <row r="209" spans="1:4" ht="15">
       <c r="A209" s="28" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="B209" s="28" t="s">
         <v>303</v>
       </c>
       <c r="C209" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D209" s="29">
         <v>15</v>
@@ -9617,13 +9586,13 @@
     </row>
     <row r="210" spans="1:4" ht="15">
       <c r="A210" s="28" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B210" s="28" t="s">
         <v>308</v>
       </c>
       <c r="C210" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D210" s="29">
         <v>10</v>
@@ -9631,13 +9600,13 @@
     </row>
     <row r="211" spans="1:4" ht="15">
       <c r="A211" s="28" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="B211" s="28" t="s">
         <v>308</v>
       </c>
       <c r="C211" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D211" s="29">
         <v>30</v>
@@ -9645,13 +9614,13 @@
     </row>
     <row r="212" spans="1:4" ht="15">
       <c r="A212" s="28" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B212" s="28" t="s">
         <v>308</v>
       </c>
       <c r="C212" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D212" s="29">
         <v>3</v>
@@ -9659,13 +9628,13 @@
     </row>
     <row r="213" spans="1:4" ht="15">
       <c r="A213" s="28" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B213" s="28" t="s">
         <v>308</v>
       </c>
       <c r="C213" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D213" s="29">
         <v>15</v>
@@ -9673,13 +9642,13 @@
     </row>
     <row r="214" spans="1:4" ht="15">
       <c r="A214" s="28" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B214" s="28" t="s">
         <v>313</v>
       </c>
       <c r="C214" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D214" s="29">
         <v>10.5</v>
@@ -9687,13 +9656,13 @@
     </row>
     <row r="215" spans="1:4" ht="15">
       <c r="A215" s="28" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="B215" s="28" t="s">
         <v>313</v>
       </c>
       <c r="C215" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D215" s="29">
         <v>30</v>
@@ -9701,13 +9670,13 @@
     </row>
     <row r="216" spans="1:4" ht="15">
       <c r="A216" s="28" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B216" s="28" t="s">
         <v>313</v>
       </c>
       <c r="C216" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D216" s="29">
         <v>3</v>
@@ -9715,13 +9684,13 @@
     </row>
     <row r="217" spans="1:4" ht="15">
       <c r="A217" s="28" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="B217" s="28" t="s">
         <v>313</v>
       </c>
       <c r="C217" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D217" s="29">
         <v>15</v>
@@ -9729,13 +9698,13 @@
     </row>
     <row r="218" spans="1:4" ht="15">
       <c r="A218" s="28" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B218" s="28" t="s">
         <v>318</v>
       </c>
       <c r="C218" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D218" s="29">
         <v>9</v>
@@ -9743,13 +9712,13 @@
     </row>
     <row r="219" spans="1:4" ht="15">
       <c r="A219" s="28" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="B219" s="28" t="s">
         <v>318</v>
       </c>
       <c r="C219" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D219" s="29">
         <v>30</v>
@@ -9757,13 +9726,13 @@
     </row>
     <row r="220" spans="1:4" ht="15">
       <c r="A220" s="28" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B220" s="28" t="s">
         <v>318</v>
       </c>
       <c r="C220" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D220" s="29">
         <v>3</v>
@@ -9771,13 +9740,13 @@
     </row>
     <row r="221" spans="1:4" ht="15">
       <c r="A221" s="28" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="B221" s="28" t="s">
         <v>318</v>
       </c>
       <c r="C221" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D221" s="29">
         <v>15</v>
@@ -9785,13 +9754,13 @@
     </row>
     <row r="222" spans="1:4" ht="15">
       <c r="A222" s="28" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B222" s="28" t="s">
         <v>323</v>
       </c>
       <c r="C222" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D222" s="29">
         <v>9</v>
@@ -9799,13 +9768,13 @@
     </row>
     <row r="223" spans="1:4" ht="15">
       <c r="A223" s="28" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="B223" s="28" t="s">
         <v>323</v>
       </c>
       <c r="C223" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D223" s="29">
         <v>30</v>
@@ -9813,13 +9782,13 @@
     </row>
     <row r="224" spans="1:4" ht="15">
       <c r="A224" s="28" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B224" s="28" t="s">
         <v>323</v>
       </c>
       <c r="C224" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D224" s="29">
         <v>3</v>
@@ -9827,13 +9796,13 @@
     </row>
     <row r="225" spans="1:4" ht="15">
       <c r="A225" s="28" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B225" s="28" t="s">
         <v>323</v>
       </c>
       <c r="C225" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D225" s="29">
         <v>15</v>
@@ -9841,13 +9810,13 @@
     </row>
     <row r="226" spans="1:4" ht="15">
       <c r="A226" s="28" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B226" s="28" t="s">
         <v>328</v>
       </c>
       <c r="C226" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D226" s="29">
         <v>9</v>
@@ -9855,13 +9824,13 @@
     </row>
     <row r="227" spans="1:4" ht="15">
       <c r="A227" s="28" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="B227" s="28" t="s">
         <v>328</v>
       </c>
       <c r="C227" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D227" s="29">
         <v>30</v>
@@ -9869,13 +9838,13 @@
     </row>
     <row r="228" spans="1:4" ht="15">
       <c r="A228" s="28" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B228" s="28" t="s">
         <v>328</v>
       </c>
       <c r="C228" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D228" s="29">
         <v>3</v>
@@ -9883,13 +9852,13 @@
     </row>
     <row r="229" spans="1:4" ht="15">
       <c r="A229" s="28" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="B229" s="28" t="s">
         <v>328</v>
       </c>
       <c r="C229" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D229" s="29">
         <v>15</v>
@@ -9897,13 +9866,13 @@
     </row>
     <row r="230" spans="1:4" ht="15">
       <c r="A230" s="28" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B230" s="28" t="s">
         <v>333</v>
       </c>
       <c r="C230" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D230" s="29">
         <v>8</v>
@@ -9911,13 +9880,13 @@
     </row>
     <row r="231" spans="1:4" ht="15">
       <c r="A231" s="28" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="B231" s="28" t="s">
         <v>333</v>
       </c>
       <c r="C231" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D231" s="29">
         <v>30</v>
@@ -9925,13 +9894,13 @@
     </row>
     <row r="232" spans="1:4" ht="15">
       <c r="A232" s="28" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B232" s="28" t="s">
         <v>333</v>
       </c>
       <c r="C232" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D232" s="29">
         <v>3</v>
@@ -9939,13 +9908,13 @@
     </row>
     <row r="233" spans="1:4" ht="15">
       <c r="A233" s="28" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="B233" s="28" t="s">
         <v>333</v>
       </c>
       <c r="C233" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D233" s="29">
         <v>20</v>
@@ -9953,13 +9922,13 @@
     </row>
     <row r="234" spans="1:4" ht="15">
       <c r="A234" s="28" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B234" s="28" t="s">
         <v>338</v>
       </c>
       <c r="C234" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D234" s="29">
         <v>8</v>
@@ -9967,13 +9936,13 @@
     </row>
     <row r="235" spans="1:4" ht="15">
       <c r="A235" s="28" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="B235" s="28" t="s">
         <v>338</v>
       </c>
       <c r="C235" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D235" s="29">
         <v>30</v>
@@ -9981,13 +9950,13 @@
     </row>
     <row r="236" spans="1:4" ht="15">
       <c r="A236" s="28" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B236" s="28" t="s">
         <v>338</v>
       </c>
       <c r="C236" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D236" s="29">
         <v>3</v>
@@ -9995,13 +9964,13 @@
     </row>
     <row r="237" spans="1:4" ht="15">
       <c r="A237" s="28" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B237" s="28" t="s">
         <v>338</v>
       </c>
       <c r="C237" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D237" s="29">
         <v>15</v>
@@ -10009,13 +9978,13 @@
     </row>
     <row r="238" spans="1:4" ht="15">
       <c r="A238" s="28" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B238" s="28" t="s">
         <v>343</v>
       </c>
       <c r="C238" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D238" s="29">
         <v>8</v>
@@ -10023,13 +9992,13 @@
     </row>
     <row r="239" spans="1:4" ht="15">
       <c r="A239" s="28" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="B239" s="28" t="s">
         <v>343</v>
       </c>
       <c r="C239" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D239" s="29">
         <v>30</v>
@@ -10037,13 +10006,13 @@
     </row>
     <row r="240" spans="1:4" ht="15">
       <c r="A240" s="28" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B240" s="28" t="s">
         <v>343</v>
       </c>
       <c r="C240" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D240" s="29">
         <v>3</v>
@@ -10051,13 +10020,13 @@
     </row>
     <row r="241" spans="1:4" ht="15">
       <c r="A241" s="28" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="B241" s="28" t="s">
         <v>343</v>
       </c>
       <c r="C241" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D241" s="29">
         <v>15</v>
@@ -10065,13 +10034,13 @@
     </row>
     <row r="242" spans="1:4" ht="15">
       <c r="A242" s="28" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B242" s="28" t="s">
         <v>348</v>
       </c>
       <c r="C242" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D242" s="29">
         <v>10</v>
@@ -10079,13 +10048,13 @@
     </row>
     <row r="243" spans="1:4" ht="15">
       <c r="A243" s="28" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B243" s="28" t="s">
         <v>348</v>
       </c>
       <c r="C243" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D243" s="29">
         <v>30</v>
@@ -10093,13 +10062,13 @@
     </row>
     <row r="244" spans="1:4" ht="15">
       <c r="A244" s="28" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="B244" s="28" t="s">
         <v>348</v>
       </c>
       <c r="C244" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D244" s="29">
         <v>3</v>
@@ -10107,13 +10076,13 @@
     </row>
     <row r="245" spans="1:4" ht="15">
       <c r="A245" s="28" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="B245" s="28" t="s">
         <v>348</v>
       </c>
       <c r="C245" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D245" s="29">
         <v>15</v>
@@ -10121,13 +10090,13 @@
     </row>
     <row r="246" spans="1:4" ht="15">
       <c r="A246" s="28" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B246" s="28" t="s">
         <v>353</v>
       </c>
       <c r="C246" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D246" s="29">
         <v>7</v>
@@ -10135,13 +10104,13 @@
     </row>
     <row r="247" spans="1:4" ht="15">
       <c r="A247" s="28" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B247" s="28" t="s">
         <v>353</v>
       </c>
       <c r="C247" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D247" s="29">
         <v>30</v>
@@ -10149,13 +10118,13 @@
     </row>
     <row r="248" spans="1:4" ht="15">
       <c r="A248" s="28" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B248" s="28" t="s">
         <v>353</v>
       </c>
       <c r="C248" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D248" s="29">
         <v>3</v>
@@ -10163,13 +10132,13 @@
     </row>
     <row r="249" spans="1:4" ht="15">
       <c r="A249" s="28" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B249" s="28" t="s">
         <v>353</v>
       </c>
       <c r="C249" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D249" s="29">
         <v>15</v>
@@ -10177,13 +10146,13 @@
     </row>
     <row r="250" spans="1:4" ht="15">
       <c r="A250" s="28" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B250" s="28" t="s">
         <v>354</v>
       </c>
       <c r="C250" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D250" s="29">
         <v>6</v>
@@ -10191,13 +10160,13 @@
     </row>
     <row r="251" spans="1:4" ht="15">
       <c r="A251" s="28" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="B251" s="28" t="s">
         <v>354</v>
       </c>
       <c r="C251" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D251" s="29">
         <v>30</v>
@@ -10205,13 +10174,13 @@
     </row>
     <row r="252" spans="1:4" ht="15">
       <c r="A252" s="28" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="B252" s="28" t="s">
         <v>354</v>
       </c>
       <c r="C252" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D252" s="29">
         <v>3</v>
@@ -10219,13 +10188,13 @@
     </row>
     <row r="253" spans="1:4" ht="15">
       <c r="A253" s="28" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="B253" s="28" t="s">
         <v>354</v>
       </c>
       <c r="C253" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D253" s="29">
         <v>15</v>
@@ -10233,13 +10202,13 @@
     </row>
     <row r="254" spans="1:4" ht="15">
       <c r="A254" s="28" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B254" s="28" t="s">
         <v>359</v>
       </c>
       <c r="C254" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D254" s="29">
         <v>8</v>
@@ -10247,13 +10216,13 @@
     </row>
     <row r="255" spans="1:4" ht="15">
       <c r="A255" s="28" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="B255" s="28" t="s">
         <v>359</v>
       </c>
       <c r="C255" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D255" s="29">
         <v>30</v>
@@ -10261,13 +10230,13 @@
     </row>
     <row r="256" spans="1:4" ht="15">
       <c r="A256" s="28" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="B256" s="28" t="s">
         <v>359</v>
       </c>
       <c r="C256" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D256" s="29">
         <v>3</v>
@@ -10275,13 +10244,13 @@
     </row>
     <row r="257" spans="1:4" ht="15">
       <c r="A257" s="28" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="B257" s="28" t="s">
         <v>359</v>
       </c>
       <c r="C257" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D257" s="29">
         <v>15</v>
@@ -10289,13 +10258,13 @@
     </row>
     <row r="258" spans="1:4" ht="15">
       <c r="A258" s="28" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B258" s="28" t="s">
         <v>364</v>
       </c>
       <c r="C258" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D258" s="29">
         <v>6</v>
@@ -10303,13 +10272,13 @@
     </row>
     <row r="259" spans="1:4" ht="15">
       <c r="A259" s="28" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="B259" s="28" t="s">
         <v>364</v>
       </c>
       <c r="C259" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D259" s="29">
         <v>30</v>
@@ -10317,13 +10286,13 @@
     </row>
     <row r="260" spans="1:4" ht="15">
       <c r="A260" s="28" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B260" s="28" t="s">
         <v>364</v>
       </c>
       <c r="C260" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D260" s="29">
         <v>3</v>
@@ -10331,13 +10300,13 @@
     </row>
     <row r="261" spans="1:4" ht="15">
       <c r="A261" s="28" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="B261" s="28" t="s">
         <v>364</v>
       </c>
       <c r="C261" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D261" s="29">
         <v>15</v>
@@ -10345,13 +10314,13 @@
     </row>
     <row r="262" spans="1:4" ht="15">
       <c r="A262" s="30" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B262" s="28" t="s">
         <v>369</v>
       </c>
       <c r="C262" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D262" s="29">
         <v>5.5</v>
@@ -10359,13 +10328,13 @@
     </row>
     <row r="263" spans="1:4" ht="15">
       <c r="A263" s="28" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B263" s="28" t="s">
         <v>369</v>
       </c>
       <c r="C263" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D263" s="29">
         <v>30</v>
@@ -10373,13 +10342,13 @@
     </row>
     <row r="264" spans="1:4" ht="15">
       <c r="A264" s="28" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="B264" s="28" t="s">
         <v>369</v>
       </c>
       <c r="C264" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D264" s="29">
         <v>3</v>
@@ -10387,13 +10356,13 @@
     </row>
     <row r="265" spans="1:4" ht="15">
       <c r="A265" s="28" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B265" s="28" t="s">
         <v>369</v>
       </c>
       <c r="C265" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D265" s="29">
         <v>15</v>
@@ -10401,13 +10370,13 @@
     </row>
     <row r="266" spans="1:4" ht="15">
       <c r="A266" s="30" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B266" s="28" t="s">
         <v>379</v>
       </c>
       <c r="C266" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D266" s="29">
         <v>2.5</v>
@@ -10415,13 +10384,13 @@
     </row>
     <row r="267" spans="1:4" ht="15">
       <c r="A267" s="28" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B267" s="28" t="s">
         <v>379</v>
       </c>
       <c r="C267" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D267" s="29">
         <v>30</v>
@@ -10429,13 +10398,13 @@
     </row>
     <row r="268" spans="1:4" ht="15">
       <c r="A268" s="28" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B268" s="28" t="s">
         <v>379</v>
       </c>
       <c r="C268" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D268" s="29">
         <v>3</v>
@@ -10443,13 +10412,13 @@
     </row>
     <row r="269" spans="1:4" ht="15">
       <c r="A269" s="28" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="B269" s="28" t="s">
         <v>379</v>
       </c>
       <c r="C269" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D269" s="29">
         <v>15</v>
@@ -10457,13 +10426,13 @@
     </row>
     <row r="270" spans="1:4" ht="15">
       <c r="A270" s="30" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B270" s="28" t="s">
         <v>384</v>
       </c>
       <c r="C270" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D270" s="29">
         <v>2</v>
@@ -10471,13 +10440,13 @@
     </row>
     <row r="271" spans="1:4" ht="15">
       <c r="A271" s="28" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="B271" s="28" t="s">
         <v>384</v>
       </c>
       <c r="C271" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D271" s="29">
         <v>30</v>
@@ -10485,13 +10454,13 @@
     </row>
     <row r="272" spans="1:4" ht="15">
       <c r="A272" s="28" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B272" s="28" t="s">
         <v>384</v>
       </c>
       <c r="C272" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D272" s="29">
         <v>3</v>
@@ -10499,13 +10468,13 @@
     </row>
     <row r="273" spans="1:4" ht="15">
       <c r="A273" s="28" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B273" s="28" t="s">
         <v>384</v>
       </c>
       <c r="C273" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D273" s="29">
         <v>15</v>
@@ -10513,13 +10482,13 @@
     </row>
     <row r="274" spans="1:4" ht="15">
       <c r="A274" s="30" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="B274" s="28" t="s">
         <v>389</v>
       </c>
       <c r="C274" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D274" s="29">
         <v>1.5</v>
@@ -10527,13 +10496,13 @@
     </row>
     <row r="275" spans="1:4" ht="15">
       <c r="A275" s="28" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="B275" s="28" t="s">
         <v>389</v>
       </c>
       <c r="C275" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D275" s="29">
         <v>30</v>
@@ -10541,13 +10510,13 @@
     </row>
     <row r="276" spans="1:4" ht="15">
       <c r="A276" s="28" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="B276" s="28" t="s">
         <v>389</v>
       </c>
       <c r="C276" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D276" s="29">
         <v>3</v>
@@ -10555,13 +10524,13 @@
     </row>
     <row r="277" spans="1:4" ht="15">
       <c r="A277" s="28" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B277" s="28" t="s">
         <v>389</v>
       </c>
       <c r="C277" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D277" s="29">
         <v>15</v>
@@ -10569,13 +10538,13 @@
     </row>
     <row r="278" spans="1:4" ht="15">
       <c r="A278" s="30" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="B278" s="28" t="s">
         <v>394</v>
       </c>
       <c r="C278" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D278" s="29">
         <v>0</v>
@@ -10583,13 +10552,13 @@
     </row>
     <row r="279" spans="1:4" ht="15">
       <c r="A279" s="30" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="B279" s="28" t="s">
         <v>394</v>
       </c>
       <c r="C279" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D279" s="29">
         <v>30</v>
@@ -10597,13 +10566,13 @@
     </row>
     <row r="280" spans="1:4" ht="15">
       <c r="A280" s="30" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="B280" s="28" t="s">
         <v>394</v>
       </c>
       <c r="C280" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D280" s="29">
         <v>3</v>
@@ -10611,13 +10580,13 @@
     </row>
     <row r="281" spans="1:4" ht="15">
       <c r="A281" s="30" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B281" s="28" t="s">
         <v>394</v>
       </c>
       <c r="C281" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D281" s="29">
         <v>15</v>
@@ -10625,13 +10594,13 @@
     </row>
     <row r="282" spans="1:4" ht="15">
       <c r="A282" s="30" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="B282" s="28" t="s">
         <v>399</v>
       </c>
       <c r="C282" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D282" s="29">
         <v>0</v>
@@ -10639,13 +10608,13 @@
     </row>
     <row r="283" spans="1:4" ht="15">
       <c r="A283" s="30" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="B283" s="28" t="s">
         <v>399</v>
       </c>
       <c r="C283" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D283" s="29">
         <v>30</v>
@@ -10653,13 +10622,13 @@
     </row>
     <row r="284" spans="1:4" ht="15">
       <c r="A284" s="30" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B284" s="28" t="s">
         <v>399</v>
       </c>
       <c r="C284" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D284" s="29">
         <v>3</v>
@@ -10667,13 +10636,13 @@
     </row>
     <row r="285" spans="1:4" ht="15">
       <c r="A285" s="30" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B285" s="28" t="s">
         <v>399</v>
       </c>
       <c r="C285" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D285" s="29">
         <v>15</v>
@@ -10681,13 +10650,13 @@
     </row>
     <row r="286" spans="1:4" ht="15">
       <c r="A286" s="30" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B286" s="28" t="s">
         <v>405</v>
       </c>
       <c r="C286" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D286" s="29">
         <v>3</v>
@@ -10695,13 +10664,13 @@
     </row>
     <row r="287" spans="1:4" ht="15">
       <c r="A287" s="30" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="B287" s="28" t="s">
         <v>405</v>
       </c>
       <c r="C287" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D287" s="29">
         <v>15</v>
@@ -10709,13 +10678,13 @@
     </row>
     <row r="288" spans="1:4" ht="15">
       <c r="A288" s="30" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B288" s="28" t="s">
         <v>405</v>
       </c>
       <c r="C288" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D288" s="29">
         <v>30</v>
@@ -10723,13 +10692,13 @@
     </row>
     <row r="289" spans="1:4" ht="15">
       <c r="A289" s="30" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B289" s="28" t="s">
         <v>405</v>
       </c>
       <c r="C289" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D289" s="29">
         <v>0</v>
@@ -10737,13 +10706,13 @@
     </row>
     <row r="290" spans="1:4" ht="15">
       <c r="A290" s="30" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="B290" s="28" t="s">
         <v>415</v>
       </c>
       <c r="C290" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D290" s="29">
         <v>0</v>
@@ -10751,13 +10720,13 @@
     </row>
     <row r="291" spans="1:4" ht="15">
       <c r="A291" s="30" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B291" s="28" t="s">
         <v>415</v>
       </c>
       <c r="C291" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D291" s="29">
         <v>30</v>
@@ -10765,13 +10734,13 @@
     </row>
     <row r="292" spans="1:4" ht="15">
       <c r="A292" s="30" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="B292" s="28" t="s">
         <v>415</v>
       </c>
       <c r="C292" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D292" s="29">
         <v>3</v>
@@ -10779,13 +10748,13 @@
     </row>
     <row r="293" spans="1:4" ht="15">
       <c r="A293" s="30" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B293" s="28" t="s">
         <v>415</v>
       </c>
       <c r="C293" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D293" s="29">
         <v>15</v>
@@ -10793,13 +10762,13 @@
     </row>
     <row r="294" spans="1:4" ht="15">
       <c r="A294" s="30" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B294" s="28" t="s">
         <v>410</v>
       </c>
       <c r="C294" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D294" s="29">
         <v>15</v>
@@ -10807,13 +10776,13 @@
     </row>
     <row r="295" spans="1:4" ht="15">
       <c r="A295" s="30" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="B295" s="28" t="s">
         <v>410</v>
       </c>
       <c r="C295" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D295" s="29">
         <v>0</v>
@@ -10821,13 +10790,13 @@
     </row>
     <row r="296" spans="1:4" ht="15">
       <c r="A296" s="30" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="B296" s="28" t="s">
         <v>410</v>
       </c>
       <c r="C296" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D296" s="29">
         <v>30</v>
@@ -10835,13 +10804,13 @@
     </row>
     <row r="297" spans="1:4" ht="15">
       <c r="A297" s="30" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B297" s="28" t="s">
         <v>410</v>
       </c>
       <c r="C297" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D297" s="29">
         <v>3</v>
@@ -10849,13 +10818,13 @@
     </row>
     <row r="298" spans="1:4" ht="15">
       <c r="A298" s="30" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="B298" s="28" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C298" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D298" s="29">
         <v>0</v>
@@ -10863,13 +10832,13 @@
     </row>
     <row r="299" spans="1:4" ht="15">
       <c r="A299" s="30" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="B299" s="28" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C299" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D299" s="29">
         <v>30</v>
@@ -10877,13 +10846,13 @@
     </row>
     <row r="300" spans="1:4" ht="15">
       <c r="A300" s="30" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="B300" s="28" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C300" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D300" s="29">
         <v>3</v>
@@ -10891,13 +10860,13 @@
     </row>
     <row r="301" spans="1:4" ht="15">
       <c r="A301" s="30" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B301" s="28" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C301" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D301" s="29">
         <v>15</v>
@@ -10905,13 +10874,13 @@
     </row>
     <row r="302" spans="1:4" ht="15">
       <c r="A302" s="30" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="B302" s="28" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C302" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D302" s="29">
         <v>0</v>
@@ -10919,13 +10888,13 @@
     </row>
     <row r="303" spans="1:4" ht="15">
       <c r="A303" s="30" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B303" s="28" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C303" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D303" s="29">
         <v>30</v>
@@ -10933,13 +10902,13 @@
     </row>
     <row r="304" spans="1:4" ht="15">
       <c r="A304" s="30" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="B304" s="28" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C304" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D304" s="29">
         <v>3</v>
@@ -10947,13 +10916,13 @@
     </row>
     <row r="305" spans="1:4" ht="15">
       <c r="A305" s="30" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B305" s="28" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C305" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D305" s="29">
         <v>15</v>
@@ -10961,13 +10930,13 @@
     </row>
     <row r="306" spans="1:4" ht="15">
       <c r="A306" s="30" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="B306" s="28" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C306" s="28" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D306" s="29">
         <v>0</v>
@@ -10975,13 +10944,13 @@
     </row>
     <row r="307" spans="1:4" ht="15">
       <c r="A307" s="30" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="B307" s="28" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C307" s="28" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D307" s="29">
         <v>30</v>
@@ -10989,13 +10958,13 @@
     </row>
     <row r="308" spans="1:4" ht="15">
       <c r="A308" s="30" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="B308" s="28" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C308" s="28" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D308" s="29">
         <v>3</v>
@@ -11003,13 +10972,13 @@
     </row>
     <row r="309" spans="1:4" ht="15">
       <c r="A309" s="30" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="B309" s="28" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C309" s="28" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D309" s="29">
         <v>15</v>
@@ -11035,409 +11004,409 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="13" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="B2" s="31">
         <v>46023</v>
       </c>
       <c r="C2" s="32" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="13" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="B3" s="31">
         <v>46024</v>
       </c>
       <c r="C3" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="13" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B4" s="31">
         <v>46025</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="B5" s="31">
         <v>46060</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="13" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B6" s="31">
         <v>46084</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="13" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B7" s="31">
         <v>46102</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="13" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="B8" s="31">
         <v>46118</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="13" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B9" s="31">
         <v>46123</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="13" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B10" s="31">
         <v>46125</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="13" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B11" s="31">
         <v>46126</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="13" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B12" s="31">
         <v>46127</v>
       </c>
       <c r="C12" s="32" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="13" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B13" s="31">
         <v>46128</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="13" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B14" s="31">
         <v>46143</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="13" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B15" s="31">
         <v>46144</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="13" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="B16" s="31">
         <v>46146</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="13" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B17" s="31">
         <v>46172</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="13" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B18" s="31">
         <v>46174</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="13" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B19" s="31">
         <v>46176</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="13" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B20" s="31">
         <v>46200</v>
       </c>
       <c r="C20" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="13" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="13" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C22" s="34" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="13" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="13" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="C24" s="32" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="13" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C25" s="34" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="13" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="C26" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="13" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="13" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="13" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" s="13" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" s="13" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" s="13" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C32" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="13" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" s="13" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" s="13" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="13" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="13" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -11484,15 +11453,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="7" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="13" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="B2" s="35" t="b">
         <v>1</v>
@@ -11500,7 +11469,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="13" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="B3" s="26" t="b">
         <v>1</v>
@@ -11508,7 +11477,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="13" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="B4" s="26" t="b">
         <v>1</v>
@@ -11516,7 +11485,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="13" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="B5" s="26" t="b">
         <v>1</v>
@@ -11524,7 +11493,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="13" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="B6" s="25" t="b">
         <v>1</v>
@@ -11532,7 +11501,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="13" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="B7" s="36" t="b">
         <v>1</v>
@@ -11540,7 +11509,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="13" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="B8" s="36" t="b">
         <v>0</v>
